--- a/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
+++ b/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
@@ -48,9 +48,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RECEPTURA_WLASNA'!$A$11:$P$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'RAPORT'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'HISTORIA'!$A$8:$L$208</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BAZA_AUTOCOLOR'!$A$8:$Q$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BAZA_DUXONE'!$A$8:$Q$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PIGMENTY'!$A$8:$L$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BAZA_AUTOCOLOR'!$A$8:$S$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BAZA_DUXONE'!$A$8:$S$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PIGMENTY'!$A$8:$N$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2006,6 +2006,8 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="32" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2036,7 +2038,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Filtruj kolumnę SYSTEM (AUTOCOLOR / DUXONE) oraz NR / NAZWA. AUTOCOLOR 123 i DUXONE 123 to dwa różne pigmenty.</t>
+          <t>Filtruj kolumnę SYSTEM (AUTOCOLOR / DUXONE) oraz NR / NAZWA. AUTOCOLOR 123 i DUXONE 123 to dwa różne pigmenty. Opisy dobarwiania Autocolor — po polsku.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2066,7 +2068,7 @@
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>Włącz filtry w wierszu 8. SYSTEM: AUTOCOLOR lub DUXONE. Wyszukaj numer lub nazwę. Nie wpisuj numerów ręcznie w recepturze — wybierz SYSTEM, potem NR z listy rozwijanej.</t>
+          <t>Włącz filtry w wierszu 8. SYSTEM: AUTOCOLOR lub DUXONE. Wyszukaj numer lub nazwę. Nie wpisuj numerów ręcznie w recepturze — wybierz SYSTEM, potem NR z listy rozwijanej. AUTOCOLOR: nazwa katalogowa EN, opis działania PL (kolumna OPIS_DOBARWIANIA).</t>
         </is>
       </c>
     </row>
@@ -2131,8 +2133,18 @@
           <t>NAZWA_PDF</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t>OPIS_EN</t>
+        </is>
+      </c>
+      <c r="N8" s="26" t="inlineStr">
+        <is>
+          <t>OPIS_DZIALANIA_PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="52">
         <f>BAZA_AUTOCOLOR!A9</f>
         <v/>
@@ -2181,8 +2193,16 @@
         <f>BAZA_AUTOCOLOR!I9</f>
         <v/>
       </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+      <c r="M9" s="52">
+        <f>BAZA_AUTOCOLOR!R9</f>
+        <v/>
+      </c>
+      <c r="N9" s="52">
+        <f>BAZA_AUTOCOLOR!S9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="52">
         <f>BAZA_AUTOCOLOR!A10</f>
         <v/>
@@ -2231,8 +2251,16 @@
         <f>BAZA_AUTOCOLOR!I10</f>
         <v/>
       </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
+      <c r="M10" s="52">
+        <f>BAZA_AUTOCOLOR!R10</f>
+        <v/>
+      </c>
+      <c r="N10" s="52">
+        <f>BAZA_AUTOCOLOR!S10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="52">
         <f>BAZA_AUTOCOLOR!A11</f>
         <v/>
@@ -2281,8 +2309,16 @@
         <f>BAZA_AUTOCOLOR!I11</f>
         <v/>
       </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
+      <c r="M11" s="52">
+        <f>BAZA_AUTOCOLOR!R11</f>
+        <v/>
+      </c>
+      <c r="N11" s="52">
+        <f>BAZA_AUTOCOLOR!S11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="52">
         <f>BAZA_AUTOCOLOR!A12</f>
         <v/>
@@ -2331,8 +2367,16 @@
         <f>BAZA_AUTOCOLOR!I12</f>
         <v/>
       </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+      <c r="M12" s="52">
+        <f>BAZA_AUTOCOLOR!R12</f>
+        <v/>
+      </c>
+      <c r="N12" s="52">
+        <f>BAZA_AUTOCOLOR!S12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="52">
         <f>BAZA_AUTOCOLOR!A13</f>
         <v/>
@@ -2381,8 +2425,16 @@
         <f>BAZA_AUTOCOLOR!I13</f>
         <v/>
       </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
+      <c r="M13" s="52">
+        <f>BAZA_AUTOCOLOR!R13</f>
+        <v/>
+      </c>
+      <c r="N13" s="52">
+        <f>BAZA_AUTOCOLOR!S13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="52">
         <f>BAZA_AUTOCOLOR!A14</f>
         <v/>
@@ -2431,8 +2483,16 @@
         <f>BAZA_AUTOCOLOR!I14</f>
         <v/>
       </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
+      <c r="M14" s="52">
+        <f>BAZA_AUTOCOLOR!R14</f>
+        <v/>
+      </c>
+      <c r="N14" s="52">
+        <f>BAZA_AUTOCOLOR!S14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="52">
         <f>BAZA_AUTOCOLOR!A15</f>
         <v/>
@@ -2481,8 +2541,16 @@
         <f>BAZA_AUTOCOLOR!I15</f>
         <v/>
       </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
+      <c r="M15" s="52">
+        <f>BAZA_AUTOCOLOR!R15</f>
+        <v/>
+      </c>
+      <c r="N15" s="52">
+        <f>BAZA_AUTOCOLOR!S15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="52">
         <f>BAZA_AUTOCOLOR!A16</f>
         <v/>
@@ -2531,8 +2599,16 @@
         <f>BAZA_AUTOCOLOR!I16</f>
         <v/>
       </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
+      <c r="M16" s="52">
+        <f>BAZA_AUTOCOLOR!R16</f>
+        <v/>
+      </c>
+      <c r="N16" s="52">
+        <f>BAZA_AUTOCOLOR!S16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="52">
         <f>BAZA_AUTOCOLOR!A17</f>
         <v/>
@@ -2581,8 +2657,16 @@
         <f>BAZA_AUTOCOLOR!I17</f>
         <v/>
       </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
+      <c r="M17" s="52">
+        <f>BAZA_AUTOCOLOR!R17</f>
+        <v/>
+      </c>
+      <c r="N17" s="52">
+        <f>BAZA_AUTOCOLOR!S17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="52">
         <f>BAZA_AUTOCOLOR!A18</f>
         <v/>
@@ -2631,8 +2715,16 @@
         <f>BAZA_AUTOCOLOR!I18</f>
         <v/>
       </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
+      <c r="M18" s="52">
+        <f>BAZA_AUTOCOLOR!R18</f>
+        <v/>
+      </c>
+      <c r="N18" s="52">
+        <f>BAZA_AUTOCOLOR!S18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="52">
         <f>BAZA_AUTOCOLOR!A19</f>
         <v/>
@@ -2681,8 +2773,16 @@
         <f>BAZA_AUTOCOLOR!I19</f>
         <v/>
       </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
+      <c r="M19" s="52">
+        <f>BAZA_AUTOCOLOR!R19</f>
+        <v/>
+      </c>
+      <c r="N19" s="52">
+        <f>BAZA_AUTOCOLOR!S19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
       <c r="A20" s="52">
         <f>BAZA_AUTOCOLOR!A20</f>
         <v/>
@@ -2731,8 +2831,16 @@
         <f>BAZA_AUTOCOLOR!I20</f>
         <v/>
       </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
+      <c r="M20" s="52">
+        <f>BAZA_AUTOCOLOR!R20</f>
+        <v/>
+      </c>
+      <c r="N20" s="52">
+        <f>BAZA_AUTOCOLOR!S20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
       <c r="A21" s="52">
         <f>BAZA_AUTOCOLOR!A21</f>
         <v/>
@@ -2781,8 +2889,16 @@
         <f>BAZA_AUTOCOLOR!I21</f>
         <v/>
       </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
+      <c r="M21" s="52">
+        <f>BAZA_AUTOCOLOR!R21</f>
+        <v/>
+      </c>
+      <c r="N21" s="52">
+        <f>BAZA_AUTOCOLOR!S21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
       <c r="A22" s="52">
         <f>BAZA_AUTOCOLOR!A22</f>
         <v/>
@@ -2831,8 +2947,16 @@
         <f>BAZA_AUTOCOLOR!I22</f>
         <v/>
       </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
+      <c r="M22" s="52">
+        <f>BAZA_AUTOCOLOR!R22</f>
+        <v/>
+      </c>
+      <c r="N22" s="52">
+        <f>BAZA_AUTOCOLOR!S22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
       <c r="A23" s="52">
         <f>BAZA_AUTOCOLOR!A23</f>
         <v/>
@@ -2881,8 +3005,16 @@
         <f>BAZA_AUTOCOLOR!I23</f>
         <v/>
       </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
+      <c r="M23" s="52">
+        <f>BAZA_AUTOCOLOR!R23</f>
+        <v/>
+      </c>
+      <c r="N23" s="52">
+        <f>BAZA_AUTOCOLOR!S23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="52">
         <f>BAZA_AUTOCOLOR!A24</f>
         <v/>
@@ -2931,8 +3063,16 @@
         <f>BAZA_AUTOCOLOR!I24</f>
         <v/>
       </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
+      <c r="M24" s="52">
+        <f>BAZA_AUTOCOLOR!R24</f>
+        <v/>
+      </c>
+      <c r="N24" s="52">
+        <f>BAZA_AUTOCOLOR!S24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
       <c r="A25" s="52">
         <f>BAZA_AUTOCOLOR!A25</f>
         <v/>
@@ -2981,8 +3121,16 @@
         <f>BAZA_AUTOCOLOR!I25</f>
         <v/>
       </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
+      <c r="M25" s="52">
+        <f>BAZA_AUTOCOLOR!R25</f>
+        <v/>
+      </c>
+      <c r="N25" s="52">
+        <f>BAZA_AUTOCOLOR!S25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="52">
         <f>BAZA_AUTOCOLOR!A26</f>
         <v/>
@@ -3031,8 +3179,16 @@
         <f>BAZA_AUTOCOLOR!I26</f>
         <v/>
       </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
+      <c r="M26" s="52">
+        <f>BAZA_AUTOCOLOR!R26</f>
+        <v/>
+      </c>
+      <c r="N26" s="52">
+        <f>BAZA_AUTOCOLOR!S26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="52">
         <f>BAZA_AUTOCOLOR!A27</f>
         <v/>
@@ -3081,8 +3237,16 @@
         <f>BAZA_AUTOCOLOR!I27</f>
         <v/>
       </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
+      <c r="M27" s="52">
+        <f>BAZA_AUTOCOLOR!R27</f>
+        <v/>
+      </c>
+      <c r="N27" s="52">
+        <f>BAZA_AUTOCOLOR!S27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="52">
         <f>BAZA_AUTOCOLOR!A28</f>
         <v/>
@@ -3131,8 +3295,16 @@
         <f>BAZA_AUTOCOLOR!I28</f>
         <v/>
       </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
+      <c r="M28" s="52">
+        <f>BAZA_AUTOCOLOR!R28</f>
+        <v/>
+      </c>
+      <c r="N28" s="52">
+        <f>BAZA_AUTOCOLOR!S28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
       <c r="A29" s="52">
         <f>BAZA_AUTOCOLOR!A29</f>
         <v/>
@@ -3181,8 +3353,16 @@
         <f>BAZA_AUTOCOLOR!I29</f>
         <v/>
       </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
+      <c r="M29" s="52">
+        <f>BAZA_AUTOCOLOR!R29</f>
+        <v/>
+      </c>
+      <c r="N29" s="52">
+        <f>BAZA_AUTOCOLOR!S29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
       <c r="A30" s="52">
         <f>BAZA_AUTOCOLOR!A30</f>
         <v/>
@@ -3231,8 +3411,16 @@
         <f>BAZA_AUTOCOLOR!I30</f>
         <v/>
       </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
+      <c r="M30" s="52">
+        <f>BAZA_AUTOCOLOR!R30</f>
+        <v/>
+      </c>
+      <c r="N30" s="52">
+        <f>BAZA_AUTOCOLOR!S30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
       <c r="A31" s="52">
         <f>BAZA_AUTOCOLOR!A31</f>
         <v/>
@@ -3281,8 +3469,16 @@
         <f>BAZA_AUTOCOLOR!I31</f>
         <v/>
       </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
+      <c r="M31" s="52">
+        <f>BAZA_AUTOCOLOR!R31</f>
+        <v/>
+      </c>
+      <c r="N31" s="52">
+        <f>BAZA_AUTOCOLOR!S31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
       <c r="A32" s="52">
         <f>BAZA_AUTOCOLOR!A32</f>
         <v/>
@@ -3331,8 +3527,16 @@
         <f>BAZA_AUTOCOLOR!I32</f>
         <v/>
       </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
+      <c r="M32" s="52">
+        <f>BAZA_AUTOCOLOR!R32</f>
+        <v/>
+      </c>
+      <c r="N32" s="52">
+        <f>BAZA_AUTOCOLOR!S32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
       <c r="A33" s="52">
         <f>BAZA_AUTOCOLOR!A33</f>
         <v/>
@@ -3381,8 +3585,16 @@
         <f>BAZA_AUTOCOLOR!I33</f>
         <v/>
       </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
+      <c r="M33" s="52">
+        <f>BAZA_AUTOCOLOR!R33</f>
+        <v/>
+      </c>
+      <c r="N33" s="52">
+        <f>BAZA_AUTOCOLOR!S33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
       <c r="A34" s="52">
         <f>BAZA_AUTOCOLOR!A34</f>
         <v/>
@@ -3431,8 +3643,16 @@
         <f>BAZA_AUTOCOLOR!I34</f>
         <v/>
       </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
+      <c r="M34" s="52">
+        <f>BAZA_AUTOCOLOR!R34</f>
+        <v/>
+      </c>
+      <c r="N34" s="52">
+        <f>BAZA_AUTOCOLOR!S34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
       <c r="A35" s="52">
         <f>BAZA_AUTOCOLOR!A35</f>
         <v/>
@@ -3481,8 +3701,16 @@
         <f>BAZA_AUTOCOLOR!I35</f>
         <v/>
       </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
+      <c r="M35" s="52">
+        <f>BAZA_AUTOCOLOR!R35</f>
+        <v/>
+      </c>
+      <c r="N35" s="52">
+        <f>BAZA_AUTOCOLOR!S35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
       <c r="A36" s="52">
         <f>BAZA_AUTOCOLOR!A36</f>
         <v/>
@@ -3531,8 +3759,16 @@
         <f>BAZA_AUTOCOLOR!I36</f>
         <v/>
       </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
+      <c r="M36" s="52">
+        <f>BAZA_AUTOCOLOR!R36</f>
+        <v/>
+      </c>
+      <c r="N36" s="52">
+        <f>BAZA_AUTOCOLOR!S36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="52">
         <f>BAZA_AUTOCOLOR!A37</f>
         <v/>
@@ -3581,8 +3817,16 @@
         <f>BAZA_AUTOCOLOR!I37</f>
         <v/>
       </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
+      <c r="M37" s="52">
+        <f>BAZA_AUTOCOLOR!R37</f>
+        <v/>
+      </c>
+      <c r="N37" s="52">
+        <f>BAZA_AUTOCOLOR!S37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
       <c r="A38" s="52">
         <f>BAZA_AUTOCOLOR!A38</f>
         <v/>
@@ -3631,8 +3875,16 @@
         <f>BAZA_AUTOCOLOR!I38</f>
         <v/>
       </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
+      <c r="M38" s="52">
+        <f>BAZA_AUTOCOLOR!R38</f>
+        <v/>
+      </c>
+      <c r="N38" s="52">
+        <f>BAZA_AUTOCOLOR!S38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
       <c r="A39" s="52">
         <f>BAZA_AUTOCOLOR!A39</f>
         <v/>
@@ -3681,8 +3933,16 @@
         <f>BAZA_AUTOCOLOR!I39</f>
         <v/>
       </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
+      <c r="M39" s="52">
+        <f>BAZA_AUTOCOLOR!R39</f>
+        <v/>
+      </c>
+      <c r="N39" s="52">
+        <f>BAZA_AUTOCOLOR!S39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
       <c r="A40" s="52">
         <f>BAZA_AUTOCOLOR!A40</f>
         <v/>
@@ -3731,8 +3991,16 @@
         <f>BAZA_AUTOCOLOR!I40</f>
         <v/>
       </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
+      <c r="M40" s="52">
+        <f>BAZA_AUTOCOLOR!R40</f>
+        <v/>
+      </c>
+      <c r="N40" s="52">
+        <f>BAZA_AUTOCOLOR!S40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
       <c r="A41" s="52">
         <f>BAZA_AUTOCOLOR!A41</f>
         <v/>
@@ -3781,8 +4049,16 @@
         <f>BAZA_AUTOCOLOR!I41</f>
         <v/>
       </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
+      <c r="M41" s="52">
+        <f>BAZA_AUTOCOLOR!R41</f>
+        <v/>
+      </c>
+      <c r="N41" s="52">
+        <f>BAZA_AUTOCOLOR!S41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
       <c r="A42" s="52">
         <f>BAZA_AUTOCOLOR!A42</f>
         <v/>
@@ -3831,8 +4107,16 @@
         <f>BAZA_AUTOCOLOR!I42</f>
         <v/>
       </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
+      <c r="M42" s="52">
+        <f>BAZA_AUTOCOLOR!R42</f>
+        <v/>
+      </c>
+      <c r="N42" s="52">
+        <f>BAZA_AUTOCOLOR!S42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
       <c r="A43" s="52">
         <f>BAZA_AUTOCOLOR!A43</f>
         <v/>
@@ -3881,8 +4165,16 @@
         <f>BAZA_AUTOCOLOR!I43</f>
         <v/>
       </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
+      <c r="M43" s="52">
+        <f>BAZA_AUTOCOLOR!R43</f>
+        <v/>
+      </c>
+      <c r="N43" s="52">
+        <f>BAZA_AUTOCOLOR!S43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
       <c r="A44" s="52">
         <f>BAZA_AUTOCOLOR!A44</f>
         <v/>
@@ -3931,8 +4223,16 @@
         <f>BAZA_AUTOCOLOR!I44</f>
         <v/>
       </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
+      <c r="M44" s="52">
+        <f>BAZA_AUTOCOLOR!R44</f>
+        <v/>
+      </c>
+      <c r="N44" s="52">
+        <f>BAZA_AUTOCOLOR!S44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
       <c r="A45" s="52">
         <f>BAZA_AUTOCOLOR!A45</f>
         <v/>
@@ -3981,8 +4281,16 @@
         <f>BAZA_AUTOCOLOR!I45</f>
         <v/>
       </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
+      <c r="M45" s="52">
+        <f>BAZA_AUTOCOLOR!R45</f>
+        <v/>
+      </c>
+      <c r="N45" s="52">
+        <f>BAZA_AUTOCOLOR!S45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
       <c r="A46" s="52">
         <f>BAZA_AUTOCOLOR!A46</f>
         <v/>
@@ -4031,8 +4339,16 @@
         <f>BAZA_AUTOCOLOR!I46</f>
         <v/>
       </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
+      <c r="M46" s="52">
+        <f>BAZA_AUTOCOLOR!R46</f>
+        <v/>
+      </c>
+      <c r="N46" s="52">
+        <f>BAZA_AUTOCOLOR!S46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
       <c r="A47" s="52">
         <f>BAZA_AUTOCOLOR!A47</f>
         <v/>
@@ -4081,8 +4397,16 @@
         <f>BAZA_AUTOCOLOR!I47</f>
         <v/>
       </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
+      <c r="M47" s="52">
+        <f>BAZA_AUTOCOLOR!R47</f>
+        <v/>
+      </c>
+      <c r="N47" s="52">
+        <f>BAZA_AUTOCOLOR!S47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
       <c r="A48" s="52">
         <f>BAZA_AUTOCOLOR!A48</f>
         <v/>
@@ -4131,8 +4455,16 @@
         <f>BAZA_AUTOCOLOR!I48</f>
         <v/>
       </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
+      <c r="M48" s="52">
+        <f>BAZA_AUTOCOLOR!R48</f>
+        <v/>
+      </c>
+      <c r="N48" s="52">
+        <f>BAZA_AUTOCOLOR!S48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
       <c r="A49" s="52">
         <f>BAZA_AUTOCOLOR!A49</f>
         <v/>
@@ -4181,8 +4513,16 @@
         <f>BAZA_AUTOCOLOR!I49</f>
         <v/>
       </c>
-    </row>
-    <row r="50" ht="32" customHeight="1">
+      <c r="M49" s="52">
+        <f>BAZA_AUTOCOLOR!R49</f>
+        <v/>
+      </c>
+      <c r="N49" s="52">
+        <f>BAZA_AUTOCOLOR!S49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
       <c r="A50" s="52">
         <f>BAZA_AUTOCOLOR!A50</f>
         <v/>
@@ -4231,8 +4571,16 @@
         <f>BAZA_AUTOCOLOR!I50</f>
         <v/>
       </c>
-    </row>
-    <row r="51" ht="32" customHeight="1">
+      <c r="M50" s="52">
+        <f>BAZA_AUTOCOLOR!R50</f>
+        <v/>
+      </c>
+      <c r="N50" s="52">
+        <f>BAZA_AUTOCOLOR!S50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
       <c r="A51" s="52">
         <f>BAZA_AUTOCOLOR!A51</f>
         <v/>
@@ -4281,8 +4629,16 @@
         <f>BAZA_AUTOCOLOR!I51</f>
         <v/>
       </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
+      <c r="M51" s="52">
+        <f>BAZA_AUTOCOLOR!R51</f>
+        <v/>
+      </c>
+      <c r="N51" s="52">
+        <f>BAZA_AUTOCOLOR!S51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
       <c r="A52" s="52">
         <f>BAZA_AUTOCOLOR!A52</f>
         <v/>
@@ -4331,8 +4687,16 @@
         <f>BAZA_AUTOCOLOR!I52</f>
         <v/>
       </c>
-    </row>
-    <row r="53" ht="32" customHeight="1">
+      <c r="M52" s="52">
+        <f>BAZA_AUTOCOLOR!R52</f>
+        <v/>
+      </c>
+      <c r="N52" s="52">
+        <f>BAZA_AUTOCOLOR!S52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
       <c r="A53" s="52">
         <f>BAZA_AUTOCOLOR!A53</f>
         <v/>
@@ -4381,8 +4745,16 @@
         <f>BAZA_AUTOCOLOR!I53</f>
         <v/>
       </c>
-    </row>
-    <row r="54" ht="32" customHeight="1">
+      <c r="M53" s="52">
+        <f>BAZA_AUTOCOLOR!R53</f>
+        <v/>
+      </c>
+      <c r="N53" s="52">
+        <f>BAZA_AUTOCOLOR!S53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
       <c r="A54" s="52">
         <f>BAZA_AUTOCOLOR!A54</f>
         <v/>
@@ -4431,8 +4803,16 @@
         <f>BAZA_AUTOCOLOR!I54</f>
         <v/>
       </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
+      <c r="M54" s="52">
+        <f>BAZA_AUTOCOLOR!R54</f>
+        <v/>
+      </c>
+      <c r="N54" s="52">
+        <f>BAZA_AUTOCOLOR!S54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
       <c r="A55" s="52">
         <f>BAZA_AUTOCOLOR!A55</f>
         <v/>
@@ -4481,8 +4861,16 @@
         <f>BAZA_AUTOCOLOR!I55</f>
         <v/>
       </c>
-    </row>
-    <row r="56" ht="32" customHeight="1">
+      <c r="M55" s="52">
+        <f>BAZA_AUTOCOLOR!R55</f>
+        <v/>
+      </c>
+      <c r="N55" s="52">
+        <f>BAZA_AUTOCOLOR!S55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
       <c r="A56" s="52">
         <f>BAZA_AUTOCOLOR!A56</f>
         <v/>
@@ -4531,8 +4919,16 @@
         <f>BAZA_AUTOCOLOR!I56</f>
         <v/>
       </c>
-    </row>
-    <row r="57" ht="32" customHeight="1">
+      <c r="M56" s="52">
+        <f>BAZA_AUTOCOLOR!R56</f>
+        <v/>
+      </c>
+      <c r="N56" s="52">
+        <f>BAZA_AUTOCOLOR!S56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
       <c r="A57" s="52">
         <f>BAZA_AUTOCOLOR!A57</f>
         <v/>
@@ -4581,8 +4977,16 @@
         <f>BAZA_AUTOCOLOR!I57</f>
         <v/>
       </c>
-    </row>
-    <row r="58" ht="32" customHeight="1">
+      <c r="M57" s="52">
+        <f>BAZA_AUTOCOLOR!R57</f>
+        <v/>
+      </c>
+      <c r="N57" s="52">
+        <f>BAZA_AUTOCOLOR!S57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
       <c r="A58" s="52">
         <f>BAZA_AUTOCOLOR!A58</f>
         <v/>
@@ -4631,8 +5035,16 @@
         <f>BAZA_AUTOCOLOR!I58</f>
         <v/>
       </c>
-    </row>
-    <row r="59" ht="32" customHeight="1">
+      <c r="M58" s="52">
+        <f>BAZA_AUTOCOLOR!R58</f>
+        <v/>
+      </c>
+      <c r="N58" s="52">
+        <f>BAZA_AUTOCOLOR!S58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
       <c r="A59" s="52">
         <f>BAZA_AUTOCOLOR!A59</f>
         <v/>
@@ -4681,8 +5093,16 @@
         <f>BAZA_AUTOCOLOR!I59</f>
         <v/>
       </c>
-    </row>
-    <row r="60" ht="32" customHeight="1">
+      <c r="M59" s="52">
+        <f>BAZA_AUTOCOLOR!R59</f>
+        <v/>
+      </c>
+      <c r="N59" s="52">
+        <f>BAZA_AUTOCOLOR!S59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
       <c r="A60" s="52">
         <f>BAZA_AUTOCOLOR!A60</f>
         <v/>
@@ -4731,8 +5151,16 @@
         <f>BAZA_AUTOCOLOR!I60</f>
         <v/>
       </c>
-    </row>
-    <row r="61" ht="32" customHeight="1">
+      <c r="M60" s="52">
+        <f>BAZA_AUTOCOLOR!R60</f>
+        <v/>
+      </c>
+      <c r="N60" s="52">
+        <f>BAZA_AUTOCOLOR!S60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
       <c r="A61" s="52">
         <f>BAZA_AUTOCOLOR!A61</f>
         <v/>
@@ -4781,8 +5209,16 @@
         <f>BAZA_AUTOCOLOR!I61</f>
         <v/>
       </c>
-    </row>
-    <row r="62" ht="32" customHeight="1">
+      <c r="M61" s="52">
+        <f>BAZA_AUTOCOLOR!R61</f>
+        <v/>
+      </c>
+      <c r="N61" s="52">
+        <f>BAZA_AUTOCOLOR!S61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
       <c r="A62" s="52">
         <f>BAZA_AUTOCOLOR!A62</f>
         <v/>
@@ -4831,8 +5267,16 @@
         <f>BAZA_AUTOCOLOR!I62</f>
         <v/>
       </c>
-    </row>
-    <row r="63" ht="32" customHeight="1">
+      <c r="M62" s="52">
+        <f>BAZA_AUTOCOLOR!R62</f>
+        <v/>
+      </c>
+      <c r="N62" s="52">
+        <f>BAZA_AUTOCOLOR!S62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
       <c r="A63" s="52">
         <f>BAZA_AUTOCOLOR!A63</f>
         <v/>
@@ -4881,8 +5325,16 @@
         <f>BAZA_AUTOCOLOR!I63</f>
         <v/>
       </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
+      <c r="M63" s="52">
+        <f>BAZA_AUTOCOLOR!R63</f>
+        <v/>
+      </c>
+      <c r="N63" s="52">
+        <f>BAZA_AUTOCOLOR!S63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
       <c r="A64" s="52">
         <f>BAZA_AUTOCOLOR!A64</f>
         <v/>
@@ -4931,8 +5383,16 @@
         <f>BAZA_AUTOCOLOR!I64</f>
         <v/>
       </c>
-    </row>
-    <row r="65" ht="32" customHeight="1">
+      <c r="M64" s="52">
+        <f>BAZA_AUTOCOLOR!R64</f>
+        <v/>
+      </c>
+      <c r="N64" s="52">
+        <f>BAZA_AUTOCOLOR!S64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
       <c r="A65" s="52">
         <f>BAZA_AUTOCOLOR!A65</f>
         <v/>
@@ -4981,8 +5441,16 @@
         <f>BAZA_AUTOCOLOR!I65</f>
         <v/>
       </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
+      <c r="M65" s="52">
+        <f>BAZA_AUTOCOLOR!R65</f>
+        <v/>
+      </c>
+      <c r="N65" s="52">
+        <f>BAZA_AUTOCOLOR!S65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
       <c r="A66" s="52">
         <f>BAZA_AUTOCOLOR!A66</f>
         <v/>
@@ -5031,8 +5499,16 @@
         <f>BAZA_AUTOCOLOR!I66</f>
         <v/>
       </c>
-    </row>
-    <row r="67" ht="32" customHeight="1">
+      <c r="M66" s="52">
+        <f>BAZA_AUTOCOLOR!R66</f>
+        <v/>
+      </c>
+      <c r="N66" s="52">
+        <f>BAZA_AUTOCOLOR!S66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
       <c r="A67" s="52">
         <f>BAZA_AUTOCOLOR!A67</f>
         <v/>
@@ -5081,8 +5557,16 @@
         <f>BAZA_AUTOCOLOR!I67</f>
         <v/>
       </c>
-    </row>
-    <row r="68" ht="32" customHeight="1">
+      <c r="M67" s="52">
+        <f>BAZA_AUTOCOLOR!R67</f>
+        <v/>
+      </c>
+      <c r="N67" s="52">
+        <f>BAZA_AUTOCOLOR!S67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
       <c r="A68" s="52">
         <f>BAZA_AUTOCOLOR!A68</f>
         <v/>
@@ -5131,8 +5615,16 @@
         <f>BAZA_AUTOCOLOR!I68</f>
         <v/>
       </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
+      <c r="M68" s="52">
+        <f>BAZA_AUTOCOLOR!R68</f>
+        <v/>
+      </c>
+      <c r="N68" s="52">
+        <f>BAZA_AUTOCOLOR!S68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
       <c r="A69" s="52">
         <f>BAZA_AUTOCOLOR!A69</f>
         <v/>
@@ -5181,8 +5673,16 @@
         <f>BAZA_AUTOCOLOR!I69</f>
         <v/>
       </c>
-    </row>
-    <row r="70" ht="32" customHeight="1">
+      <c r="M69" s="52">
+        <f>BAZA_AUTOCOLOR!R69</f>
+        <v/>
+      </c>
+      <c r="N69" s="52">
+        <f>BAZA_AUTOCOLOR!S69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
       <c r="A70" s="52">
         <f>BAZA_AUTOCOLOR!A70</f>
         <v/>
@@ -5231,8 +5731,16 @@
         <f>BAZA_AUTOCOLOR!I70</f>
         <v/>
       </c>
-    </row>
-    <row r="71" ht="32" customHeight="1">
+      <c r="M70" s="52">
+        <f>BAZA_AUTOCOLOR!R70</f>
+        <v/>
+      </c>
+      <c r="N70" s="52">
+        <f>BAZA_AUTOCOLOR!S70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
       <c r="A71" s="52">
         <f>BAZA_AUTOCOLOR!A71</f>
         <v/>
@@ -5281,8 +5789,16 @@
         <f>BAZA_AUTOCOLOR!I71</f>
         <v/>
       </c>
-    </row>
-    <row r="72" ht="32" customHeight="1">
+      <c r="M71" s="52">
+        <f>BAZA_AUTOCOLOR!R71</f>
+        <v/>
+      </c>
+      <c r="N71" s="52">
+        <f>BAZA_AUTOCOLOR!S71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
       <c r="A72" s="52">
         <f>BAZA_AUTOCOLOR!A72</f>
         <v/>
@@ -5331,8 +5847,16 @@
         <f>BAZA_AUTOCOLOR!I72</f>
         <v/>
       </c>
-    </row>
-    <row r="73" ht="32" customHeight="1">
+      <c r="M72" s="52">
+        <f>BAZA_AUTOCOLOR!R72</f>
+        <v/>
+      </c>
+      <c r="N72" s="52">
+        <f>BAZA_AUTOCOLOR!S72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
       <c r="A73" s="52">
         <f>BAZA_AUTOCOLOR!A73</f>
         <v/>
@@ -5381,8 +5905,16 @@
         <f>BAZA_AUTOCOLOR!I73</f>
         <v/>
       </c>
-    </row>
-    <row r="74" ht="32" customHeight="1">
+      <c r="M73" s="52">
+        <f>BAZA_AUTOCOLOR!R73</f>
+        <v/>
+      </c>
+      <c r="N73" s="52">
+        <f>BAZA_AUTOCOLOR!S73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
       <c r="A74" s="52">
         <f>BAZA_AUTOCOLOR!A74</f>
         <v/>
@@ -5431,8 +5963,16 @@
         <f>BAZA_AUTOCOLOR!I74</f>
         <v/>
       </c>
-    </row>
-    <row r="75" ht="32" customHeight="1">
+      <c r="M74" s="52">
+        <f>BAZA_AUTOCOLOR!R74</f>
+        <v/>
+      </c>
+      <c r="N74" s="52">
+        <f>BAZA_AUTOCOLOR!S74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
       <c r="A75" s="52">
         <f>BAZA_AUTOCOLOR!A75</f>
         <v/>
@@ -5481,8 +6021,16 @@
         <f>BAZA_AUTOCOLOR!I75</f>
         <v/>
       </c>
-    </row>
-    <row r="76" ht="32" customHeight="1">
+      <c r="M75" s="52">
+        <f>BAZA_AUTOCOLOR!R75</f>
+        <v/>
+      </c>
+      <c r="N75" s="52">
+        <f>BAZA_AUTOCOLOR!S75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
       <c r="A76" s="52">
         <f>BAZA_AUTOCOLOR!A76</f>
         <v/>
@@ -5531,8 +6079,16 @@
         <f>BAZA_AUTOCOLOR!I76</f>
         <v/>
       </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
+      <c r="M76" s="52">
+        <f>BAZA_AUTOCOLOR!R76</f>
+        <v/>
+      </c>
+      <c r="N76" s="52">
+        <f>BAZA_AUTOCOLOR!S76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
       <c r="A77" s="52">
         <f>BAZA_AUTOCOLOR!A77</f>
         <v/>
@@ -5581,8 +6137,16 @@
         <f>BAZA_AUTOCOLOR!I77</f>
         <v/>
       </c>
-    </row>
-    <row r="78" ht="32" customHeight="1">
+      <c r="M77" s="52">
+        <f>BAZA_AUTOCOLOR!R77</f>
+        <v/>
+      </c>
+      <c r="N77" s="52">
+        <f>BAZA_AUTOCOLOR!S77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
       <c r="A78" s="52">
         <f>BAZA_AUTOCOLOR!A78</f>
         <v/>
@@ -5631,8 +6195,16 @@
         <f>BAZA_AUTOCOLOR!I78</f>
         <v/>
       </c>
-    </row>
-    <row r="79" ht="32" customHeight="1">
+      <c r="M78" s="52">
+        <f>BAZA_AUTOCOLOR!R78</f>
+        <v/>
+      </c>
+      <c r="N78" s="52">
+        <f>BAZA_AUTOCOLOR!S78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
       <c r="A79" s="52">
         <f>BAZA_AUTOCOLOR!A79</f>
         <v/>
@@ -5681,8 +6253,16 @@
         <f>BAZA_AUTOCOLOR!I79</f>
         <v/>
       </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
+      <c r="M79" s="52">
+        <f>BAZA_AUTOCOLOR!R79</f>
+        <v/>
+      </c>
+      <c r="N79" s="52">
+        <f>BAZA_AUTOCOLOR!S79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
       <c r="A80" s="52">
         <f>BAZA_AUTOCOLOR!A80</f>
         <v/>
@@ -5731,8 +6311,16 @@
         <f>BAZA_AUTOCOLOR!I80</f>
         <v/>
       </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
+      <c r="M80" s="52">
+        <f>BAZA_AUTOCOLOR!R80</f>
+        <v/>
+      </c>
+      <c r="N80" s="52">
+        <f>BAZA_AUTOCOLOR!S80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
       <c r="A81" s="52">
         <f>BAZA_AUTOCOLOR!A81</f>
         <v/>
@@ -5781,8 +6369,16 @@
         <f>BAZA_AUTOCOLOR!I81</f>
         <v/>
       </c>
-    </row>
-    <row r="82" ht="32" customHeight="1">
+      <c r="M81" s="52">
+        <f>BAZA_AUTOCOLOR!R81</f>
+        <v/>
+      </c>
+      <c r="N81" s="52">
+        <f>BAZA_AUTOCOLOR!S81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
       <c r="A82" s="52">
         <f>BAZA_AUTOCOLOR!A82</f>
         <v/>
@@ -5831,8 +6427,16 @@
         <f>BAZA_AUTOCOLOR!I82</f>
         <v/>
       </c>
-    </row>
-    <row r="83" ht="32" customHeight="1">
+      <c r="M82" s="52">
+        <f>BAZA_AUTOCOLOR!R82</f>
+        <v/>
+      </c>
+      <c r="N82" s="52">
+        <f>BAZA_AUTOCOLOR!S82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
       <c r="A83" s="52">
         <f>BAZA_AUTOCOLOR!A83</f>
         <v/>
@@ -5881,8 +6485,16 @@
         <f>BAZA_AUTOCOLOR!I83</f>
         <v/>
       </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
+      <c r="M83" s="52">
+        <f>BAZA_AUTOCOLOR!R83</f>
+        <v/>
+      </c>
+      <c r="N83" s="52">
+        <f>BAZA_AUTOCOLOR!S83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
       <c r="A84" s="52">
         <f>BAZA_AUTOCOLOR!A84</f>
         <v/>
@@ -5931,8 +6543,16 @@
         <f>BAZA_AUTOCOLOR!I84</f>
         <v/>
       </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
+      <c r="M84" s="52">
+        <f>BAZA_AUTOCOLOR!R84</f>
+        <v/>
+      </c>
+      <c r="N84" s="52">
+        <f>BAZA_AUTOCOLOR!S84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
       <c r="A85" s="52">
         <f>BAZA_AUTOCOLOR!A85</f>
         <v/>
@@ -5981,8 +6601,16 @@
         <f>BAZA_AUTOCOLOR!I85</f>
         <v/>
       </c>
-    </row>
-    <row r="86" ht="32" customHeight="1">
+      <c r="M85" s="52">
+        <f>BAZA_AUTOCOLOR!R85</f>
+        <v/>
+      </c>
+      <c r="N85" s="52">
+        <f>BAZA_AUTOCOLOR!S85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
       <c r="A86" s="52">
         <f>BAZA_AUTOCOLOR!A86</f>
         <v/>
@@ -6031,8 +6659,16 @@
         <f>BAZA_AUTOCOLOR!I86</f>
         <v/>
       </c>
-    </row>
-    <row r="87" ht="32" customHeight="1">
+      <c r="M86" s="52">
+        <f>BAZA_AUTOCOLOR!R86</f>
+        <v/>
+      </c>
+      <c r="N86" s="52">
+        <f>BAZA_AUTOCOLOR!S86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
       <c r="A87" s="52">
         <f>BAZA_AUTOCOLOR!A87</f>
         <v/>
@@ -6081,8 +6717,16 @@
         <f>BAZA_AUTOCOLOR!I87</f>
         <v/>
       </c>
-    </row>
-    <row r="88" ht="32" customHeight="1">
+      <c r="M87" s="52">
+        <f>BAZA_AUTOCOLOR!R87</f>
+        <v/>
+      </c>
+      <c r="N87" s="52">
+        <f>BAZA_AUTOCOLOR!S87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
       <c r="A88" s="52">
         <f>BAZA_AUTOCOLOR!A88</f>
         <v/>
@@ -6131,8 +6775,16 @@
         <f>BAZA_AUTOCOLOR!I88</f>
         <v/>
       </c>
-    </row>
-    <row r="89" ht="32" customHeight="1">
+      <c r="M88" s="52">
+        <f>BAZA_AUTOCOLOR!R88</f>
+        <v/>
+      </c>
+      <c r="N88" s="52">
+        <f>BAZA_AUTOCOLOR!S88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
       <c r="A89" s="52">
         <f>BAZA_AUTOCOLOR!A89</f>
         <v/>
@@ -6181,8 +6833,16 @@
         <f>BAZA_AUTOCOLOR!I89</f>
         <v/>
       </c>
-    </row>
-    <row r="90" ht="32" customHeight="1">
+      <c r="M89" s="52">
+        <f>BAZA_AUTOCOLOR!R89</f>
+        <v/>
+      </c>
+      <c r="N89" s="52">
+        <f>BAZA_AUTOCOLOR!S89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
       <c r="A90" s="52">
         <f>BAZA_AUTOCOLOR!A90</f>
         <v/>
@@ -6231,8 +6891,16 @@
         <f>BAZA_AUTOCOLOR!I90</f>
         <v/>
       </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
+      <c r="M90" s="52">
+        <f>BAZA_AUTOCOLOR!R90</f>
+        <v/>
+      </c>
+      <c r="N90" s="52">
+        <f>BAZA_AUTOCOLOR!S90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
       <c r="A91" s="52">
         <f>BAZA_AUTOCOLOR!A91</f>
         <v/>
@@ -6281,8 +6949,16 @@
         <f>BAZA_AUTOCOLOR!I91</f>
         <v/>
       </c>
-    </row>
-    <row r="92" ht="32" customHeight="1">
+      <c r="M91" s="52">
+        <f>BAZA_AUTOCOLOR!R91</f>
+        <v/>
+      </c>
+      <c r="N91" s="52">
+        <f>BAZA_AUTOCOLOR!S91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
       <c r="A92" s="52">
         <f>BAZA_AUTOCOLOR!A92</f>
         <v/>
@@ -6331,8 +7007,16 @@
         <f>BAZA_AUTOCOLOR!I92</f>
         <v/>
       </c>
-    </row>
-    <row r="93" ht="32" customHeight="1">
+      <c r="M92" s="52">
+        <f>BAZA_AUTOCOLOR!R92</f>
+        <v/>
+      </c>
+      <c r="N92" s="52">
+        <f>BAZA_AUTOCOLOR!S92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
       <c r="A93" s="52">
         <f>BAZA_AUTOCOLOR!A93</f>
         <v/>
@@ -6381,8 +7065,16 @@
         <f>BAZA_AUTOCOLOR!I93</f>
         <v/>
       </c>
-    </row>
-    <row r="94" ht="32" customHeight="1">
+      <c r="M93" s="52">
+        <f>BAZA_AUTOCOLOR!R93</f>
+        <v/>
+      </c>
+      <c r="N93" s="52">
+        <f>BAZA_AUTOCOLOR!S93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
       <c r="A94" s="52">
         <f>BAZA_AUTOCOLOR!A94</f>
         <v/>
@@ -6431,8 +7123,16 @@
         <f>BAZA_AUTOCOLOR!I94</f>
         <v/>
       </c>
-    </row>
-    <row r="95" ht="32" customHeight="1">
+      <c r="M94" s="52">
+        <f>BAZA_AUTOCOLOR!R94</f>
+        <v/>
+      </c>
+      <c r="N94" s="52">
+        <f>BAZA_AUTOCOLOR!S94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
       <c r="A95" s="52">
         <f>BAZA_AUTOCOLOR!A95</f>
         <v/>
@@ -6481,8 +7181,16 @@
         <f>BAZA_AUTOCOLOR!I95</f>
         <v/>
       </c>
-    </row>
-    <row r="96" ht="32" customHeight="1">
+      <c r="M95" s="52">
+        <f>BAZA_AUTOCOLOR!R95</f>
+        <v/>
+      </c>
+      <c r="N95" s="52">
+        <f>BAZA_AUTOCOLOR!S95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
       <c r="A96" s="52">
         <f>BAZA_AUTOCOLOR!A96</f>
         <v/>
@@ -6531,8 +7239,16 @@
         <f>BAZA_AUTOCOLOR!I96</f>
         <v/>
       </c>
-    </row>
-    <row r="97" ht="32" customHeight="1">
+      <c r="M96" s="52">
+        <f>BAZA_AUTOCOLOR!R96</f>
+        <v/>
+      </c>
+      <c r="N96" s="52">
+        <f>BAZA_AUTOCOLOR!S96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
       <c r="A97" s="52">
         <f>BAZA_AUTOCOLOR!A97</f>
         <v/>
@@ -6581,8 +7297,16 @@
         <f>BAZA_AUTOCOLOR!I97</f>
         <v/>
       </c>
-    </row>
-    <row r="98" ht="32" customHeight="1">
+      <c r="M97" s="52">
+        <f>BAZA_AUTOCOLOR!R97</f>
+        <v/>
+      </c>
+      <c r="N97" s="52">
+        <f>BAZA_AUTOCOLOR!S97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
       <c r="A98" s="52">
         <f>BAZA_AUTOCOLOR!A98</f>
         <v/>
@@ -6631,8 +7355,16 @@
         <f>BAZA_AUTOCOLOR!I98</f>
         <v/>
       </c>
-    </row>
-    <row r="99" ht="32" customHeight="1">
+      <c r="M98" s="52">
+        <f>BAZA_AUTOCOLOR!R98</f>
+        <v/>
+      </c>
+      <c r="N98" s="52">
+        <f>BAZA_AUTOCOLOR!S98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
       <c r="A99" s="52">
         <f>BAZA_AUTOCOLOR!A99</f>
         <v/>
@@ -6681,8 +7413,16 @@
         <f>BAZA_AUTOCOLOR!I99</f>
         <v/>
       </c>
-    </row>
-    <row r="100" ht="32" customHeight="1">
+      <c r="M99" s="52">
+        <f>BAZA_AUTOCOLOR!R99</f>
+        <v/>
+      </c>
+      <c r="N99" s="52">
+        <f>BAZA_AUTOCOLOR!S99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
       <c r="A100" s="52">
         <f>BAZA_AUTOCOLOR!A100</f>
         <v/>
@@ -6731,8 +7471,16 @@
         <f>BAZA_AUTOCOLOR!I100</f>
         <v/>
       </c>
-    </row>
-    <row r="101" ht="32" customHeight="1">
+      <c r="M100" s="52">
+        <f>BAZA_AUTOCOLOR!R100</f>
+        <v/>
+      </c>
+      <c r="N100" s="52">
+        <f>BAZA_AUTOCOLOR!S100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
       <c r="A101" s="52">
         <f>BAZA_AUTOCOLOR!A101</f>
         <v/>
@@ -6781,8 +7529,16 @@
         <f>BAZA_AUTOCOLOR!I101</f>
         <v/>
       </c>
-    </row>
-    <row r="102" ht="32" customHeight="1">
+      <c r="M101" s="52">
+        <f>BAZA_AUTOCOLOR!R101</f>
+        <v/>
+      </c>
+      <c r="N101" s="52">
+        <f>BAZA_AUTOCOLOR!S101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
       <c r="A102" s="52">
         <f>BAZA_AUTOCOLOR!A102</f>
         <v/>
@@ -6831,8 +7587,16 @@
         <f>BAZA_AUTOCOLOR!I102</f>
         <v/>
       </c>
-    </row>
-    <row r="103" ht="32" customHeight="1">
+      <c r="M102" s="52">
+        <f>BAZA_AUTOCOLOR!R102</f>
+        <v/>
+      </c>
+      <c r="N102" s="52">
+        <f>BAZA_AUTOCOLOR!S102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
       <c r="A103" s="52">
         <f>BAZA_AUTOCOLOR!A103</f>
         <v/>
@@ -6881,8 +7645,16 @@
         <f>BAZA_AUTOCOLOR!I103</f>
         <v/>
       </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
+      <c r="M103" s="52">
+        <f>BAZA_AUTOCOLOR!R103</f>
+        <v/>
+      </c>
+      <c r="N103" s="52">
+        <f>BAZA_AUTOCOLOR!S103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
       <c r="A104" s="52">
         <f>BAZA_AUTOCOLOR!A104</f>
         <v/>
@@ -6931,8 +7703,16 @@
         <f>BAZA_AUTOCOLOR!I104</f>
         <v/>
       </c>
-    </row>
-    <row r="105" ht="32" customHeight="1">
+      <c r="M104" s="52">
+        <f>BAZA_AUTOCOLOR!R104</f>
+        <v/>
+      </c>
+      <c r="N104" s="52">
+        <f>BAZA_AUTOCOLOR!S104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
       <c r="A105" s="52">
         <f>BAZA_AUTOCOLOR!A105</f>
         <v/>
@@ -6981,8 +7761,16 @@
         <f>BAZA_AUTOCOLOR!I105</f>
         <v/>
       </c>
-    </row>
-    <row r="106" ht="32" customHeight="1">
+      <c r="M105" s="52">
+        <f>BAZA_AUTOCOLOR!R105</f>
+        <v/>
+      </c>
+      <c r="N105" s="52">
+        <f>BAZA_AUTOCOLOR!S105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
       <c r="A106" s="52">
         <f>BAZA_AUTOCOLOR!A106</f>
         <v/>
@@ -7031,8 +7819,16 @@
         <f>BAZA_AUTOCOLOR!I106</f>
         <v/>
       </c>
-    </row>
-    <row r="107" ht="32" customHeight="1">
+      <c r="M106" s="52">
+        <f>BAZA_AUTOCOLOR!R106</f>
+        <v/>
+      </c>
+      <c r="N106" s="52">
+        <f>BAZA_AUTOCOLOR!S106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
       <c r="A107" s="52">
         <f>BAZA_AUTOCOLOR!A107</f>
         <v/>
@@ -7081,8 +7877,16 @@
         <f>BAZA_AUTOCOLOR!I107</f>
         <v/>
       </c>
-    </row>
-    <row r="108" ht="32" customHeight="1">
+      <c r="M107" s="52">
+        <f>BAZA_AUTOCOLOR!R107</f>
+        <v/>
+      </c>
+      <c r="N107" s="52">
+        <f>BAZA_AUTOCOLOR!S107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
       <c r="A108" s="52">
         <f>BAZA_AUTOCOLOR!A108</f>
         <v/>
@@ -7131,8 +7935,16 @@
         <f>BAZA_AUTOCOLOR!I108</f>
         <v/>
       </c>
-    </row>
-    <row r="109" ht="32" customHeight="1">
+      <c r="M108" s="52">
+        <f>BAZA_AUTOCOLOR!R108</f>
+        <v/>
+      </c>
+      <c r="N108" s="52">
+        <f>BAZA_AUTOCOLOR!S108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="40" customHeight="1">
       <c r="A109" s="52">
         <f>BAZA_AUTOCOLOR!A109</f>
         <v/>
@@ -7181,8 +7993,16 @@
         <f>BAZA_AUTOCOLOR!I109</f>
         <v/>
       </c>
-    </row>
-    <row r="110" ht="32" customHeight="1">
+      <c r="M109" s="52">
+        <f>BAZA_AUTOCOLOR!R109</f>
+        <v/>
+      </c>
+      <c r="N109" s="52">
+        <f>BAZA_AUTOCOLOR!S109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
       <c r="A110" s="52">
         <f>BAZA_AUTOCOLOR!A110</f>
         <v/>
@@ -7231,8 +8051,16 @@
         <f>BAZA_AUTOCOLOR!I110</f>
         <v/>
       </c>
-    </row>
-    <row r="111" ht="32" customHeight="1">
+      <c r="M110" s="52">
+        <f>BAZA_AUTOCOLOR!R110</f>
+        <v/>
+      </c>
+      <c r="N110" s="52">
+        <f>BAZA_AUTOCOLOR!S110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
       <c r="A111" s="52">
         <f>BAZA_AUTOCOLOR!A111</f>
         <v/>
@@ -7281,8 +8109,16 @@
         <f>BAZA_AUTOCOLOR!I111</f>
         <v/>
       </c>
-    </row>
-    <row r="112" ht="32" customHeight="1">
+      <c r="M111" s="52">
+        <f>BAZA_AUTOCOLOR!R111</f>
+        <v/>
+      </c>
+      <c r="N111" s="52">
+        <f>BAZA_AUTOCOLOR!S111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
       <c r="A112" s="52">
         <f>BAZA_AUTOCOLOR!A112</f>
         <v/>
@@ -7331,8 +8167,16 @@
         <f>BAZA_AUTOCOLOR!I112</f>
         <v/>
       </c>
-    </row>
-    <row r="113" ht="32" customHeight="1">
+      <c r="M112" s="52">
+        <f>BAZA_AUTOCOLOR!R112</f>
+        <v/>
+      </c>
+      <c r="N112" s="52">
+        <f>BAZA_AUTOCOLOR!S112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
       <c r="A113" s="52">
         <f>BAZA_AUTOCOLOR!A113</f>
         <v/>
@@ -7381,8 +8225,16 @@
         <f>BAZA_AUTOCOLOR!I113</f>
         <v/>
       </c>
-    </row>
-    <row r="114" ht="32" customHeight="1">
+      <c r="M113" s="52">
+        <f>BAZA_AUTOCOLOR!R113</f>
+        <v/>
+      </c>
+      <c r="N113" s="52">
+        <f>BAZA_AUTOCOLOR!S113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
       <c r="A114" s="52">
         <f>BAZA_AUTOCOLOR!A114</f>
         <v/>
@@ -7431,8 +8283,16 @@
         <f>BAZA_AUTOCOLOR!I114</f>
         <v/>
       </c>
-    </row>
-    <row r="115" ht="32" customHeight="1">
+      <c r="M114" s="52">
+        <f>BAZA_AUTOCOLOR!R114</f>
+        <v/>
+      </c>
+      <c r="N114" s="52">
+        <f>BAZA_AUTOCOLOR!S114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
       <c r="A115" s="52">
         <f>BAZA_AUTOCOLOR!A115</f>
         <v/>
@@ -7481,8 +8341,16 @@
         <f>BAZA_AUTOCOLOR!I115</f>
         <v/>
       </c>
-    </row>
-    <row r="116" ht="32" customHeight="1">
+      <c r="M115" s="52">
+        <f>BAZA_AUTOCOLOR!R115</f>
+        <v/>
+      </c>
+      <c r="N115" s="52">
+        <f>BAZA_AUTOCOLOR!S115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
       <c r="A116" s="52">
         <f>BAZA_DUXONE!A9</f>
         <v/>
@@ -7531,8 +8399,16 @@
         <f>BAZA_DUXONE!I9</f>
         <v/>
       </c>
-    </row>
-    <row r="117" ht="32" customHeight="1">
+      <c r="M116" s="52">
+        <f>BAZA_DUXONE!R9</f>
+        <v/>
+      </c>
+      <c r="N116" s="52">
+        <f>BAZA_DUXONE!S9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
       <c r="A117" s="52">
         <f>BAZA_DUXONE!A10</f>
         <v/>
@@ -7581,8 +8457,16 @@
         <f>BAZA_DUXONE!I10</f>
         <v/>
       </c>
-    </row>
-    <row r="118" ht="32" customHeight="1">
+      <c r="M117" s="52">
+        <f>BAZA_DUXONE!R10</f>
+        <v/>
+      </c>
+      <c r="N117" s="52">
+        <f>BAZA_DUXONE!S10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
       <c r="A118" s="52">
         <f>BAZA_DUXONE!A11</f>
         <v/>
@@ -7631,8 +8515,16 @@
         <f>BAZA_DUXONE!I11</f>
         <v/>
       </c>
-    </row>
-    <row r="119" ht="32" customHeight="1">
+      <c r="M118" s="52">
+        <f>BAZA_DUXONE!R11</f>
+        <v/>
+      </c>
+      <c r="N118" s="52">
+        <f>BAZA_DUXONE!S11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
       <c r="A119" s="52">
         <f>BAZA_DUXONE!A12</f>
         <v/>
@@ -7681,8 +8573,16 @@
         <f>BAZA_DUXONE!I12</f>
         <v/>
       </c>
-    </row>
-    <row r="120" ht="32" customHeight="1">
+      <c r="M119" s="52">
+        <f>BAZA_DUXONE!R12</f>
+        <v/>
+      </c>
+      <c r="N119" s="52">
+        <f>BAZA_DUXONE!S12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
       <c r="A120" s="52">
         <f>BAZA_DUXONE!A13</f>
         <v/>
@@ -7731,8 +8631,16 @@
         <f>BAZA_DUXONE!I13</f>
         <v/>
       </c>
-    </row>
-    <row r="121" ht="32" customHeight="1">
+      <c r="M120" s="52">
+        <f>BAZA_DUXONE!R13</f>
+        <v/>
+      </c>
+      <c r="N120" s="52">
+        <f>BAZA_DUXONE!S13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
       <c r="A121" s="52">
         <f>BAZA_DUXONE!A14</f>
         <v/>
@@ -7781,8 +8689,16 @@
         <f>BAZA_DUXONE!I14</f>
         <v/>
       </c>
-    </row>
-    <row r="122" ht="32" customHeight="1">
+      <c r="M121" s="52">
+        <f>BAZA_DUXONE!R14</f>
+        <v/>
+      </c>
+      <c r="N121" s="52">
+        <f>BAZA_DUXONE!S14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
       <c r="A122" s="52">
         <f>BAZA_DUXONE!A15</f>
         <v/>
@@ -7831,8 +8747,16 @@
         <f>BAZA_DUXONE!I15</f>
         <v/>
       </c>
-    </row>
-    <row r="123" ht="32" customHeight="1">
+      <c r="M122" s="52">
+        <f>BAZA_DUXONE!R15</f>
+        <v/>
+      </c>
+      <c r="N122" s="52">
+        <f>BAZA_DUXONE!S15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
       <c r="A123" s="52">
         <f>BAZA_DUXONE!A16</f>
         <v/>
@@ -7881,8 +8805,16 @@
         <f>BAZA_DUXONE!I16</f>
         <v/>
       </c>
-    </row>
-    <row r="124" ht="32" customHeight="1">
+      <c r="M123" s="52">
+        <f>BAZA_DUXONE!R16</f>
+        <v/>
+      </c>
+      <c r="N123" s="52">
+        <f>BAZA_DUXONE!S16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
       <c r="A124" s="52">
         <f>BAZA_DUXONE!A17</f>
         <v/>
@@ -7931,8 +8863,16 @@
         <f>BAZA_DUXONE!I17</f>
         <v/>
       </c>
-    </row>
-    <row r="125" ht="32" customHeight="1">
+      <c r="M124" s="52">
+        <f>BAZA_DUXONE!R17</f>
+        <v/>
+      </c>
+      <c r="N124" s="52">
+        <f>BAZA_DUXONE!S17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
       <c r="A125" s="52">
         <f>BAZA_DUXONE!A18</f>
         <v/>
@@ -7981,8 +8921,16 @@
         <f>BAZA_DUXONE!I18</f>
         <v/>
       </c>
-    </row>
-    <row r="126" ht="32" customHeight="1">
+      <c r="M125" s="52">
+        <f>BAZA_DUXONE!R18</f>
+        <v/>
+      </c>
+      <c r="N125" s="52">
+        <f>BAZA_DUXONE!S18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
       <c r="A126" s="52">
         <f>BAZA_DUXONE!A19</f>
         <v/>
@@ -8031,8 +8979,16 @@
         <f>BAZA_DUXONE!I19</f>
         <v/>
       </c>
-    </row>
-    <row r="127" ht="32" customHeight="1">
+      <c r="M126" s="52">
+        <f>BAZA_DUXONE!R19</f>
+        <v/>
+      </c>
+      <c r="N126" s="52">
+        <f>BAZA_DUXONE!S19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
       <c r="A127" s="52">
         <f>BAZA_DUXONE!A20</f>
         <v/>
@@ -8081,8 +9037,16 @@
         <f>BAZA_DUXONE!I20</f>
         <v/>
       </c>
-    </row>
-    <row r="128" ht="32" customHeight="1">
+      <c r="M127" s="52">
+        <f>BAZA_DUXONE!R20</f>
+        <v/>
+      </c>
+      <c r="N127" s="52">
+        <f>BAZA_DUXONE!S20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
       <c r="A128" s="52">
         <f>BAZA_DUXONE!A21</f>
         <v/>
@@ -8131,8 +9095,16 @@
         <f>BAZA_DUXONE!I21</f>
         <v/>
       </c>
-    </row>
-    <row r="129" ht="32" customHeight="1">
+      <c r="M128" s="52">
+        <f>BAZA_DUXONE!R21</f>
+        <v/>
+      </c>
+      <c r="N128" s="52">
+        <f>BAZA_DUXONE!S21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
       <c r="A129" s="52">
         <f>BAZA_DUXONE!A22</f>
         <v/>
@@ -8181,8 +9153,16 @@
         <f>BAZA_DUXONE!I22</f>
         <v/>
       </c>
-    </row>
-    <row r="130" ht="32" customHeight="1">
+      <c r="M129" s="52">
+        <f>BAZA_DUXONE!R22</f>
+        <v/>
+      </c>
+      <c r="N129" s="52">
+        <f>BAZA_DUXONE!S22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
       <c r="A130" s="52">
         <f>BAZA_DUXONE!A23</f>
         <v/>
@@ -8231,8 +9211,16 @@
         <f>BAZA_DUXONE!I23</f>
         <v/>
       </c>
-    </row>
-    <row r="131" ht="32" customHeight="1">
+      <c r="M130" s="52">
+        <f>BAZA_DUXONE!R23</f>
+        <v/>
+      </c>
+      <c r="N130" s="52">
+        <f>BAZA_DUXONE!S23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
       <c r="A131" s="52">
         <f>BAZA_DUXONE!A24</f>
         <v/>
@@ -8281,8 +9269,16 @@
         <f>BAZA_DUXONE!I24</f>
         <v/>
       </c>
-    </row>
-    <row r="132" ht="32" customHeight="1">
+      <c r="M131" s="52">
+        <f>BAZA_DUXONE!R24</f>
+        <v/>
+      </c>
+      <c r="N131" s="52">
+        <f>BAZA_DUXONE!S24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
       <c r="A132" s="52">
         <f>BAZA_DUXONE!A25</f>
         <v/>
@@ -8331,8 +9327,16 @@
         <f>BAZA_DUXONE!I25</f>
         <v/>
       </c>
-    </row>
-    <row r="133" ht="32" customHeight="1">
+      <c r="M132" s="52">
+        <f>BAZA_DUXONE!R25</f>
+        <v/>
+      </c>
+      <c r="N132" s="52">
+        <f>BAZA_DUXONE!S25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
       <c r="A133" s="52">
         <f>BAZA_DUXONE!A26</f>
         <v/>
@@ -8381,8 +9385,16 @@
         <f>BAZA_DUXONE!I26</f>
         <v/>
       </c>
-    </row>
-    <row r="134" ht="32" customHeight="1">
+      <c r="M133" s="52">
+        <f>BAZA_DUXONE!R26</f>
+        <v/>
+      </c>
+      <c r="N133" s="52">
+        <f>BAZA_DUXONE!S26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
       <c r="A134" s="52">
         <f>BAZA_DUXONE!A27</f>
         <v/>
@@ -8431,8 +9443,16 @@
         <f>BAZA_DUXONE!I27</f>
         <v/>
       </c>
-    </row>
-    <row r="135" ht="32" customHeight="1">
+      <c r="M134" s="52">
+        <f>BAZA_DUXONE!R27</f>
+        <v/>
+      </c>
+      <c r="N134" s="52">
+        <f>BAZA_DUXONE!S27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
       <c r="A135" s="52">
         <f>BAZA_DUXONE!A28</f>
         <v/>
@@ -8481,8 +9501,16 @@
         <f>BAZA_DUXONE!I28</f>
         <v/>
       </c>
-    </row>
-    <row r="136" ht="32" customHeight="1">
+      <c r="M135" s="52">
+        <f>BAZA_DUXONE!R28</f>
+        <v/>
+      </c>
+      <c r="N135" s="52">
+        <f>BAZA_DUXONE!S28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
       <c r="A136" s="52">
         <f>BAZA_DUXONE!A29</f>
         <v/>
@@ -8531,8 +9559,16 @@
         <f>BAZA_DUXONE!I29</f>
         <v/>
       </c>
-    </row>
-    <row r="137" ht="32" customHeight="1">
+      <c r="M136" s="52">
+        <f>BAZA_DUXONE!R29</f>
+        <v/>
+      </c>
+      <c r="N136" s="52">
+        <f>BAZA_DUXONE!S29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
       <c r="A137" s="52">
         <f>BAZA_DUXONE!A30</f>
         <v/>
@@ -8581,8 +9617,16 @@
         <f>BAZA_DUXONE!I30</f>
         <v/>
       </c>
-    </row>
-    <row r="138" ht="32" customHeight="1">
+      <c r="M137" s="52">
+        <f>BAZA_DUXONE!R30</f>
+        <v/>
+      </c>
+      <c r="N137" s="52">
+        <f>BAZA_DUXONE!S30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
       <c r="A138" s="52">
         <f>BAZA_DUXONE!A31</f>
         <v/>
@@ -8631,8 +9675,16 @@
         <f>BAZA_DUXONE!I31</f>
         <v/>
       </c>
-    </row>
-    <row r="139" ht="32" customHeight="1">
+      <c r="M138" s="52">
+        <f>BAZA_DUXONE!R31</f>
+        <v/>
+      </c>
+      <c r="N138" s="52">
+        <f>BAZA_DUXONE!S31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
       <c r="A139" s="52">
         <f>BAZA_DUXONE!A32</f>
         <v/>
@@ -8681,8 +9733,16 @@
         <f>BAZA_DUXONE!I32</f>
         <v/>
       </c>
-    </row>
-    <row r="140" ht="32" customHeight="1">
+      <c r="M139" s="52">
+        <f>BAZA_DUXONE!R32</f>
+        <v/>
+      </c>
+      <c r="N139" s="52">
+        <f>BAZA_DUXONE!S32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
       <c r="A140" s="52">
         <f>BAZA_DUXONE!A33</f>
         <v/>
@@ -8731,8 +9791,16 @@
         <f>BAZA_DUXONE!I33</f>
         <v/>
       </c>
-    </row>
-    <row r="141" ht="32" customHeight="1">
+      <c r="M140" s="52">
+        <f>BAZA_DUXONE!R33</f>
+        <v/>
+      </c>
+      <c r="N140" s="52">
+        <f>BAZA_DUXONE!S33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
       <c r="A141" s="52">
         <f>BAZA_DUXONE!A34</f>
         <v/>
@@ -8781,8 +9849,16 @@
         <f>BAZA_DUXONE!I34</f>
         <v/>
       </c>
-    </row>
-    <row r="142" ht="32" customHeight="1">
+      <c r="M141" s="52">
+        <f>BAZA_DUXONE!R34</f>
+        <v/>
+      </c>
+      <c r="N141" s="52">
+        <f>BAZA_DUXONE!S34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
       <c r="A142" s="52">
         <f>BAZA_DUXONE!A35</f>
         <v/>
@@ -8831,8 +9907,16 @@
         <f>BAZA_DUXONE!I35</f>
         <v/>
       </c>
-    </row>
-    <row r="143" ht="32" customHeight="1">
+      <c r="M142" s="52">
+        <f>BAZA_DUXONE!R35</f>
+        <v/>
+      </c>
+      <c r="N142" s="52">
+        <f>BAZA_DUXONE!S35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
       <c r="A143" s="52">
         <f>BAZA_DUXONE!A36</f>
         <v/>
@@ -8881,8 +9965,16 @@
         <f>BAZA_DUXONE!I36</f>
         <v/>
       </c>
-    </row>
-    <row r="144" ht="32" customHeight="1">
+      <c r="M143" s="52">
+        <f>BAZA_DUXONE!R36</f>
+        <v/>
+      </c>
+      <c r="N143" s="52">
+        <f>BAZA_DUXONE!S36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
       <c r="A144" s="52">
         <f>BAZA_DUXONE!A37</f>
         <v/>
@@ -8931,8 +10023,16 @@
         <f>BAZA_DUXONE!I37</f>
         <v/>
       </c>
-    </row>
-    <row r="145" ht="32" customHeight="1">
+      <c r="M144" s="52">
+        <f>BAZA_DUXONE!R37</f>
+        <v/>
+      </c>
+      <c r="N144" s="52">
+        <f>BAZA_DUXONE!S37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
       <c r="A145" s="52">
         <f>BAZA_DUXONE!A38</f>
         <v/>
@@ -8981,8 +10081,16 @@
         <f>BAZA_DUXONE!I38</f>
         <v/>
       </c>
-    </row>
-    <row r="146" ht="32" customHeight="1">
+      <c r="M145" s="52">
+        <f>BAZA_DUXONE!R38</f>
+        <v/>
+      </c>
+      <c r="N145" s="52">
+        <f>BAZA_DUXONE!S38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
       <c r="A146" s="52">
         <f>BAZA_DUXONE!A39</f>
         <v/>
@@ -9031,8 +10139,16 @@
         <f>BAZA_DUXONE!I39</f>
         <v/>
       </c>
-    </row>
-    <row r="147" ht="32" customHeight="1">
+      <c r="M146" s="52">
+        <f>BAZA_DUXONE!R39</f>
+        <v/>
+      </c>
+      <c r="N146" s="52">
+        <f>BAZA_DUXONE!S39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
       <c r="A147" s="52">
         <f>BAZA_DUXONE!A40</f>
         <v/>
@@ -9081,8 +10197,16 @@
         <f>BAZA_DUXONE!I40</f>
         <v/>
       </c>
-    </row>
-    <row r="148" ht="32" customHeight="1">
+      <c r="M147" s="52">
+        <f>BAZA_DUXONE!R40</f>
+        <v/>
+      </c>
+      <c r="N147" s="52">
+        <f>BAZA_DUXONE!S40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" ht="40" customHeight="1">
       <c r="A148" s="52">
         <f>BAZA_DUXONE!A41</f>
         <v/>
@@ -9131,8 +10255,16 @@
         <f>BAZA_DUXONE!I41</f>
         <v/>
       </c>
-    </row>
-    <row r="149" ht="32" customHeight="1">
+      <c r="M148" s="52">
+        <f>BAZA_DUXONE!R41</f>
+        <v/>
+      </c>
+      <c r="N148" s="52">
+        <f>BAZA_DUXONE!S41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" ht="40" customHeight="1">
       <c r="A149" s="52">
         <f>BAZA_DUXONE!A42</f>
         <v/>
@@ -9181,8 +10313,16 @@
         <f>BAZA_DUXONE!I42</f>
         <v/>
       </c>
-    </row>
-    <row r="150" ht="32" customHeight="1">
+      <c r="M149" s="52">
+        <f>BAZA_DUXONE!R42</f>
+        <v/>
+      </c>
+      <c r="N149" s="52">
+        <f>BAZA_DUXONE!S42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" ht="40" customHeight="1">
       <c r="A150" s="52">
         <f>BAZA_DUXONE!A43</f>
         <v/>
@@ -9231,8 +10371,16 @@
         <f>BAZA_DUXONE!I43</f>
         <v/>
       </c>
-    </row>
-    <row r="151" ht="32" customHeight="1">
+      <c r="M150" s="52">
+        <f>BAZA_DUXONE!R43</f>
+        <v/>
+      </c>
+      <c r="N150" s="52">
+        <f>BAZA_DUXONE!S43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" ht="40" customHeight="1">
       <c r="A151" s="52">
         <f>BAZA_DUXONE!A44</f>
         <v/>
@@ -9281,8 +10429,16 @@
         <f>BAZA_DUXONE!I44</f>
         <v/>
       </c>
-    </row>
-    <row r="152" ht="32" customHeight="1">
+      <c r="M151" s="52">
+        <f>BAZA_DUXONE!R44</f>
+        <v/>
+      </c>
+      <c r="N151" s="52">
+        <f>BAZA_DUXONE!S44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" ht="40" customHeight="1">
       <c r="A152" s="52">
         <f>BAZA_DUXONE!A45</f>
         <v/>
@@ -9331,8 +10487,16 @@
         <f>BAZA_DUXONE!I45</f>
         <v/>
       </c>
-    </row>
-    <row r="153" ht="32" customHeight="1">
+      <c r="M152" s="52">
+        <f>BAZA_DUXONE!R45</f>
+        <v/>
+      </c>
+      <c r="N152" s="52">
+        <f>BAZA_DUXONE!S45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" ht="40" customHeight="1">
       <c r="A153" s="52">
         <f>BAZA_DUXONE!A46</f>
         <v/>
@@ -9381,8 +10545,16 @@
         <f>BAZA_DUXONE!I46</f>
         <v/>
       </c>
-    </row>
-    <row r="154" ht="32" customHeight="1">
+      <c r="M153" s="52">
+        <f>BAZA_DUXONE!R46</f>
+        <v/>
+      </c>
+      <c r="N153" s="52">
+        <f>BAZA_DUXONE!S46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" ht="40" customHeight="1">
       <c r="A154" s="52">
         <f>BAZA_DUXONE!A47</f>
         <v/>
@@ -9431,8 +10603,16 @@
         <f>BAZA_DUXONE!I47</f>
         <v/>
       </c>
-    </row>
-    <row r="155" ht="32" customHeight="1">
+      <c r="M154" s="52">
+        <f>BAZA_DUXONE!R47</f>
+        <v/>
+      </c>
+      <c r="N154" s="52">
+        <f>BAZA_DUXONE!S47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" ht="40" customHeight="1">
       <c r="A155" s="52">
         <f>BAZA_DUXONE!A48</f>
         <v/>
@@ -9481,8 +10661,16 @@
         <f>BAZA_DUXONE!I48</f>
         <v/>
       </c>
-    </row>
-    <row r="156" ht="32" customHeight="1">
+      <c r="M155" s="52">
+        <f>BAZA_DUXONE!R48</f>
+        <v/>
+      </c>
+      <c r="N155" s="52">
+        <f>BAZA_DUXONE!S48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" ht="40" customHeight="1">
       <c r="A156" s="52">
         <f>BAZA_DUXONE!A49</f>
         <v/>
@@ -9531,8 +10719,16 @@
         <f>BAZA_DUXONE!I49</f>
         <v/>
       </c>
-    </row>
-    <row r="157" ht="32" customHeight="1">
+      <c r="M156" s="52">
+        <f>BAZA_DUXONE!R49</f>
+        <v/>
+      </c>
+      <c r="N156" s="52">
+        <f>BAZA_DUXONE!S49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" ht="40" customHeight="1">
       <c r="A157" s="52">
         <f>BAZA_DUXONE!A50</f>
         <v/>
@@ -9581,8 +10777,16 @@
         <f>BAZA_DUXONE!I50</f>
         <v/>
       </c>
-    </row>
-    <row r="158" ht="32" customHeight="1">
+      <c r="M157" s="52">
+        <f>BAZA_DUXONE!R50</f>
+        <v/>
+      </c>
+      <c r="N157" s="52">
+        <f>BAZA_DUXONE!S50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" ht="40" customHeight="1">
       <c r="A158" s="52">
         <f>BAZA_DUXONE!A51</f>
         <v/>
@@ -9631,8 +10835,16 @@
         <f>BAZA_DUXONE!I51</f>
         <v/>
       </c>
-    </row>
-    <row r="159" ht="32" customHeight="1">
+      <c r="M158" s="52">
+        <f>BAZA_DUXONE!R51</f>
+        <v/>
+      </c>
+      <c r="N158" s="52">
+        <f>BAZA_DUXONE!S51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" ht="40" customHeight="1">
       <c r="A159" s="52">
         <f>BAZA_DUXONE!A52</f>
         <v/>
@@ -9681,8 +10893,16 @@
         <f>BAZA_DUXONE!I52</f>
         <v/>
       </c>
-    </row>
-    <row r="160" ht="32" customHeight="1">
+      <c r="M159" s="52">
+        <f>BAZA_DUXONE!R52</f>
+        <v/>
+      </c>
+      <c r="N159" s="52">
+        <f>BAZA_DUXONE!S52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" ht="40" customHeight="1">
       <c r="A160" s="52">
         <f>BAZA_DUXONE!A53</f>
         <v/>
@@ -9731,8 +10951,16 @@
         <f>BAZA_DUXONE!I53</f>
         <v/>
       </c>
-    </row>
-    <row r="161" ht="32" customHeight="1">
+      <c r="M160" s="52">
+        <f>BAZA_DUXONE!R53</f>
+        <v/>
+      </c>
+      <c r="N160" s="52">
+        <f>BAZA_DUXONE!S53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" ht="40" customHeight="1">
       <c r="A161" s="52">
         <f>BAZA_DUXONE!A54</f>
         <v/>
@@ -9781,8 +11009,16 @@
         <f>BAZA_DUXONE!I54</f>
         <v/>
       </c>
-    </row>
-    <row r="162" ht="32" customHeight="1">
+      <c r="M161" s="52">
+        <f>BAZA_DUXONE!R54</f>
+        <v/>
+      </c>
+      <c r="N161" s="52">
+        <f>BAZA_DUXONE!S54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" ht="40" customHeight="1">
       <c r="A162" s="52">
         <f>BAZA_DUXONE!A55</f>
         <v/>
@@ -9831,8 +11067,16 @@
         <f>BAZA_DUXONE!I55</f>
         <v/>
       </c>
-    </row>
-    <row r="163" ht="32" customHeight="1">
+      <c r="M162" s="52">
+        <f>BAZA_DUXONE!R55</f>
+        <v/>
+      </c>
+      <c r="N162" s="52">
+        <f>BAZA_DUXONE!S55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" ht="40" customHeight="1">
       <c r="A163" s="52">
         <f>BAZA_DUXONE!A56</f>
         <v/>
@@ -9881,8 +11125,16 @@
         <f>BAZA_DUXONE!I56</f>
         <v/>
       </c>
-    </row>
-    <row r="164" ht="32" customHeight="1">
+      <c r="M163" s="52">
+        <f>BAZA_DUXONE!R56</f>
+        <v/>
+      </c>
+      <c r="N163" s="52">
+        <f>BAZA_DUXONE!S56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="40" customHeight="1">
       <c r="A164" s="52">
         <f>BAZA_DUXONE!A57</f>
         <v/>
@@ -9931,8 +11183,16 @@
         <f>BAZA_DUXONE!I57</f>
         <v/>
       </c>
-    </row>
-    <row r="165" ht="32" customHeight="1">
+      <c r="M164" s="52">
+        <f>BAZA_DUXONE!R57</f>
+        <v/>
+      </c>
+      <c r="N164" s="52">
+        <f>BAZA_DUXONE!S57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" ht="40" customHeight="1">
       <c r="A165" s="52">
         <f>BAZA_DUXONE!A58</f>
         <v/>
@@ -9981,8 +11241,16 @@
         <f>BAZA_DUXONE!I58</f>
         <v/>
       </c>
-    </row>
-    <row r="166" ht="32" customHeight="1">
+      <c r="M165" s="52">
+        <f>BAZA_DUXONE!R58</f>
+        <v/>
+      </c>
+      <c r="N165" s="52">
+        <f>BAZA_DUXONE!S58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="40" customHeight="1">
       <c r="A166" s="52">
         <f>BAZA_DUXONE!A59</f>
         <v/>
@@ -10031,8 +11299,16 @@
         <f>BAZA_DUXONE!I59</f>
         <v/>
       </c>
-    </row>
-    <row r="167" ht="32" customHeight="1">
+      <c r="M166" s="52">
+        <f>BAZA_DUXONE!R59</f>
+        <v/>
+      </c>
+      <c r="N166" s="52">
+        <f>BAZA_DUXONE!S59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" ht="40" customHeight="1">
       <c r="A167" s="52">
         <f>BAZA_DUXONE!A60</f>
         <v/>
@@ -10081,8 +11357,16 @@
         <f>BAZA_DUXONE!I60</f>
         <v/>
       </c>
-    </row>
-    <row r="168" ht="32" customHeight="1">
+      <c r="M167" s="52">
+        <f>BAZA_DUXONE!R60</f>
+        <v/>
+      </c>
+      <c r="N167" s="52">
+        <f>BAZA_DUXONE!S60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" ht="40" customHeight="1">
       <c r="A168" s="52">
         <f>BAZA_DUXONE!A61</f>
         <v/>
@@ -10131,8 +11415,16 @@
         <f>BAZA_DUXONE!I61</f>
         <v/>
       </c>
-    </row>
-    <row r="169" ht="32" customHeight="1">
+      <c r="M168" s="52">
+        <f>BAZA_DUXONE!R61</f>
+        <v/>
+      </c>
+      <c r="N168" s="52">
+        <f>BAZA_DUXONE!S61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" ht="40" customHeight="1">
       <c r="A169" s="52">
         <f>BAZA_DUXONE!A62</f>
         <v/>
@@ -10181,8 +11473,16 @@
         <f>BAZA_DUXONE!I62</f>
         <v/>
       </c>
-    </row>
-    <row r="170" ht="32" customHeight="1">
+      <c r="M169" s="52">
+        <f>BAZA_DUXONE!R62</f>
+        <v/>
+      </c>
+      <c r="N169" s="52">
+        <f>BAZA_DUXONE!S62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" ht="40" customHeight="1">
       <c r="A170" s="52">
         <f>BAZA_DUXONE!A63</f>
         <v/>
@@ -10231,8 +11531,16 @@
         <f>BAZA_DUXONE!I63</f>
         <v/>
       </c>
-    </row>
-    <row r="171" ht="32" customHeight="1">
+      <c r="M170" s="52">
+        <f>BAZA_DUXONE!R63</f>
+        <v/>
+      </c>
+      <c r="N170" s="52">
+        <f>BAZA_DUXONE!S63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" ht="40" customHeight="1">
       <c r="A171" s="52">
         <f>BAZA_DUXONE!A64</f>
         <v/>
@@ -10281,8 +11589,16 @@
         <f>BAZA_DUXONE!I64</f>
         <v/>
       </c>
-    </row>
-    <row r="172" ht="32" customHeight="1">
+      <c r="M171" s="52">
+        <f>BAZA_DUXONE!R64</f>
+        <v/>
+      </c>
+      <c r="N171" s="52">
+        <f>BAZA_DUXONE!S64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" ht="40" customHeight="1">
       <c r="A172" s="52">
         <f>BAZA_DUXONE!A65</f>
         <v/>
@@ -10331,8 +11647,16 @@
         <f>BAZA_DUXONE!I65</f>
         <v/>
       </c>
-    </row>
-    <row r="173" ht="32" customHeight="1">
+      <c r="M172" s="52">
+        <f>BAZA_DUXONE!R65</f>
+        <v/>
+      </c>
+      <c r="N172" s="52">
+        <f>BAZA_DUXONE!S65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" ht="40" customHeight="1">
       <c r="A173" s="52">
         <f>BAZA_DUXONE!A66</f>
         <v/>
@@ -10381,8 +11705,16 @@
         <f>BAZA_DUXONE!I66</f>
         <v/>
       </c>
-    </row>
-    <row r="174" ht="32" customHeight="1">
+      <c r="M173" s="52">
+        <f>BAZA_DUXONE!R66</f>
+        <v/>
+      </c>
+      <c r="N173" s="52">
+        <f>BAZA_DUXONE!S66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" ht="40" customHeight="1">
       <c r="A174" s="52">
         <f>BAZA_DUXONE!A67</f>
         <v/>
@@ -10431,8 +11763,16 @@
         <f>BAZA_DUXONE!I67</f>
         <v/>
       </c>
-    </row>
-    <row r="175" ht="32" customHeight="1">
+      <c r="M174" s="52">
+        <f>BAZA_DUXONE!R67</f>
+        <v/>
+      </c>
+      <c r="N174" s="52">
+        <f>BAZA_DUXONE!S67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" ht="40" customHeight="1">
       <c r="A175" s="52">
         <f>BAZA_DUXONE!A68</f>
         <v/>
@@ -10481,8 +11821,16 @@
         <f>BAZA_DUXONE!I68</f>
         <v/>
       </c>
-    </row>
-    <row r="176" ht="32" customHeight="1">
+      <c r="M175" s="52">
+        <f>BAZA_DUXONE!R68</f>
+        <v/>
+      </c>
+      <c r="N175" s="52">
+        <f>BAZA_DUXONE!S68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" ht="40" customHeight="1">
       <c r="A176" s="52">
         <f>BAZA_DUXONE!A69</f>
         <v/>
@@ -10531,8 +11879,16 @@
         <f>BAZA_DUXONE!I69</f>
         <v/>
       </c>
-    </row>
-    <row r="177" ht="32" customHeight="1">
+      <c r="M176" s="52">
+        <f>BAZA_DUXONE!R69</f>
+        <v/>
+      </c>
+      <c r="N176" s="52">
+        <f>BAZA_DUXONE!S69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" ht="40" customHeight="1">
       <c r="A177" s="52">
         <f>BAZA_DUXONE!A70</f>
         <v/>
@@ -10581,8 +11937,16 @@
         <f>BAZA_DUXONE!I70</f>
         <v/>
       </c>
-    </row>
-    <row r="178" ht="32" customHeight="1">
+      <c r="M177" s="52">
+        <f>BAZA_DUXONE!R70</f>
+        <v/>
+      </c>
+      <c r="N177" s="52">
+        <f>BAZA_DUXONE!S70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" ht="40" customHeight="1">
       <c r="A178" s="52">
         <f>BAZA_DUXONE!A71</f>
         <v/>
@@ -10631,8 +11995,16 @@
         <f>BAZA_DUXONE!I71</f>
         <v/>
       </c>
-    </row>
-    <row r="179" ht="32" customHeight="1">
+      <c r="M178" s="52">
+        <f>BAZA_DUXONE!R71</f>
+        <v/>
+      </c>
+      <c r="N178" s="52">
+        <f>BAZA_DUXONE!S71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
       <c r="A179" s="52">
         <f>BAZA_DUXONE!A72</f>
         <v/>
@@ -10681,8 +12053,16 @@
         <f>BAZA_DUXONE!I72</f>
         <v/>
       </c>
-    </row>
-    <row r="180" ht="32" customHeight="1">
+      <c r="M179" s="52">
+        <f>BAZA_DUXONE!R72</f>
+        <v/>
+      </c>
+      <c r="N179" s="52">
+        <f>BAZA_DUXONE!S72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" ht="40" customHeight="1">
       <c r="A180" s="52">
         <f>BAZA_DUXONE!A73</f>
         <v/>
@@ -10731,8 +12111,16 @@
         <f>BAZA_DUXONE!I73</f>
         <v/>
       </c>
-    </row>
-    <row r="181" ht="32" customHeight="1">
+      <c r="M180" s="52">
+        <f>BAZA_DUXONE!R73</f>
+        <v/>
+      </c>
+      <c r="N180" s="52">
+        <f>BAZA_DUXONE!S73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
       <c r="A181" s="52">
         <f>BAZA_DUXONE!A74</f>
         <v/>
@@ -10781,8 +12169,16 @@
         <f>BAZA_DUXONE!I74</f>
         <v/>
       </c>
-    </row>
-    <row r="182" ht="32" customHeight="1">
+      <c r="M181" s="52">
+        <f>BAZA_DUXONE!R74</f>
+        <v/>
+      </c>
+      <c r="N181" s="52">
+        <f>BAZA_DUXONE!S74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
       <c r="A182" s="52">
         <f>BAZA_DUXONE!A75</f>
         <v/>
@@ -10831,8 +12227,16 @@
         <f>BAZA_DUXONE!I75</f>
         <v/>
       </c>
-    </row>
-    <row r="183" ht="32" customHeight="1">
+      <c r="M182" s="52">
+        <f>BAZA_DUXONE!R75</f>
+        <v/>
+      </c>
+      <c r="N182" s="52">
+        <f>BAZA_DUXONE!S75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
       <c r="A183" s="52">
         <f>BAZA_DUXONE!A76</f>
         <v/>
@@ -10881,8 +12285,16 @@
         <f>BAZA_DUXONE!I76</f>
         <v/>
       </c>
-    </row>
-    <row r="184" ht="32" customHeight="1">
+      <c r="M183" s="52">
+        <f>BAZA_DUXONE!R76</f>
+        <v/>
+      </c>
+      <c r="N183" s="52">
+        <f>BAZA_DUXONE!S76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
       <c r="A184" s="52">
         <f>BAZA_DUXONE!A77</f>
         <v/>
@@ -10931,8 +12343,16 @@
         <f>BAZA_DUXONE!I77</f>
         <v/>
       </c>
-    </row>
-    <row r="185" ht="32" customHeight="1">
+      <c r="M184" s="52">
+        <f>BAZA_DUXONE!R77</f>
+        <v/>
+      </c>
+      <c r="N184" s="52">
+        <f>BAZA_DUXONE!S77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
       <c r="A185" s="52">
         <f>BAZA_DUXONE!A78</f>
         <v/>
@@ -10981,8 +12401,16 @@
         <f>BAZA_DUXONE!I78</f>
         <v/>
       </c>
-    </row>
-    <row r="186" ht="32" customHeight="1">
+      <c r="M185" s="52">
+        <f>BAZA_DUXONE!R78</f>
+        <v/>
+      </c>
+      <c r="N185" s="52">
+        <f>BAZA_DUXONE!S78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
       <c r="A186" s="52">
         <f>BAZA_DUXONE!A79</f>
         <v/>
@@ -11031,8 +12459,16 @@
         <f>BAZA_DUXONE!I79</f>
         <v/>
       </c>
-    </row>
-    <row r="187" ht="32" customHeight="1">
+      <c r="M186" s="52">
+        <f>BAZA_DUXONE!R79</f>
+        <v/>
+      </c>
+      <c r="N186" s="52">
+        <f>BAZA_DUXONE!S79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
       <c r="A187" s="52">
         <f>BAZA_DUXONE!A80</f>
         <v/>
@@ -11081,8 +12517,16 @@
         <f>BAZA_DUXONE!I80</f>
         <v/>
       </c>
-    </row>
-    <row r="188" ht="32" customHeight="1">
+      <c r="M187" s="52">
+        <f>BAZA_DUXONE!R80</f>
+        <v/>
+      </c>
+      <c r="N187" s="52">
+        <f>BAZA_DUXONE!S80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
       <c r="A188" s="52">
         <f>BAZA_DUXONE!A81</f>
         <v/>
@@ -11131,8 +12575,16 @@
         <f>BAZA_DUXONE!I81</f>
         <v/>
       </c>
-    </row>
-    <row r="189" ht="32" customHeight="1">
+      <c r="M188" s="52">
+        <f>BAZA_DUXONE!R81</f>
+        <v/>
+      </c>
+      <c r="N188" s="52">
+        <f>BAZA_DUXONE!S81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
       <c r="A189" s="52">
         <f>BAZA_DUXONE!A82</f>
         <v/>
@@ -11181,8 +12633,16 @@
         <f>BAZA_DUXONE!I82</f>
         <v/>
       </c>
-    </row>
-    <row r="190" ht="32" customHeight="1">
+      <c r="M189" s="52">
+        <f>BAZA_DUXONE!R82</f>
+        <v/>
+      </c>
+      <c r="N189" s="52">
+        <f>BAZA_DUXONE!S82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
       <c r="A190" s="52">
         <f>BAZA_DUXONE!A83</f>
         <v/>
@@ -11231,8 +12691,16 @@
         <f>BAZA_DUXONE!I83</f>
         <v/>
       </c>
-    </row>
-    <row r="191" ht="32" customHeight="1">
+      <c r="M190" s="52">
+        <f>BAZA_DUXONE!R83</f>
+        <v/>
+      </c>
+      <c r="N190" s="52">
+        <f>BAZA_DUXONE!S83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
       <c r="A191" s="52">
         <f>BAZA_DUXONE!A84</f>
         <v/>
@@ -11281,8 +12749,16 @@
         <f>BAZA_DUXONE!I84</f>
         <v/>
       </c>
-    </row>
-    <row r="192" ht="32" customHeight="1">
+      <c r="M191" s="52">
+        <f>BAZA_DUXONE!R84</f>
+        <v/>
+      </c>
+      <c r="N191" s="52">
+        <f>BAZA_DUXONE!S84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
       <c r="A192" s="52">
         <f>BAZA_DUXONE!A85</f>
         <v/>
@@ -11331,8 +12807,16 @@
         <f>BAZA_DUXONE!I85</f>
         <v/>
       </c>
-    </row>
-    <row r="193" ht="32" customHeight="1">
+      <c r="M192" s="52">
+        <f>BAZA_DUXONE!R85</f>
+        <v/>
+      </c>
+      <c r="N192" s="52">
+        <f>BAZA_DUXONE!S85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
       <c r="A193" s="52">
         <f>BAZA_DUXONE!A86</f>
         <v/>
@@ -11381,8 +12865,16 @@
         <f>BAZA_DUXONE!I86</f>
         <v/>
       </c>
-    </row>
-    <row r="194" ht="32" customHeight="1">
+      <c r="M193" s="52">
+        <f>BAZA_DUXONE!R86</f>
+        <v/>
+      </c>
+      <c r="N193" s="52">
+        <f>BAZA_DUXONE!S86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
       <c r="A194" s="52">
         <f>BAZA_DUXONE!A87</f>
         <v/>
@@ -11431,14 +12923,22 @@
         <f>BAZA_DUXONE!I87</f>
         <v/>
       </c>
+      <c r="M194" s="52">
+        <f>BAZA_DUXONE!R87</f>
+        <v/>
+      </c>
+      <c r="N194" s="52">
+        <f>BAZA_DUXONE!S87</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
-  <autoFilter ref="A8:L194"/>
+  <autoFilter ref="A8:N194"/>
   <mergeCells count="3">
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29217,7 +30717,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Źródło: nexa-autocolor-2k-tint-chart-guide.pdf oraz Duxone - Tint Descriptions - PL.pdf (kopie w data/backup).</t>
+          <t>Źródło: nexa-autocolor-2k-tint-chart-guide.pdf (opisy działania Autocolor przetłumaczone na PL) oraz Duxone - Tint Descriptions - PL.pdf (kopie w data/backup).</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -29292,7 +30792,7 @@
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
         <is>
-          <t>Opis / procedura</t>
+          <t>Opis działania (PL)</t>
         </is>
       </c>
       <c r="B8" s="38">
@@ -29351,7 +30851,7 @@
       </c>
       <c r="C17" s="47" t="inlineStr">
         <is>
-          <t>FACE — kąt silnie zależny od metalików/pereł. FLOP — kąt zwykle ciemniejszy, zależny od tonerów konwencjonalnych. TONE — odcień względem sąsiedniej rodziny barw.</t>
+          <t>ŚWIATŁO (FACE) — kąt mocno zależny od metalików/pereł. FLOP (CIEŃ) — kąt zwykle ciemniejszy, zależny od tonerów konwencjonalnych. TONE (ODCIEŃ) — odcień względem sąsiedniej rodziny barw.</t>
         </is>
       </c>
     </row>
@@ -29436,7 +30936,7 @@
       </c>
       <c r="C22" s="47" t="inlineStr">
         <is>
-          <t>W PDF: Blue Frost — dodaje żółć na face i jasny błękit na flop w metalikach. W katalogu ODS ten sam kod ma inną nazwę — weryfikuj przed użyciem (status KOLIZJA jeśli wykryta).</t>
+          <t>W PDF: Blue Frost — dodaje żółć na świetle (face) i jasny błękit na flopie w metalikach. W katalogu ODS ten sam kod ma inną nazwę — weryfikuj przed użyciem (status KOLIZJA jeśli wykryta).</t>
         </is>
       </c>
     </row>
@@ -29681,6 +31181,8 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -29711,7 +31213,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kopia robocza bazy. Oryginalne pliki ODS/PDF nie są zmieniane. Klucz = SYSTEM|NR_PIGMENTU.</t>
+          <t>Kopia robocza bazy. Oryginalne pliki ODS/PDF nie są zmieniane. Klucz = SYSTEM|NR_PIGMENTU. AUTOCOLOR: OPIS_DOBARWIANIA i OPIS_DZIALANIA_PL po polsku (tint chart); nazwy katalogowe EN. DUXONE: opisy z PDF PL.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -29819,8 +31321,18 @@
           <t>W_SZABLONIE_ODS</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+      <c r="R8" s="26" t="inlineStr">
+        <is>
+          <t>OPIS_EN</t>
+        </is>
+      </c>
+      <c r="S8" s="26" t="inlineStr">
+        <is>
+          <t>OPIS_DZIALANIA_PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P192-475</t>
@@ -29859,8 +31371,16 @@
           <t>2K REGULATOR BAZY</t>
         </is>
       </c>
-      <c r="I9" s="48" t="inlineStr"/>
-      <c r="J9" s="48" t="inlineStr"/>
+      <c r="I9" s="48" t="inlineStr">
+        <is>
+          <t>REGULATOR BAZY</t>
+        </is>
+      </c>
+      <c r="J9" s="48" t="inlineStr">
+        <is>
+          <t>Regulator bazy — rozcieńcza i ułatwia aplikację mieszanki, bez zmiany odcienia. Nie jest tonerem kolorystycznym.</t>
+        </is>
+      </c>
       <c r="K9" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -29892,8 +31412,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+      <c r="R9" s="48" t="inlineStr">
+        <is>
+          <t>Base blender / reducer. Does not shift hue; adjusts viscosity and application of the mixing base.</t>
+        </is>
+      </c>
+      <c r="S9" s="48" t="inlineStr">
+        <is>
+          <t>Regulator bazy — rozcieńcza i ułatwia aplikację mieszanki, bez zmiany odcienia. Nie jest tonerem kolorystycznym.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P192-528</t>
@@ -29932,8 +31462,16 @@
           <t>2K REGULATOR UŁOŻENIA ZIARNA</t>
         </is>
       </c>
-      <c r="I10" s="48" t="inlineStr"/>
-      <c r="J10" s="48" t="inlineStr"/>
+      <c r="I10" s="48" t="inlineStr">
+        <is>
+          <t>REGULATOR UŁOŻENIA ZIARNA</t>
+        </is>
+      </c>
+      <c r="J10" s="48" t="inlineStr">
+        <is>
+          <t>Regulator ułożenia ziarna — poprawia orientację płatków metalicznych, uspokaja układ ziarna na powierzchni.</t>
+        </is>
+      </c>
       <c r="K10" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -29965,8 +31503,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+      <c r="R10" s="48" t="inlineStr">
+        <is>
+          <t>Grain / flake orientation controller. Settles metallic flake layout.</t>
+        </is>
+      </c>
+      <c r="S10" s="48" t="inlineStr">
+        <is>
+          <t>Regulator ułożenia ziarna — poprawia orientację płatków metalicznych, uspokaja układ ziarna na powierzchni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P192-5600</t>
@@ -30005,8 +31553,16 @@
           <t>2K REGULATOR FLOPU</t>
         </is>
       </c>
-      <c r="I11" s="48" t="inlineStr"/>
-      <c r="J11" s="48" t="inlineStr"/>
+      <c r="I11" s="48" t="inlineStr">
+        <is>
+          <t>REGULATOR FLOPU</t>
+        </is>
+      </c>
+      <c r="J11" s="48" t="inlineStr">
+        <is>
+          <t>Regulator flopu — koryguje różnicę światło/cień, uspokaja lub pogłębia flop (cień) w metalikach i perłach.</t>
+        </is>
+      </c>
       <c r="K11" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -30038,8 +31594,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+      <c r="R11" s="48" t="inlineStr">
+        <is>
+          <t>Flop controller. Adjusts the light-to-dark travel (face vs flop).</t>
+        </is>
+      </c>
+      <c r="S11" s="48" t="inlineStr">
+        <is>
+          <t>Regulator flopu — koryguje różnicę światło/cień, uspokaja lub pogłębia flop (cień) w metalikach i perłach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-902RT</t>
@@ -30070,7 +31636,7 @@
       </c>
       <c r="G12" s="48" t="inlineStr">
         <is>
-          <t>RT Pale White Strong white.</t>
+          <t>RT Pale White</t>
         </is>
       </c>
       <c r="H12" s="48" t="inlineStr">
@@ -30080,12 +31646,12 @@
       </c>
       <c r="I12" s="48" t="inlineStr">
         <is>
-          <t>RT Pale White Strong white.</t>
+          <t>RT Pale White</t>
         </is>
       </c>
       <c r="J12" s="48" t="inlineStr">
         <is>
-          <t>If more than 10% use P425-900.</t>
+          <t>Mocna biel — silnie rozjaśnia. Toner RT (obniżona moc). Jeżeli udział przekracza 10%, użyj P425-900.</t>
         </is>
       </c>
       <c r="K12" s="48" t="inlineStr">
@@ -30119,8 +31685,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+      <c r="R12" s="48" t="inlineStr">
+        <is>
+          <t>Strong white. If more than 10% use P425-900.</t>
+        </is>
+      </c>
+      <c r="S12" s="48" t="inlineStr">
+        <is>
+          <t>Mocna biel — silnie rozjaśnia. Toner RT (obniżona moc). Jeżeli udział przekracza 10%, użyj P425-900.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-903RT</t>
@@ -30151,7 +31727,7 @@
       </c>
       <c r="G13" s="48" t="inlineStr">
         <is>
-          <t>Rt Medium Pale Yellow</t>
+          <t>RT Medium Pale Yellow</t>
         </is>
       </c>
       <c r="H13" s="48" t="inlineStr">
@@ -30161,12 +31737,12 @@
       </c>
       <c r="I13" s="48" t="inlineStr">
         <is>
-          <t>Rt Medium Pale Yellow</t>
+          <t>RT Medium Pale Yellow</t>
         </is>
       </c>
       <c r="J13" s="48" t="inlineStr">
         <is>
-          <t>Pale yellow with a greenish yellow flop.</t>
+          <t>Bladożółty z zielonkawożółtym flopem (cień). Toner RT — rozjaśnia w stronę bladego żółtego.</t>
         </is>
       </c>
       <c r="K13" s="48" t="inlineStr">
@@ -30200,8 +31776,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+      <c r="R13" s="48" t="inlineStr">
+        <is>
+          <t>Pale yellow with a greenish yellow flop.</t>
+        </is>
+      </c>
+      <c r="S13" s="48" t="inlineStr">
+        <is>
+          <t>Bladożółty z zielonkawożółtym flopem (cień). Toner RT — rozjaśnia w stronę bladego żółtego.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-904RT</t>
@@ -30247,7 +31833,7 @@
       </c>
       <c r="J14" s="48" t="inlineStr">
         <is>
-          <t>Yellow-shade black, darker flop than</t>
+          <t>Czerń o żółtym odcieniu, ciemniejszy flop niż P420-933. Toner RT, transparentniejszy niż pełna czerń. Jeżeli udział przekracza 10%, użyj P425-948.</t>
         </is>
       </c>
       <c r="K14" s="48" t="inlineStr">
@@ -30281,8 +31867,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+      <c r="R14" s="48" t="inlineStr">
+        <is>
+          <t>Yellow-shade black, darker flop than P420-933. If more than 10% use P425-948.</t>
+        </is>
+      </c>
+      <c r="S14" s="48" t="inlineStr">
+        <is>
+          <t>Czerń o żółtym odcieniu, ciemniejszy flop niż P420-933. Toner RT, transparentniejszy niż pełna czerń. Jeżeli udział przekracza 10%, użyj P425-948.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-905</t>
@@ -30328,7 +31924,7 @@
       </c>
       <c r="J15" s="48" t="inlineStr">
         <is>
-          <t>Opaque yellow oxide.</t>
+          <t>Kryjący tlenek żółty. Dodaje żółć tlenkową (ciepłą, ziemistą), silne krycie, przytłumia czystość tonu.</t>
         </is>
       </c>
       <c r="K15" s="48" t="inlineStr">
@@ -30362,8 +31958,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+      <c r="R15" s="48" t="inlineStr">
+        <is>
+          <t>Opaque yellow oxide.</t>
+        </is>
+      </c>
+      <c r="S15" s="48" t="inlineStr">
+        <is>
+          <t>Kryjący tlenek żółty. Dodaje żółć tlenkową (ciepłą, ziemistą), silne krycie, przytłumia czystość tonu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-907</t>
@@ -30407,7 +32013,11 @@
           <t>Red Oxide</t>
         </is>
       </c>
-      <c r="J16" s="48" t="inlineStr"/>
+      <c r="J16" s="48" t="inlineStr">
+        <is>
+          <t>Tlenek czerwony (rdzawy). Kryjący toner tlenkowy; pełna moc odpowiednika RT Russet (P420-908RT).</t>
+        </is>
+      </c>
       <c r="K16" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -30439,8 +32049,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+      <c r="R16" s="48" t="inlineStr">
+        <is>
+          <t>Red oxide. Full-strength counterpart of RT Russet P420-908RT.</t>
+        </is>
+      </c>
+      <c r="S16" s="48" t="inlineStr">
+        <is>
+          <t>Tlenek czerwony (rdzawy). Kryjący toner tlenkowy; pełna moc odpowiednika RT Russet (P420-908RT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-908RT</t>
@@ -30471,7 +32091,7 @@
       </c>
       <c r="G17" s="48" t="inlineStr">
         <is>
-          <t>RT Russet Blue shade red oxide.</t>
+          <t>RT Russet</t>
         </is>
       </c>
       <c r="H17" s="48" t="inlineStr">
@@ -30481,12 +32101,12 @@
       </c>
       <c r="I17" s="48" t="inlineStr">
         <is>
-          <t>RT Russet Blue shade red oxide.</t>
+          <t>RT Russet</t>
         </is>
       </c>
       <c r="J17" s="48" t="inlineStr">
         <is>
-          <t>If more than 10% use P420-907.</t>
+          <t>Tlenek czerwony o niebieskim odcieniu. Toner RT. Jeżeli udział przekracza 10%, użyj P420-907.</t>
         </is>
       </c>
       <c r="K17" s="48" t="inlineStr">
@@ -30520,8 +32140,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+      <c r="R17" s="48" t="inlineStr">
+        <is>
+          <t>Blue shade red oxide. If more than 10% use P420-907.</t>
+        </is>
+      </c>
+      <c r="S17" s="48" t="inlineStr">
+        <is>
+          <t>Tlenek czerwony o niebieskim odcieniu. Toner RT. Jeżeli udział przekracza 10%, użyj P420-907.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
       <c r="A18" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-910RT</t>
@@ -30567,7 +32197,7 @@
       </c>
       <c r="J18" s="48" t="inlineStr">
         <is>
-          <t>High strength transparent blue. If more than 10% use P425-957.</t>
+          <t>Wysokowydajny transparentny niebieski. Toner RT. Jeżeli udział przekracza 10%, użyj P425-957.</t>
         </is>
       </c>
       <c r="K18" s="48" t="inlineStr">
@@ -30601,8 +32231,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+      <c r="R18" s="48" t="inlineStr">
+        <is>
+          <t>High strength transparent blue. If more than 10% use P425-957.</t>
+        </is>
+      </c>
+      <c r="S18" s="48" t="inlineStr">
+        <is>
+          <t>Wysokowydajny transparentny niebieski. Toner RT. Jeżeli udział przekracza 10%, użyj P425-957.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-920</t>
@@ -30648,7 +32288,7 @@
       </c>
       <c r="J19" s="48" t="inlineStr">
         <is>
-          <t>Clean violet with a dirty yellow flop, redder than P420-930.</t>
+          <t>Czysty fiolet z brudnym żółtym flopem; bardziej czerwony niż P420-930. Czyste światło (face), cieplejszy/brudniejszy cień.</t>
         </is>
       </c>
       <c r="K19" s="48" t="inlineStr">
@@ -30682,8 +32322,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+      <c r="R19" s="48" t="inlineStr">
+        <is>
+          <t>Clean violet with a dirty yellow flop, redder than P420-930.</t>
+        </is>
+      </c>
+      <c r="S19" s="48" t="inlineStr">
+        <is>
+          <t>Czysty fiolet z brudnym żółtym flopem; bardziej czerwony niż P420-930. Czyste światło (face), cieplejszy/brudniejszy cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
       <c r="A20" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-926</t>
@@ -30714,7 +32364,7 @@
       </c>
       <c r="G20" s="48" t="inlineStr">
         <is>
-          <t>Super Red Clean red.</t>
+          <t>Super Red</t>
         </is>
       </c>
       <c r="H20" s="48" t="inlineStr">
@@ -30724,10 +32374,14 @@
       </c>
       <c r="I20" s="48" t="inlineStr">
         <is>
-          <t>Super Red Clean red.</t>
-        </is>
-      </c>
-      <c r="J20" s="48" t="inlineStr"/>
+          <t>Super Red</t>
+        </is>
+      </c>
+      <c r="J20" s="48" t="inlineStr">
+        <is>
+          <t>Czysta czerwień. Dodaje czysty czerwony ton (bez tlenkowego przytłumienia).</t>
+        </is>
+      </c>
       <c r="K20" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -30759,8 +32413,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="R20" s="48" t="inlineStr">
+        <is>
+          <t>Clean red.</t>
+        </is>
+      </c>
+      <c r="S20" s="48" t="inlineStr">
+        <is>
+          <t>Czysta czerwień. Dodaje czysty czerwony ton (bez tlenkowego przytłumienia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-930</t>
@@ -30791,7 +32455,7 @@
       </c>
       <c r="G21" s="49" t="inlineStr">
         <is>
-          <t>Lake Blue Red shade blue.</t>
+          <t>Lake Blue</t>
         </is>
       </c>
       <c r="H21" s="49" t="inlineStr">
@@ -30801,10 +32465,14 @@
       </c>
       <c r="I21" s="49" t="inlineStr">
         <is>
-          <t>Lake Blue Red shade blue.</t>
-        </is>
-      </c>
-      <c r="J21" s="49" t="inlineStr"/>
+          <t>Lake Blue</t>
+        </is>
+      </c>
+      <c r="J21" s="49" t="inlineStr">
+        <is>
+          <t>Niebieski o czerwonym odcieniu. Przesuwa ton w stronę czerwono-niebieskiego (cieplejszy błękit).</t>
+        </is>
+      </c>
       <c r="K21" s="49" t="inlineStr">
         <is>
           <t>g</t>
@@ -30840,8 +32508,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+      <c r="R21" s="49" t="inlineStr">
+        <is>
+          <t>Red shade blue.</t>
+        </is>
+      </c>
+      <c r="S21" s="49" t="inlineStr">
+        <is>
+          <t>Niebieski o czerwonym odcieniu. Przesuwa ton w stronę czerwono-niebieskiego (cieplejszy błękit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
       <c r="A22" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-933</t>
@@ -30887,7 +32565,7 @@
       </c>
       <c r="J22" s="48" t="inlineStr">
         <is>
-          <t>Blue-shade black, lighter and bluer flop than P425-948.</t>
+          <t>Czerń o niebieskim odcieniu; jaśniejszy i bardziej niebieski flop niż P425-948. Ściemia z niebieskim cieniem.</t>
         </is>
       </c>
       <c r="K22" s="48" t="inlineStr">
@@ -30921,8 +32599,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+      <c r="R22" s="48" t="inlineStr">
+        <is>
+          <t>Blue-shade black, lighter and bluer flop than P425-948.</t>
+        </is>
+      </c>
+      <c r="S22" s="48" t="inlineStr">
+        <is>
+          <t>Czerń o niebieskim odcieniu; jaśniejszy i bardziej niebieski flop niż P425-948. Ściemia z niebieskim cieniem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-938</t>
@@ -30953,7 +32641,7 @@
       </c>
       <c r="G23" s="48" t="inlineStr">
         <is>
-          <t>Tone Controller appearance and lightens the</t>
+          <t>Tone Controller</t>
         </is>
       </c>
       <c r="H23" s="48" t="inlineStr">
@@ -30963,12 +32651,12 @@
       </c>
       <c r="I23" s="48" t="inlineStr">
         <is>
-          <t>Tone Controller appearance and lightens the</t>
+          <t>Tone Controller</t>
         </is>
       </c>
       <c r="J23" s="48" t="inlineStr">
         <is>
-          <t>Gives a more coarse flake flop.</t>
+          <t>Kontroler tonu — daje wrażenie grubszego ziarna i rozjaśnia flop (cień). Uspokaja zbyt ciemny/płaski cień metaliku.</t>
         </is>
       </c>
       <c r="K23" s="48" t="inlineStr">
@@ -31002,8 +32690,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+      <c r="R23" s="48" t="inlineStr">
+        <is>
+          <t>Gives a more coarse flake appearance and lightens the flop.</t>
+        </is>
+      </c>
+      <c r="S23" s="48" t="inlineStr">
+        <is>
+          <t>Kontroler tonu — daje wrażenie grubszego ziarna i rozjaśnia flop (cień). Uspokaja zbyt ciemny/płaski cień metaliku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
       <c r="A24" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-942</t>
@@ -31049,7 +32747,7 @@
       </c>
       <c r="J24" s="48" t="inlineStr">
         <is>
-          <t>Golden brown transparent red oxide with a yellow shade flop. Cleaner face, lighter and yellower flop than P420-978.</t>
+          <t>Złotobrązowy transparentny tlenek czerwony z żółtym flopem. Czystsze światło (face), jaśniejszy i bardziej żółty flop niż P420-978.</t>
         </is>
       </c>
       <c r="K24" s="48" t="inlineStr">
@@ -31083,8 +32781,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="R24" s="48" t="inlineStr">
+        <is>
+          <t>Golden brown transparent red oxide with a yellow shade flop. Cleaner face, lighter and yellower flop than P420-978.</t>
+        </is>
+      </c>
+      <c r="S24" s="48" t="inlineStr">
+        <is>
+          <t>Złotobrązowy transparentny tlenek czerwony z żółtym flopem. Czystsze światło (face), jaśniejszy i bardziej żółty flop niż P420-978.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-952</t>
@@ -31115,7 +32823,7 @@
       </c>
       <c r="G25" s="48" t="inlineStr">
         <is>
-          <t>Fast Blue Mid-shade blue.</t>
+          <t>Fast Blue</t>
         </is>
       </c>
       <c r="H25" s="48" t="inlineStr">
@@ -31125,10 +32833,14 @@
       </c>
       <c r="I25" s="48" t="inlineStr">
         <is>
-          <t>Fast Blue Mid-shade blue.</t>
-        </is>
-      </c>
-      <c r="J25" s="48" t="inlineStr"/>
+          <t>Fast Blue</t>
+        </is>
+      </c>
+      <c r="J25" s="48" t="inlineStr">
+        <is>
+          <t>Niebieski o środkowym odcieniu. Neutralny błękit do korekty tonu bez silnego przesunięcia w zieleń lub czerwień.</t>
+        </is>
+      </c>
       <c r="K25" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -31160,8 +32872,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
+      <c r="R25" s="48" t="inlineStr">
+        <is>
+          <t>Mid-shade blue.</t>
+        </is>
+      </c>
+      <c r="S25" s="48" t="inlineStr">
+        <is>
+          <t>Niebieski o środkowym odcieniu. Neutralny błękit do korekty tonu bez silnego przesunięcia w zieleń lub czerwień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-960RT</t>
@@ -31192,7 +32914,7 @@
       </c>
       <c r="G26" s="49" t="inlineStr">
         <is>
-          <t>RT Burgundy pigments in a formula.</t>
+          <t>RT Burgundy</t>
         </is>
       </c>
       <c r="H26" s="49" t="inlineStr">
@@ -31202,12 +32924,12 @@
       </c>
       <c r="I26" s="49" t="inlineStr">
         <is>
-          <t>RT Burgundy pigments in a formula.</t>
+          <t>RT Burgundy</t>
         </is>
       </c>
       <c r="J26" s="49" t="inlineStr">
         <is>
-          <t>Blue shade violet, dirtier face and darker flop than P425-921. If more than 10% use P429-976. by the conventional pigments in a metallic or pearlescent colour. (green-shade blue, mid-shade blue, red-shade blue).</t>
+          <t>Fiolet o niebieskim odcieniu; brudniejsze światło (face) i ciemniejszy flop niż P425-921. Toner RT. Jeżeli udział przekracza 10%, użyj P429-976.</t>
         </is>
       </c>
       <c r="K26" s="49" t="inlineStr">
@@ -31245,8 +32967,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+      <c r="R26" s="49" t="inlineStr">
+        <is>
+          <t>Blue shade violet, dirtier face and darker flop than P425-921. If more than 10% use P429-976.</t>
+        </is>
+      </c>
+      <c r="S26" s="49" t="inlineStr">
+        <is>
+          <t>Fiolet o niebieskim odcieniu; brudniejsze światło (face) i ciemniejszy flop niż P425-921. Toner RT. Jeżeli udział przekracza 10%, użyj P429-976.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-975</t>
@@ -31292,7 +33024,7 @@
       </c>
       <c r="J27" s="48" t="inlineStr">
         <is>
-          <t>Golden green face, yellow shade flop.</t>
+          <t>Złocista zieleń na świetle (face), żółty odcień na flopie. Ciepła zieleń z żółtym cieniem.</t>
         </is>
       </c>
       <c r="K27" s="48" t="inlineStr">
@@ -31326,8 +33058,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+      <c r="R27" s="48" t="inlineStr">
+        <is>
+          <t>Golden green face, yellow shade flop.</t>
+        </is>
+      </c>
+      <c r="S27" s="48" t="inlineStr">
+        <is>
+          <t>Złocista zieleń na świetle (face), żółty odcień na flopie. Ciepła zieleń z żółtym cieniem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-978</t>
@@ -31373,7 +33115,7 @@
       </c>
       <c r="J28" s="48" t="inlineStr">
         <is>
-          <t>Dark brown with a yellower flop than</t>
+          <t>Ciemny brąz z bardziej żółtym flopem niż P429-923. Ściemia i ociepla, szczególnie w cieniu.</t>
         </is>
       </c>
       <c r="K28" s="48" t="inlineStr">
@@ -31407,8 +33149,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+      <c r="R28" s="48" t="inlineStr">
+        <is>
+          <t>Dark brown with a yellower flop than P429-923.</t>
+        </is>
+      </c>
+      <c r="S28" s="48" t="inlineStr">
+        <is>
+          <t>Ciemny brąz z bardziej żółtym flopem niż P429-923. Ściemia i ociepla, szczególnie w cieniu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-983</t>
@@ -31454,7 +33206,7 @@
       </c>
       <c r="J29" s="48" t="inlineStr">
         <is>
-          <t>Orange shade yellow, can be used when a green tone flop is needed. Cleaner than</t>
+          <t>Żółty o pomarańczowym odcieniu; stosować, gdy potrzebny zielony flop. Czystszy niż P420-982.</t>
         </is>
       </c>
       <c r="K29" s="48" t="inlineStr">
@@ -31488,8 +33240,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+      <c r="R29" s="48" t="inlineStr">
+        <is>
+          <t>Orange shade yellow, can be used when a green tone flop is needed. Cleaner than P420-982.</t>
+        </is>
+      </c>
+      <c r="S29" s="48" t="inlineStr">
+        <is>
+          <t>Żółty o pomarańczowym odcieniu; stosować, gdy potrzebny zielony flop. Czystszy niż P420-982.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
       <c r="A30" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-900</t>
@@ -31533,7 +33295,11 @@
           <t>HS Super White</t>
         </is>
       </c>
-      <c r="J30" s="48" t="inlineStr"/>
+      <c r="J30" s="48" t="inlineStr">
+        <is>
+          <t>Mocna biel HS — silnie rozjaśnia recepturę. Pełna moc odpowiednika RT Pale White (P420-902RT).</t>
+        </is>
+      </c>
       <c r="K30" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -31565,8 +33331,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+      <c r="R30" s="48" t="inlineStr">
+        <is>
+          <t>Strong HS white. Full-strength counterpart of RT Pale White P420-902RT.</t>
+        </is>
+      </c>
+      <c r="S30" s="48" t="inlineStr">
+        <is>
+          <t>Mocna biel HS — silnie rozjaśnia recepturę. Pełna moc odpowiednika RT Pale White (P420-902RT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-919</t>
@@ -31612,7 +33388,7 @@
       </c>
       <c r="J31" s="48" t="inlineStr">
         <is>
-          <t>Medium violet with deep flop.</t>
+          <t>Średni fiolet z głębokim flopem. Czysty czerwono-fioletowy ton, mocno pogłębia cień.</t>
         </is>
       </c>
       <c r="K31" s="48" t="inlineStr">
@@ -31646,8 +33422,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+      <c r="R31" s="48" t="inlineStr">
+        <is>
+          <t>Medium violet with deep flop.</t>
+        </is>
+      </c>
+      <c r="S31" s="48" t="inlineStr">
+        <is>
+          <t>Średni fiolet z głębokim flopem. Czysty czerwono-fioletowy ton, mocno pogłębia cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
       <c r="A32" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-921</t>
@@ -31678,7 +33464,7 @@
       </c>
       <c r="G32" s="48" t="inlineStr">
         <is>
-          <t>HS Claret Clean blue tone magenta, cleaner and lighter</t>
+          <t>HS Claret</t>
         </is>
       </c>
       <c r="H32" s="48" t="inlineStr">
@@ -31688,12 +33474,12 @@
       </c>
       <c r="I32" s="48" t="inlineStr">
         <is>
-          <t>HS Claret Clean blue tone magenta, cleaner and lighter</t>
+          <t>HS Claret</t>
         </is>
       </c>
       <c r="J32" s="48" t="inlineStr">
         <is>
-          <t>than P429-976.</t>
+          <t>Czysta magenta o niebieskim tonie; czystsza i jaśniejsza niż P429-976. Czysty, chłodny czerwono-fiolet.</t>
         </is>
       </c>
       <c r="K32" s="48" t="inlineStr">
@@ -31727,8 +33513,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+      <c r="R32" s="48" t="inlineStr">
+        <is>
+          <t>Clean blue tone magenta, cleaner and lighter than P429-976.</t>
+        </is>
+      </c>
+      <c r="S32" s="48" t="inlineStr">
+        <is>
+          <t>Czysta magenta o niebieskim tonie; czystsza i jaśniejsza niż P429-976. Czysty, chłodny czerwono-fiolet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-922</t>
@@ -31759,7 +33555,7 @@
       </c>
       <c r="G33" s="48" t="inlineStr">
         <is>
-          <t>HS Lagoon Blue metallic/pearl formulations.</t>
+          <t>HS Lagoon Blue</t>
         </is>
       </c>
       <c r="H33" s="48" t="inlineStr">
@@ -31769,12 +33565,12 @@
       </c>
       <c r="I33" s="48" t="inlineStr">
         <is>
-          <t>HS Lagoon Blue metallic/pearl formulations.</t>
+          <t>HS Lagoon Blue</t>
         </is>
       </c>
       <c r="J33" s="48" t="inlineStr">
         <is>
-          <t>Green shade blue with a green flop. Used in</t>
+          <t>Zielonawy niebieski z zielonym flopem. Do receptur metalik/perła — przesuwa błękit w zieleń, także w cieniu.</t>
         </is>
       </c>
       <c r="K33" s="48" t="inlineStr">
@@ -31808,8 +33604,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+      <c r="R33" s="48" t="inlineStr">
+        <is>
+          <t>Green shade blue with a green flop. Used in metallic/pearl formulations.</t>
+        </is>
+      </c>
+      <c r="S33" s="48" t="inlineStr">
+        <is>
+          <t>Zielonawy niebieski z zielonym flopem. Do receptur metalik/perła — przesuwa błękit w zieleń, także w cieniu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-941</t>
@@ -31840,7 +33646,7 @@
       </c>
       <c r="G34" s="48" t="inlineStr">
         <is>
-          <t>HS Strong Red solid colours.</t>
+          <t>HS Strong Red</t>
         </is>
       </c>
       <c r="H34" s="48" t="inlineStr">
@@ -31850,12 +33656,12 @@
       </c>
       <c r="I34" s="48" t="inlineStr">
         <is>
-          <t>HS Strong Red solid colours.</t>
+          <t>HS Strong Red</t>
         </is>
       </c>
       <c r="J34" s="48" t="inlineStr">
         <is>
-          <t>Clean, high strength red used primarily in</t>
+          <t>Czysta, wysokowydajna czerwień — głównie kolory solid. Silna siła barwienia, czysty czerwony ton.</t>
         </is>
       </c>
       <c r="K34" s="48" t="inlineStr">
@@ -31889,8 +33695,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+      <c r="R34" s="48" t="inlineStr">
+        <is>
+          <t>Clean, high strength red used primarily in solid colours.</t>
+        </is>
+      </c>
+      <c r="S34" s="48" t="inlineStr">
+        <is>
+          <t>Czysta, wysokowydajna czerwień — głównie kolory solid. Silna siła barwienia, czysty czerwony ton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
       <c r="A35" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-948</t>
@@ -31934,7 +33750,11 @@
           <t>HS Black</t>
         </is>
       </c>
-      <c r="J35" s="48" t="inlineStr"/>
+      <c r="J35" s="48" t="inlineStr">
+        <is>
+          <t>Czerń HS. Ściemia światło i flop. Pełna moc odpowiednika RT Transparent Black (P420-904RT).</t>
+        </is>
+      </c>
       <c r="K35" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -31966,8 +33786,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+      <c r="R35" s="48" t="inlineStr">
+        <is>
+          <t>HS black. Full-strength counterpart of RT Transparent Black P420-904RT.</t>
+        </is>
+      </c>
+      <c r="S35" s="48" t="inlineStr">
+        <is>
+          <t>Czerń HS. Ściemia światło i flop. Pełna moc odpowiednika RT Transparent Black (P420-904RT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
       <c r="A36" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-950</t>
@@ -32013,7 +33843,7 @@
       </c>
       <c r="J36" s="48" t="inlineStr">
         <is>
-          <t>Yellow-shade black, darker flop than</t>
+          <t>Czerń o żółtym odcieniu, ciemniejszy flop niż P425-948. Głębszy, cieplejszy cień niż standardowa czerń HS.</t>
         </is>
       </c>
       <c r="K36" s="48" t="inlineStr">
@@ -32047,8 +33877,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+      <c r="R36" s="48" t="inlineStr">
+        <is>
+          <t>Yellow-shade black, darker flop than P425-948.</t>
+        </is>
+      </c>
+      <c r="S36" s="48" t="inlineStr">
+        <is>
+          <t>Czerń o żółtym odcieniu, ciemniejszy flop niż P425-948. Głębszy, cieplejszy cień niż standardowa czerń HS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1">
       <c r="A37" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-954</t>
@@ -32079,7 +33919,7 @@
       </c>
       <c r="G37" s="48" t="inlineStr">
         <is>
-          <t>HS Blue Green Blue shade green.</t>
+          <t>HS Blue Green</t>
         </is>
       </c>
       <c r="H37" s="48" t="inlineStr">
@@ -32089,10 +33929,14 @@
       </c>
       <c r="I37" s="48" t="inlineStr">
         <is>
-          <t>HS Blue Green Blue shade green.</t>
-        </is>
-      </c>
-      <c r="J37" s="48" t="inlineStr"/>
+          <t>HS Blue Green</t>
+        </is>
+      </c>
+      <c r="J37" s="48" t="inlineStr">
+        <is>
+          <t>Zieleń o niebieskim odcieniu. Chłodna zieleń — przesuwa ton od żółtozielonego w stronę błękitu.</t>
+        </is>
+      </c>
       <c r="K37" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -32124,8 +33968,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+      <c r="R37" s="48" t="inlineStr">
+        <is>
+          <t>Blue shade green.</t>
+        </is>
+      </c>
+      <c r="S37" s="48" t="inlineStr">
+        <is>
+          <t>Zieleń o niebieskim odcieniu. Chłodna zieleń — przesuwa ton od żółtozielonego w stronę błękitu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
       <c r="A38" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-956</t>
@@ -32171,7 +34025,7 @@
       </c>
       <c r="J38" s="48" t="inlineStr">
         <is>
-          <t>Mid-shade blue with green face and red tone flop.</t>
+          <t>Niebieski środkowy z zielonym światłem (face) i czerwonym flopem. Na świetle chłodniejszy, w cieniu cieplejszy.</t>
         </is>
       </c>
       <c r="K38" s="48" t="inlineStr">
@@ -32205,8 +34059,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+      <c r="R38" s="48" t="inlineStr">
+        <is>
+          <t>Mid-shade blue with green face and red tone flop.</t>
+        </is>
+      </c>
+      <c r="S38" s="48" t="inlineStr">
+        <is>
+          <t>Niebieski środkowy z zielonym światłem (face) i czerwonym flopem. Na świetle chłodniejszy, w cieniu cieplejszy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
       <c r="A39" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-957</t>
@@ -32250,7 +34114,11 @@
           <t>HS Fast Blue</t>
         </is>
       </c>
-      <c r="J39" s="48" t="inlineStr"/>
+      <c r="J39" s="48" t="inlineStr">
+        <is>
+          <t>Wysokowydajny niebieski HS. Pełna moc odpowiednika RT Deep Blue (P420-910RT).</t>
+        </is>
+      </c>
       <c r="K39" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -32282,8 +34150,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
+      <c r="R39" s="48" t="inlineStr">
+        <is>
+          <t>High strength blue. Full-strength counterpart of RT Deep Blue P420-910RT.</t>
+        </is>
+      </c>
+      <c r="S39" s="48" t="inlineStr">
+        <is>
+          <t>Wysokowydajny niebieski HS. Pełna moc odpowiednika RT Deep Blue (P420-910RT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
       <c r="A40" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-971</t>
@@ -32314,7 +34192,7 @@
       </c>
       <c r="G40" s="48" t="inlineStr">
         <is>
-          <t>HS Brilliant Red Clean yellow tone red.</t>
+          <t>HS Brilliant Red</t>
         </is>
       </c>
       <c r="H40" s="48" t="inlineStr">
@@ -32324,10 +34202,14 @@
       </c>
       <c r="I40" s="48" t="inlineStr">
         <is>
-          <t>HS Brilliant Red Clean yellow tone red.</t>
-        </is>
-      </c>
-      <c r="J40" s="48" t="inlineStr"/>
+          <t>HS Brilliant Red</t>
+        </is>
+      </c>
+      <c r="J40" s="48" t="inlineStr">
+        <is>
+          <t>Czysta czerwień o żółtym tonie. Ciepła, jaskrawa czerwień (w stronę pomarańczu), bez brudzenia flopu.</t>
+        </is>
+      </c>
       <c r="K40" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -32359,8 +34241,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
+      <c r="R40" s="48" t="inlineStr">
+        <is>
+          <t>Clean yellow tone red.</t>
+        </is>
+      </c>
+      <c r="S40" s="48" t="inlineStr">
+        <is>
+          <t>Czysta czerwień o żółtym tonie. Ciepła, jaskrawa czerwień (w stronę pomarańczu), bez brudzenia flopu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1">
       <c r="A41" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-984</t>
@@ -32406,46 +34298,56 @@
       </c>
       <c r="J41" s="49" t="inlineStr">
         <is>
+          <t>Drobny, jasny metalik z ciemniejszym flopem niż P425-986. Rozjaśnia światło, pogłębia cień względem średniego aluminium.</t>
+        </is>
+      </c>
+      <c r="K41" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L41" s="49" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="M41" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N41" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K BRIGHT MEDIUM ALUMINIUM | PDF: HS Medium Fine Aluminium</t>
+        </is>
+      </c>
+      <c r="O41" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P41" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q41" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R41" s="49" t="inlineStr">
+        <is>
           <t>Fine bright metallic with darker flop than P425-986.</t>
         </is>
       </c>
-      <c r="K41" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L41" s="49" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="M41" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N41" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K BRIGHT MEDIUM ALUMINIUM | PDF: HS Medium Fine Aluminium</t>
-        </is>
-      </c>
-      <c r="O41" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P41" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q41" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
+      <c r="S41" s="49" t="inlineStr">
+        <is>
+          <t>Drobny, jasny metalik z ciemniejszym flopem niż P425-986. Rozjaśnia światło, pogłębia cień względem średniego aluminium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
       <c r="A42" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-985</t>
@@ -32491,7 +34393,7 @@
       </c>
       <c r="J42" s="48" t="inlineStr">
         <is>
-          <t>Fine metallic with a dark face and light flop.</t>
+          <t>Drobny metalik z ciemnym światłem (face) i jasnym flopem. Drobne ziarno: ciemniejszy na wprost, jaśniejszy w cieniu.</t>
         </is>
       </c>
       <c r="K42" s="48" t="inlineStr">
@@ -32525,8 +34427,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
+      <c r="R42" s="48" t="inlineStr">
+        <is>
+          <t>Fine metallic with a dark face and light flop.</t>
+        </is>
+      </c>
+      <c r="S42" s="48" t="inlineStr">
+        <is>
+          <t>Drobny metalik z ciemnym światłem (face) i jasnym flopem. Drobne ziarno: ciemniejszy na wprost, jaśniejszy w cieniu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1">
       <c r="A43" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-986</t>
@@ -32572,7 +34484,7 @@
       </c>
       <c r="J43" s="48" t="inlineStr">
         <is>
-          <t>Medium metallic with a darker flop than P425-985.</t>
+          <t>Średni metalik z ciemniejszym flopem niż P425-985. Grubsze ziarno niż Fine — ciemniejszy cień.</t>
         </is>
       </c>
       <c r="K43" s="48" t="inlineStr">
@@ -32606,8 +34518,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
+      <c r="R43" s="48" t="inlineStr">
+        <is>
+          <t>Medium metallic with a darker flop than P425-985.</t>
+        </is>
+      </c>
+      <c r="S43" s="48" t="inlineStr">
+        <is>
+          <t>Średni metalik z ciemniejszym flopem niż P425-985. Grubsze ziarno niż Fine — ciemniejszy cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
       <c r="A44" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-987</t>
@@ -32653,7 +34575,7 @@
       </c>
       <c r="J44" s="48" t="inlineStr">
         <is>
-          <t>Medium metallic with a darker flop than P425-985.</t>
+          <t>Średnio grube aluminium z ciemniejszym flopem niż P425-985. Wyraźniejsze ziarno, ciemniejszy cień.</t>
         </is>
       </c>
       <c r="K44" s="48" t="inlineStr">
@@ -32687,8 +34609,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
+      <c r="R44" s="48" t="inlineStr">
+        <is>
+          <t>Medium metallic with a darker flop than P425-985.</t>
+        </is>
+      </c>
+      <c r="S44" s="48" t="inlineStr">
+        <is>
+          <t>Średnio grube aluminium z ciemniejszym flopem niż P425-985. Wyraźniejsze ziarno, ciemniejszy cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
       <c r="A45" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-988</t>
@@ -32734,7 +34666,7 @@
       </c>
       <c r="J45" s="48" t="inlineStr">
         <is>
-          <t>Brighter face, darker flop than P425-987.</t>
+          <t>Grube aluminium: jaśniejsze światło (face), ciemniejszy flop niż P425-987. Mocniejszy błysk ziarna, głębszy cień.</t>
         </is>
       </c>
       <c r="K45" s="48" t="inlineStr">
@@ -32768,8 +34700,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
+      <c r="R45" s="48" t="inlineStr">
+        <is>
+          <t>Brighter face, darker flop than P425-987.</t>
+        </is>
+      </c>
+      <c r="S45" s="48" t="inlineStr">
+        <is>
+          <t>Grube aluminium: jaśniejsze światło (face), ciemniejszy flop niż P425-987. Mocniejszy błysk ziarna, głębszy cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
       <c r="A46" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-989</t>
@@ -32800,7 +34742,7 @@
       </c>
       <c r="G46" s="48" t="inlineStr">
         <is>
-          <t>HS Very Coarse Aluminium Very coarse, bright aluminium</t>
+          <t>HS Very Coarse Aluminium</t>
         </is>
       </c>
       <c r="H46" s="48" t="inlineStr">
@@ -32810,12 +34752,12 @@
       </c>
       <c r="I46" s="48" t="inlineStr">
         <is>
-          <t>HS Very Coarse Aluminium Very coarse, bright aluminium</t>
+          <t>HS Very Coarse Aluminium</t>
         </is>
       </c>
       <c r="J46" s="48" t="inlineStr">
         <is>
-          <t>with a dark flop.</t>
+          <t>Bardzo grube, jasne aluminium z ciemnym flopem. Duże ziarno, silny błysk na świetle, głęboki cień.</t>
         </is>
       </c>
       <c r="K46" s="48" t="inlineStr">
@@ -32849,8 +34791,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
+      <c r="R46" s="48" t="inlineStr">
+        <is>
+          <t>Very coarse, bright aluminium with a dark flop.</t>
+        </is>
+      </c>
+      <c r="S46" s="48" t="inlineStr">
+        <is>
+          <t>Bardzo grube, jasne aluminium z ciemnym flopem. Duże ziarno, silny błysk na świetle, głęboki cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-991</t>
@@ -32881,7 +34833,7 @@
       </c>
       <c r="G47" s="48" t="inlineStr">
         <is>
-          <t>Fine Satin Aluminium Fine aluminium. Darker</t>
+          <t>Fine Satin Aluminium</t>
         </is>
       </c>
       <c r="H47" s="48" t="inlineStr">
@@ -32891,12 +34843,12 @@
       </c>
       <c r="I47" s="48" t="inlineStr">
         <is>
-          <t>Fine Satin Aluminium Fine aluminium. Darker</t>
+          <t>Fine Satin Aluminium</t>
         </is>
       </c>
       <c r="J47" s="48" t="inlineStr">
         <is>
-          <t>face and lighter flop than</t>
+          <t>Drobne aluminium satynowe. Ciemniejsze światło i jaśniejszy flop niż P425-984. Uspokaja błysk, rozjaśnia cień.</t>
         </is>
       </c>
       <c r="K47" s="48" t="inlineStr">
@@ -32930,8 +34882,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
+      <c r="R47" s="48" t="inlineStr">
+        <is>
+          <t>Fine aluminium. Darker face and lighter flop than P425-984.</t>
+        </is>
+      </c>
+      <c r="S47" s="48" t="inlineStr">
+        <is>
+          <t>Drobne aluminium satynowe. Ciemniejsze światło i jaśniejszy flop niż P425-984. Uspokaja błysk, rozjaśnia cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
       <c r="A48" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-992</t>
@@ -32977,7 +34939,7 @@
       </c>
       <c r="J48" s="48" t="inlineStr">
         <is>
-          <t>Medium bright metallic with a darker flop than P425-984.</t>
+          <t>Średnio jasny, błyszczący grubszy metalik z ciemniejszym flopem niż P425-984.</t>
         </is>
       </c>
       <c r="K48" s="48" t="inlineStr">
@@ -33011,8 +34973,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
+      <c r="R48" s="48" t="inlineStr">
+        <is>
+          <t>Medium bright metallic with a darker flop than P425-984.</t>
+        </is>
+      </c>
+      <c r="S48" s="48" t="inlineStr">
+        <is>
+          <t>Średnio jasny, błyszczący grubszy metalik z ciemniejszym flopem niż P425-984.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-998</t>
@@ -33043,7 +35015,7 @@
       </c>
       <c r="G49" s="48" t="inlineStr">
         <is>
-          <t>HS Coarse Silver Dollar Aluminium Bright coarse aluminium.</t>
+          <t>HS Coarse Silver Dollar Aluminium</t>
         </is>
       </c>
       <c r="H49" s="48" t="inlineStr">
@@ -33053,12 +35025,12 @@
       </c>
       <c r="I49" s="48" t="inlineStr">
         <is>
-          <t>HS Coarse Silver Dollar Aluminium Bright coarse aluminium.</t>
+          <t>HS Coarse Silver Dollar Aluminium</t>
         </is>
       </c>
       <c r="J49" s="48" t="inlineStr">
         <is>
-          <t>Cleaner face and darker flop than P425-992.</t>
+          <t>Jasne grube aluminium typu silver dollar. Czystsze światło i ciemniejszy flop niż P425-992.</t>
         </is>
       </c>
       <c r="K49" s="48" t="inlineStr">
@@ -33092,8 +35064,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+      <c r="R49" s="48" t="inlineStr">
+        <is>
+          <t>Bright coarse aluminium. Cleaner face and darker flop than P425-992.</t>
+        </is>
+      </c>
+      <c r="S49" s="48" t="inlineStr">
+        <is>
+          <t>Jasne grube aluminium typu silver dollar. Czystsze światło i ciemniejszy flop niż P425-992.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P425-EB02</t>
@@ -33132,8 +35114,16 @@
           <t>2K KONWERTER BAZY DO KOMÓR SILNIKA</t>
         </is>
       </c>
-      <c r="I50" s="48" t="inlineStr"/>
-      <c r="J50" s="48" t="inlineStr"/>
+      <c r="I50" s="48" t="inlineStr">
+        <is>
+          <t>KONWERTER BAZY DO KOMÓR SILNIKA</t>
+        </is>
+      </c>
+      <c r="J50" s="48" t="inlineStr">
+        <is>
+          <t>Konwerter bazy do komór silnika — zmienia bazę pod aplikację w komorze silnika. Nie jest tonerem kolorystycznym.</t>
+        </is>
+      </c>
       <c r="K50" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -33165,8 +35155,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+      <c r="R50" s="48" t="inlineStr">
+        <is>
+          <t>Engine-bay base converter. Not a colour toner.</t>
+        </is>
+      </c>
+      <c r="S50" s="48" t="inlineStr">
+        <is>
+          <t>Konwerter bazy do komór silnika — zmienia bazę pod aplikację w komorze silnika. Nie jest tonerem kolorystycznym.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-HE02</t>
@@ -33212,46 +35212,56 @@
       </c>
       <c r="J51" s="49" t="inlineStr">
         <is>
+          <t>W metalikach dodaje żółć na świetle (face) i jasnoniebieski ton na flopie. Koryguje flop w stronę chłodnego błękitu.</t>
+        </is>
+      </c>
+      <c r="K51" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L51" s="49" t="inlineStr">
+        <is>
+          <t>Czerń/Biel</t>
+        </is>
+      </c>
+      <c r="M51" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N51" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K ULTRA FINE WHITE | PDF: Blue Frost</t>
+        </is>
+      </c>
+      <c r="O51" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P51" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q51" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R51" s="49" t="inlineStr">
+        <is>
           <t>Used in metallic colours to add yellow to the face and light blue tone to the flop.</t>
         </is>
       </c>
-      <c r="K51" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L51" s="49" t="inlineStr">
-        <is>
-          <t>Czerń/Biel</t>
-        </is>
-      </c>
-      <c r="M51" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N51" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K ULTRA FINE WHITE | PDF: Blue Frost</t>
-        </is>
-      </c>
-      <c r="O51" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P51" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q51" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
+      <c r="S51" s="49" t="inlineStr">
+        <is>
+          <t>W metalikach dodaje żółć na świetle (face) i jasnoniebieski ton na flopie. Koryguje flop w stronę chłodnego błękitu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1">
       <c r="A52" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-HE03</t>
@@ -33297,7 +35307,7 @@
       </c>
       <c r="J52" s="48" t="inlineStr">
         <is>
-          <t>Subtle blue tone on face, lightens flop.</t>
+          <t>Subtelny niebieski ton na świetle (face), rozjaśnia flop. Grafitowe ziarno — uspokaja i rozjaśnia cień.</t>
         </is>
       </c>
       <c r="K52" s="48" t="inlineStr">
@@ -33331,8 +35341,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
+      <c r="R52" s="48" t="inlineStr">
+        <is>
+          <t>Subtle blue tone on face, lightens flop.</t>
+        </is>
+      </c>
+      <c r="S52" s="48" t="inlineStr">
+        <is>
+          <t>Subtelny niebieski ton na świetle (face), rozjaśnia flop. Grafitowe ziarno — uspokaja i rozjaśnia cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
       <c r="A53" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-HE04</t>
@@ -33363,7 +35383,7 @@
       </c>
       <c r="G53" s="48" t="inlineStr">
         <is>
-          <t>Gold Flash Medium gold aluminium flake.</t>
+          <t>Gold Flash</t>
         </is>
       </c>
       <c r="H53" s="48" t="inlineStr">
@@ -33373,10 +35393,14 @@
       </c>
       <c r="I53" s="48" t="inlineStr">
         <is>
-          <t>Gold Flash Medium gold aluminium flake.</t>
-        </is>
-      </c>
-      <c r="J53" s="48" t="inlineStr"/>
+          <t>Gold Flash</t>
+        </is>
+      </c>
+      <c r="J53" s="48" t="inlineStr">
+        <is>
+          <t>Średni złoty płatek aluminiowy. Dodaje złoty błysk ziarna (nie toner konwencjonalny).</t>
+        </is>
+      </c>
       <c r="K53" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -33408,8 +35432,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
+      <c r="R53" s="48" t="inlineStr">
+        <is>
+          <t>Medium gold aluminium flake.</t>
+        </is>
+      </c>
+      <c r="S53" s="48" t="inlineStr">
+        <is>
+          <t>Średni złoty płatek aluminiowy. Dodaje złoty błysk ziarna (nie toner konwencjonalny).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
       <c r="A54" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-HE05</t>
@@ -33440,7 +35474,7 @@
       </c>
       <c r="G54" s="48" t="inlineStr">
         <is>
-          <t>Orange Flash Orange aluminium flake.</t>
+          <t>Orange Flash</t>
         </is>
       </c>
       <c r="H54" s="48" t="inlineStr">
@@ -33450,10 +35484,14 @@
       </c>
       <c r="I54" s="48" t="inlineStr">
         <is>
-          <t>Orange Flash Orange aluminium flake.</t>
-        </is>
-      </c>
-      <c r="J54" s="48" t="inlineStr"/>
+          <t>Orange Flash</t>
+        </is>
+      </c>
+      <c r="J54" s="48" t="inlineStr">
+        <is>
+          <t>Pomarańczowy płatek aluminiowy. Dodaje pomarańczowy refleks na ziarnie.</t>
+        </is>
+      </c>
       <c r="K54" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -33485,8 +35523,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
+      <c r="R54" s="48" t="inlineStr">
+        <is>
+          <t>Orange aluminium flake.</t>
+        </is>
+      </c>
+      <c r="S54" s="48" t="inlineStr">
+        <is>
+          <t>Pomarańczowy płatek aluminiowy. Dodaje pomarańczowy refleks na ziarnie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
       <c r="A55" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-HE08</t>
@@ -33525,8 +35573,16 @@
           <t>2K BLUE ALUMINIUM</t>
         </is>
       </c>
-      <c r="I55" s="48" t="inlineStr"/>
-      <c r="J55" s="48" t="inlineStr"/>
+      <c r="I55" s="48" t="inlineStr">
+        <is>
+          <t>BLUE ALUMINIUM</t>
+        </is>
+      </c>
+      <c r="J55" s="48" t="inlineStr">
+        <is>
+          <t>Niebieskie aluminium — barwiony płatek metaliczny, dodaje niebieski refleks na ziarnie.</t>
+        </is>
+      </c>
       <c r="K55" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -33558,8 +35614,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
+      <c r="R55" s="48" t="inlineStr">
+        <is>
+          <t>Blue coloured aluminium flake.</t>
+        </is>
+      </c>
+      <c r="S55" s="48" t="inlineStr">
+        <is>
+          <t>Niebieskie aluminium — barwiony płatek metaliczny, dodaje niebieski refleks na ziarnie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
       <c r="A56" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP05</t>
@@ -33605,7 +35671,7 @@
       </c>
       <c r="J56" s="48" t="inlineStr">
         <is>
-          <t>Clean white. Brighter face, darker flop than P426-PP06.</t>
+          <t>Czysta biel perłowa. Jaśniejsze światło (face), ciemniejszy flop niż P426-PP06. Rozjaśnia perły, pogłębia cień względem Fine White Pearl.</t>
         </is>
       </c>
       <c r="K56" s="48" t="inlineStr">
@@ -33639,8 +35705,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
+      <c r="R56" s="48" t="inlineStr">
+        <is>
+          <t>Clean white. Brighter face, darker flop than P426-PP06.</t>
+        </is>
+      </c>
+      <c r="S56" s="48" t="inlineStr">
+        <is>
+          <t>Czysta biel perłowa. Jaśniejsze światło (face), ciemniejszy flop niż P426-PP06. Rozjaśnia perły, pogłębia cień względem Fine White Pearl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1">
       <c r="A57" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP06</t>
@@ -33686,46 +35762,56 @@
       </c>
       <c r="J57" s="49" t="inlineStr">
         <is>
+          <t>Drobna biała perła. Brudniejsze światło i jaśniejszy flop niż P426-PP05. Drobniejsze ziarno, uspokaja kontrast światło/cień.</t>
+        </is>
+      </c>
+      <c r="K57" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L57" s="49" t="inlineStr">
+        <is>
+          <t>Perła</t>
+        </is>
+      </c>
+      <c r="M57" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N57" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K FINE PEARL WHITE | PDF: Fine White Pearl</t>
+        </is>
+      </c>
+      <c r="O57" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P57" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q57" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R57" s="49" t="inlineStr">
+        <is>
           <t>Dirtier face and lighter flop than P426-PP05.</t>
         </is>
       </c>
-      <c r="K57" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L57" s="49" t="inlineStr">
-        <is>
-          <t>Perła</t>
-        </is>
-      </c>
-      <c r="M57" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N57" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K FINE PEARL WHITE | PDF: Fine White Pearl</t>
-        </is>
-      </c>
-      <c r="O57" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P57" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q57" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="36" customHeight="1">
+      <c r="S57" s="49" t="inlineStr">
+        <is>
+          <t>Drobna biała perła. Brudniejsze światło i jaśniejszy flop niż P426-PP05. Drobniejsze ziarno, uspokaja kontrast światło/cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1">
       <c r="A58" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP07</t>
@@ -33771,7 +35857,7 @@
       </c>
       <c r="J58" s="49" t="inlineStr">
         <is>
-          <t>Blue face, yellow flop. Coarser than</t>
+          <t>Niebieskie światło (face), żółty flop. Grubsza niż P426-PP63. Perła z travel: błękit na wprost, żółć w cieniu.</t>
         </is>
       </c>
       <c r="K58" s="49" t="inlineStr">
@@ -33809,8 +35895,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
+      <c r="R58" s="49" t="inlineStr">
+        <is>
+          <t>Blue face, yellow flop. Coarser than P426-PP63.</t>
+        </is>
+      </c>
+      <c r="S58" s="49" t="inlineStr">
+        <is>
+          <t>Niebieskie światło (face), żółty flop. Grubsza niż P426-PP63. Perła z travel: błękit na wprost, żółć w cieniu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1">
       <c r="A59" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP08</t>
@@ -33856,7 +35952,7 @@
       </c>
       <c r="J59" s="48" t="inlineStr">
         <is>
-          <t>Red mica, coarser than P426-PP62.</t>
+          <t>Czerwona mika, grubsza niż P426-PP62. Dodaje czerwony efekt perłowy, wyraźniejsze ziarno.</t>
         </is>
       </c>
       <c r="K59" s="48" t="inlineStr">
@@ -33890,8 +35986,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="60" ht="36" customHeight="1">
+      <c r="R59" s="48" t="inlineStr">
+        <is>
+          <t>Red mica, coarser than P426-PP62.</t>
+        </is>
+      </c>
+      <c r="S59" s="48" t="inlineStr">
+        <is>
+          <t>Czerwona mika, grubsza niż P426-PP62. Dodaje czerwony efekt perłowy, wyraźniejsze ziarno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
       <c r="A60" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP09</t>
@@ -33937,46 +36043,56 @@
       </c>
       <c r="J60" s="49" t="inlineStr">
         <is>
+          <t>Złote światło (face), niebieskawy flop. Złota perła z chłodniejszym cieniem.</t>
+        </is>
+      </c>
+      <c r="K60" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L60" s="49" t="inlineStr">
+        <is>
+          <t>Perła</t>
+        </is>
+      </c>
+      <c r="M60" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N60" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K PEARL GOLD | PDF: Gold Pearl</t>
+        </is>
+      </c>
+      <c r="O60" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P60" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q60" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R60" s="49" t="inlineStr">
+        <is>
           <t>Gold face, bluish tone flop.</t>
         </is>
       </c>
-      <c r="K60" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L60" s="49" t="inlineStr">
-        <is>
-          <t>Perła</t>
-        </is>
-      </c>
-      <c r="M60" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N60" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K PEARL GOLD | PDF: Gold Pearl</t>
-        </is>
-      </c>
-      <c r="O60" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P60" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q60" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
+      <c r="S60" s="49" t="inlineStr">
+        <is>
+          <t>Złote światło (face), niebieskawy flop. Złota perła z chłodniejszym cieniem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
       <c r="A61" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP10</t>
@@ -34022,7 +36138,7 @@
       </c>
       <c r="J61" s="48" t="inlineStr">
         <is>
-          <t>Copper face, travels to dark copper tone on the flop.</t>
+          <t>Miedziane światło (face), na flopie przechodzi w ciemną miedź. Perła z travel miedzianym.</t>
         </is>
       </c>
       <c r="K61" s="48" t="inlineStr">
@@ -34056,8 +36172,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="36" customHeight="1">
+      <c r="R61" s="48" t="inlineStr">
+        <is>
+          <t>Copper face, travels to dark copper tone on the flop.</t>
+        </is>
+      </c>
+      <c r="S61" s="48" t="inlineStr">
+        <is>
+          <t>Miedziane światło (face), na flopie przechodzi w ciemną miedź. Perła z travel miedzianym.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
       <c r="A62" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP60</t>
@@ -34088,7 +36214,7 @@
       </c>
       <c r="G62" s="49" t="inlineStr">
         <is>
-          <t>White Satin Pearl Fine white flake.</t>
+          <t>White Satin Pearl</t>
         </is>
       </c>
       <c r="H62" s="49" t="inlineStr">
@@ -34098,10 +36224,14 @@
       </c>
       <c r="I62" s="49" t="inlineStr">
         <is>
-          <t>White Satin Pearl Fine white flake.</t>
-        </is>
-      </c>
-      <c r="J62" s="49" t="inlineStr"/>
+          <t>White Satin Pearl</t>
+        </is>
+      </c>
+      <c r="J62" s="49" t="inlineStr">
+        <is>
+          <t>Drobne białe ziarno perłowe (satyna). Subtelna biała perła, uspokaja błysk.</t>
+        </is>
+      </c>
       <c r="K62" s="49" t="inlineStr">
         <is>
           <t>g</t>
@@ -34137,8 +36267,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="36" customHeight="1">
+      <c r="R62" s="49" t="inlineStr">
+        <is>
+          <t>Fine white flake.</t>
+        </is>
+      </c>
+      <c r="S62" s="49" t="inlineStr">
+        <is>
+          <t>Drobne białe ziarno perłowe (satyna). Subtelna biała perła, uspokaja błysk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
       <c r="A63" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP61</t>
@@ -34184,46 +36324,56 @@
       </c>
       <c r="J63" s="49" t="inlineStr">
         <is>
+          <t>Interferencyjna czerwona mika z zielonym flopem. Czerwień na świetle, zieleń w cieniu.</t>
+        </is>
+      </c>
+      <c r="K63" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L63" s="49" t="inlineStr">
+        <is>
+          <t>Perła</t>
+        </is>
+      </c>
+      <c r="M63" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N63" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K PEARL RED FINE | PDF: Fine Red Pearl</t>
+        </is>
+      </c>
+      <c r="O63" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P63" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q63" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R63" s="49" t="inlineStr">
+        <is>
           <t>Interference red mica with a green flop.</t>
         </is>
       </c>
-      <c r="K63" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L63" s="49" t="inlineStr">
-        <is>
-          <t>Perła</t>
-        </is>
-      </c>
-      <c r="M63" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N63" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K PEARL RED FINE | PDF: Fine Red Pearl</t>
-        </is>
-      </c>
-      <c r="O63" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P63" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q63" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
+      <c r="S63" s="49" t="inlineStr">
+        <is>
+          <t>Interferencyjna czerwona mika z zielonym flopem. Czerwień na świetle, zieleń w cieniu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
       <c r="A64" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP62</t>
@@ -34269,46 +36419,56 @@
       </c>
       <c r="J64" s="49" t="inlineStr">
         <is>
+          <t>Czerwona mika, drobniejsza niż P426-PP08. Russet perłowy o drobniejszym ziarnie.</t>
+        </is>
+      </c>
+      <c r="K64" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L64" s="49" t="inlineStr">
+        <is>
+          <t>Perła</t>
+        </is>
+      </c>
+      <c r="M64" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N64" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K RUSSET PEARL FINE | PDF: Fine Russet Pearl</t>
+        </is>
+      </c>
+      <c r="O64" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P64" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q64" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R64" s="49" t="inlineStr">
+        <is>
           <t>Red mica. Finer than P426-PP08.</t>
         </is>
       </c>
-      <c r="K64" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L64" s="49" t="inlineStr">
-        <is>
-          <t>Perła</t>
-        </is>
-      </c>
-      <c r="M64" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N64" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K RUSSET PEARL FINE | PDF: Fine Russet Pearl</t>
-        </is>
-      </c>
-      <c r="O64" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P64" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q64" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="36" customHeight="1">
+      <c r="S64" s="49" t="inlineStr">
+        <is>
+          <t>Czerwona mika, drobniejsza niż P426-PP08. Russet perłowy o drobniejszym ziarnie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP63</t>
@@ -34354,46 +36514,56 @@
       </c>
       <c r="J65" s="49" t="inlineStr">
         <is>
+          <t>Niebieskie światło, żółty flop. Drobniejsza niż P426-PP07. Ten sam travel co Blue Pearl, spokojniejsze ziarno.</t>
+        </is>
+      </c>
+      <c r="K65" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L65" s="49" t="inlineStr">
+        <is>
+          <t>Perła</t>
+        </is>
+      </c>
+      <c r="M65" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N65" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K PEARL BLUE FINE | PDF: Fine Blue Pearl</t>
+        </is>
+      </c>
+      <c r="O65" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P65" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q65" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R65" s="49" t="inlineStr">
+        <is>
           <t>Blue face, yellow flop. Finer than P426-PP07.</t>
         </is>
       </c>
-      <c r="K65" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L65" s="49" t="inlineStr">
-        <is>
-          <t>Perła</t>
-        </is>
-      </c>
-      <c r="M65" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N65" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K PEARL BLUE FINE | PDF: Fine Blue Pearl</t>
-        </is>
-      </c>
-      <c r="O65" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P65" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q65" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="36" customHeight="1">
+      <c r="S65" s="49" t="inlineStr">
+        <is>
+          <t>Niebieskie światło, żółty flop. Drobniejsza niż P426-PP07. Ten sam travel co Blue Pearl, spokojniejsze ziarno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="48" customHeight="1">
       <c r="A66" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP64</t>
@@ -34439,7 +36609,7 @@
       </c>
       <c r="J66" s="48" t="inlineStr">
         <is>
-          <t>Lilac face, green flop.</t>
+          <t>Liliowe światło (face), zielony flop. Fioletowa perła z zielonym cieniem.</t>
         </is>
       </c>
       <c r="K66" s="48" t="inlineStr">
@@ -34473,8 +36643,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+      <c r="R66" s="48" t="inlineStr">
+        <is>
+          <t>Lilac face, green flop.</t>
+        </is>
+      </c>
+      <c r="S66" s="48" t="inlineStr">
+        <is>
+          <t>Liliowe światło (face), zielony flop. Fioletowa perła z zielonym cieniem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="48" customHeight="1">
       <c r="A67" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP65</t>
@@ -34520,7 +36700,7 @@
       </c>
       <c r="J67" s="48" t="inlineStr">
         <is>
-          <t>Green face, reddish tone flop.</t>
+          <t>Zielone światło (face), czerwonawy flop. Zielona perła z ciepłym cieniem.</t>
         </is>
       </c>
       <c r="K67" s="48" t="inlineStr">
@@ -34554,8 +36734,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
+      <c r="R67" s="48" t="inlineStr">
+        <is>
+          <t>Green face, reddish tone flop.</t>
+        </is>
+      </c>
+      <c r="S67" s="48" t="inlineStr">
+        <is>
+          <t>Zielone światło (face), czerwonawy flop. Zielona perła z ciepłym cieniem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-PP68</t>
@@ -34601,46 +36791,56 @@
       </c>
       <c r="J68" s="49" t="inlineStr">
         <is>
+          <t>Czyste pomarańczowe światło (face), zielony flop. Czysta pomarańcz perłowa z chłodniejszym cieniem.</t>
+        </is>
+      </c>
+      <c r="K68" s="49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L68" s="49" t="inlineStr">
+        <is>
+          <t>Perła</t>
+        </is>
+      </c>
+      <c r="M68" s="49" t="inlineStr">
+        <is>
+          <t>KOLIZJA NAZW</t>
+        </is>
+      </c>
+      <c r="N68" s="49" t="inlineStr">
+        <is>
+          <t>ODS: 2K PEARL ORANGE | PDF: Orange Pearl</t>
+        </is>
+      </c>
+      <c r="O68" s="49" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P68" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Q68" s="49" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="R68" s="49" t="inlineStr">
+        <is>
           <t>Clean orange face, green tone flop.</t>
         </is>
       </c>
-      <c r="K68" s="49" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L68" s="49" t="inlineStr">
-        <is>
-          <t>Perła</t>
-        </is>
-      </c>
-      <c r="M68" s="49" t="inlineStr">
-        <is>
-          <t>KOLIZJA NAZW</t>
-        </is>
-      </c>
-      <c r="N68" s="49" t="inlineStr">
-        <is>
-          <t>ODS: 2K PEARL ORANGE | PDF: Orange Pearl</t>
-        </is>
-      </c>
-      <c r="O68" s="49" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P68" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="Q68" s="49" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="36" customHeight="1">
+      <c r="S68" s="49" t="inlineStr">
+        <is>
+          <t>Czyste pomarańczowe światło (face), zielony flop. Czysta pomarańcz perłowa z chłodniejszym cieniem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="48" customHeight="1">
       <c r="A69" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-914</t>
@@ -34679,8 +36879,16 @@
           <t>2K HS CLEAN BLUE VIOLET</t>
         </is>
       </c>
-      <c r="I69" s="48" t="inlineStr"/>
-      <c r="J69" s="48" t="inlineStr"/>
+      <c r="I69" s="48" t="inlineStr">
+        <is>
+          <t>HS CLEAN BLUE VIOLET</t>
+        </is>
+      </c>
+      <c r="J69" s="48" t="inlineStr">
+        <is>
+          <t>Czysty fiolet o niebieskim odcieniu (HS). Chłodny, czysty ton — korekta w stronę niebieskiego fioletu.</t>
+        </is>
+      </c>
       <c r="K69" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -34712,8 +36920,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
+      <c r="R69" s="48" t="inlineStr">
+        <is>
+          <t>Clean blue-shade violet HS toner.</t>
+        </is>
+      </c>
+      <c r="S69" s="48" t="inlineStr">
+        <is>
+          <t>Czysty fiolet o niebieskim odcieniu (HS). Chłodny, czysty ton — korekta w stronę niebieskiego fioletu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="48" customHeight="1">
       <c r="A70" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-917</t>
@@ -34752,8 +36970,16 @@
           <t>2K HS GREEN GOLD</t>
         </is>
       </c>
-      <c r="I70" s="48" t="inlineStr"/>
-      <c r="J70" s="48" t="inlineStr"/>
+      <c r="I70" s="48" t="inlineStr">
+        <is>
+          <t>HS GREEN GOLD</t>
+        </is>
+      </c>
+      <c r="J70" s="48" t="inlineStr">
+        <is>
+          <t>Złoto-zielony toner HS. Dodaje złocistą zieleń na świetle, ciepły zielonożółty ton.</t>
+        </is>
+      </c>
       <c r="K70" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -34785,8 +37011,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="71" ht="36" customHeight="1">
+      <c r="R70" s="48" t="inlineStr">
+        <is>
+          <t>Green-gold HS toner.</t>
+        </is>
+      </c>
+      <c r="S70" s="48" t="inlineStr">
+        <is>
+          <t>Złoto-zielony toner HS. Dodaje złocistą zieleń na świetle, ciepły zielonożółty ton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="48" customHeight="1">
       <c r="A71" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-923</t>
@@ -34832,7 +37068,7 @@
       </c>
       <c r="J71" s="48" t="inlineStr">
         <is>
-          <t>Mid-shade transparent maroon, dark flop.</t>
+          <t>Transparentny bordo o środkowym odcieniu, ciemny flop. Ściemia i czerwieni w cieniu, bez silnego krycia.</t>
         </is>
       </c>
       <c r="K71" s="48" t="inlineStr">
@@ -34866,8 +37102,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="36" customHeight="1">
+      <c r="R71" s="48" t="inlineStr">
+        <is>
+          <t>Mid-shade transparent maroon, dark flop.</t>
+        </is>
+      </c>
+      <c r="S71" s="48" t="inlineStr">
+        <is>
+          <t>Transparentny bordo o środkowym odcieniu, ciemny flop. Ściemia i czerwieni w cieniu, bez silnego krycia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1">
       <c r="A72" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-932</t>
@@ -34906,8 +37152,16 @@
           <t>2K HS CLEAN ORGANIC ORANGE</t>
         </is>
       </c>
-      <c r="I72" s="48" t="inlineStr"/>
-      <c r="J72" s="48" t="inlineStr"/>
+      <c r="I72" s="48" t="inlineStr">
+        <is>
+          <t>HS CLEAN ORGANIC ORANGE</t>
+        </is>
+      </c>
+      <c r="J72" s="48" t="inlineStr">
+        <is>
+          <t>Czysta organiczna pomarańcz HS. Nasycony, czysty ton pomarańczowy (nie tlenkowy).</t>
+        </is>
+      </c>
       <c r="K72" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -34939,8 +37193,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="36" customHeight="1">
+      <c r="R72" s="48" t="inlineStr">
+        <is>
+          <t>Clean organic orange HS toner.</t>
+        </is>
+      </c>
+      <c r="S72" s="48" t="inlineStr">
+        <is>
+          <t>Czysta organiczna pomarańcz HS. Nasycony, czysty ton pomarańczowy (nie tlenkowy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="48" customHeight="1">
       <c r="A73" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-937</t>
@@ -34986,7 +37250,7 @@
       </c>
       <c r="J73" s="48" t="inlineStr">
         <is>
-          <t>Green shade yellow with a green shade flop.</t>
+          <t>Żółty o zielonym odcieniu, z zielonym flopem. Chłodna, blada żółć — rozjaśnia w stronę zieleni.</t>
         </is>
       </c>
       <c r="K73" s="48" t="inlineStr">
@@ -35020,8 +37284,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="36" customHeight="1">
+      <c r="R73" s="48" t="inlineStr">
+        <is>
+          <t>Green shade yellow with a green shade flop.</t>
+        </is>
+      </c>
+      <c r="S73" s="48" t="inlineStr">
+        <is>
+          <t>Żółty o zielonym odcieniu, z zielonym flopem. Chłodna, blada żółć — rozjaśnia w stronę zieleni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="48" customHeight="1">
       <c r="A74" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-961</t>
@@ -35067,7 +37341,7 @@
       </c>
       <c r="J74" s="48" t="inlineStr">
         <is>
-          <t>Clean blue tone violet, darker flop than</t>
+          <t>Czysty fiolet o niebieskim tonie, ciemniejszy flop niż P425-921. Chłodna magenta, głębszy cień.</t>
         </is>
       </c>
       <c r="K74" s="48" t="inlineStr">
@@ -35101,8 +37375,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="36" customHeight="1">
+      <c r="R74" s="48" t="inlineStr">
+        <is>
+          <t>Clean blue tone violet, darker flop than P425-921.</t>
+        </is>
+      </c>
+      <c r="S74" s="48" t="inlineStr">
+        <is>
+          <t>Czysty fiolet o niebieskim tonie, ciemniejszy flop niż P425-921. Chłodna magenta, głębszy cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="48" customHeight="1">
       <c r="A75" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-967</t>
@@ -35133,7 +37417,7 @@
       </c>
       <c r="G75" s="48" t="inlineStr">
         <is>
-          <t>HS Deep Angle Black 2 =====</t>
+          <t>HS Deep Angle Black</t>
         </is>
       </c>
       <c r="H75" s="48" t="inlineStr">
@@ -35143,12 +37427,12 @@
       </c>
       <c r="I75" s="48" t="inlineStr">
         <is>
-          <t>HS Deep Angle Black 2 =====</t>
+          <t>HS Deep Angle Black</t>
         </is>
       </c>
       <c r="J75" s="48" t="inlineStr">
         <is>
-          <t>Yellow-shade black, darkest flop.</t>
+          <t>Czerń o żółtym odcieniu, najciemniejszy flop. Najgłębszy cień spośród czerni 2K — ściemia kąt duży.</t>
         </is>
       </c>
       <c r="K75" s="48" t="inlineStr">
@@ -35182,8 +37466,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="36" customHeight="1">
+      <c r="R75" s="48" t="inlineStr">
+        <is>
+          <t>Yellow-shade black, darkest flop.</t>
+        </is>
+      </c>
+      <c r="S75" s="48" t="inlineStr">
+        <is>
+          <t>Czerń o żółtym odcieniu, najciemniejszy flop. Najgłębszy cień spośród czerni 2K — ściemia kąt duży.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="48" customHeight="1">
       <c r="A76" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-972</t>
@@ -35229,7 +37523,7 @@
       </c>
       <c r="J76" s="48" t="inlineStr">
         <is>
-          <t>Bright orange used primarily in solid colours. Cleaner than P420-982 and P420-983.</t>
+          <t>Jasna pomarańcz, głównie kolory solid. Czystsza niż P420-982 i P420-983.</t>
         </is>
       </c>
       <c r="K76" s="48" t="inlineStr">
@@ -35263,8 +37557,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="36" customHeight="1">
+      <c r="R76" s="48" t="inlineStr">
+        <is>
+          <t>Bright orange used primarily in solid colours. Cleaner than P420-982 and P420-983.</t>
+        </is>
+      </c>
+      <c r="S76" s="48" t="inlineStr">
+        <is>
+          <t>Jasna pomarańcz, głównie kolory solid. Czystsza niż P420-982 i P420-983.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="48" customHeight="1">
       <c r="A77" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-973</t>
@@ -35295,7 +37599,7 @@
       </c>
       <c r="G77" s="48" t="inlineStr">
         <is>
-          <t>HS Bright Orange Red shade orange.</t>
+          <t>HS Bright Orange</t>
         </is>
       </c>
       <c r="H77" s="48" t="inlineStr">
@@ -35305,10 +37609,14 @@
       </c>
       <c r="I77" s="48" t="inlineStr">
         <is>
-          <t>HS Bright Orange Red shade orange.</t>
-        </is>
-      </c>
-      <c r="J77" s="48" t="inlineStr"/>
+          <t>HS Bright Orange</t>
+        </is>
+      </c>
+      <c r="J77" s="48" t="inlineStr">
+        <is>
+          <t>Pomarańcz o czerwonym odcieniu. Ciepła, czerwona pomarańcz do korekty tonu.</t>
+        </is>
+      </c>
       <c r="K77" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -35340,8 +37648,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="36" customHeight="1">
+      <c r="R77" s="48" t="inlineStr">
+        <is>
+          <t>Red shade orange.</t>
+        </is>
+      </c>
+      <c r="S77" s="48" t="inlineStr">
+        <is>
+          <t>Pomarańcz o czerwonym odcieniu. Ciepła, czerwona pomarańcz do korekty tonu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-976</t>
@@ -35385,7 +37703,11 @@
           <t>HS Red Violet</t>
         </is>
       </c>
-      <c r="J78" s="48" t="inlineStr"/>
+      <c r="J78" s="48" t="inlineStr">
+        <is>
+          <t>Fiolet czerwony HS. Pełna moc odpowiednika RT Burgundy (P420-960RT).</t>
+        </is>
+      </c>
       <c r="K78" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -35417,8 +37739,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="36" customHeight="1">
+      <c r="R78" s="48" t="inlineStr">
+        <is>
+          <t>Red violet HS. Full-strength counterpart of RT Burgundy P420-960RT.</t>
+        </is>
+      </c>
+      <c r="S78" s="48" t="inlineStr">
+        <is>
+          <t>Fiolet czerwony HS. Pełna moc odpowiednika RT Burgundy (P420-960RT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
       <c r="A79" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-980</t>
@@ -35449,7 +37781,7 @@
       </c>
       <c r="G79" s="48" t="inlineStr">
         <is>
-          <t>HS Speed Red colours above 20%.</t>
+          <t>HS Speed Red</t>
         </is>
       </c>
       <c r="H79" s="48" t="inlineStr">
@@ -35459,12 +37791,12 @@
       </c>
       <c r="I79" s="48" t="inlineStr">
         <is>
-          <t>HS Speed Red colours above 20%.</t>
+          <t>HS Speed Red</t>
         </is>
       </c>
       <c r="J79" s="48" t="inlineStr">
         <is>
-          <t>Bright clean red, used primarily in solid</t>
+          <t>Jasna, czysta czerwień — głównie kolory solid, zwykle powyżej 20% udziału. Silna, czysta czerwień solid.</t>
         </is>
       </c>
       <c r="K79" s="48" t="inlineStr">
@@ -35498,8 +37830,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
+      <c r="R79" s="48" t="inlineStr">
+        <is>
+          <t>Bright clean red, used primarily in solid colours above 20%.</t>
+        </is>
+      </c>
+      <c r="S79" s="48" t="inlineStr">
+        <is>
+          <t>Jasna, czysta czerwień — głównie kolory solid, zwykle powyżej 20% udziału. Silna, czysta czerwień solid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
       <c r="A80" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P429-981</t>
@@ -35538,8 +37880,16 @@
           <t>2K Transparent Gold</t>
         </is>
       </c>
-      <c r="I80" s="48" t="inlineStr"/>
-      <c r="J80" s="48" t="inlineStr"/>
+      <c r="I80" s="48" t="inlineStr">
+        <is>
+          <t>Transparent Gold</t>
+        </is>
+      </c>
+      <c r="J80" s="48" t="inlineStr">
+        <is>
+          <t>Transparentne złoto. Dodaje złoty ton bez silnego krycia; ociepla światło, słabiej buduje flop.</t>
+        </is>
+      </c>
       <c r="K80" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -35571,8 +37921,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="36" customHeight="1">
+      <c r="R80" s="48" t="inlineStr">
+        <is>
+          <t>Transparent gold toner.</t>
+        </is>
+      </c>
+      <c r="S80" s="48" t="inlineStr">
+        <is>
+          <t>Transparentne złoto. Dodaje złoty ton bez silnego krycia; ociepla światło, słabiej buduje flop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="48" customHeight="1">
       <c r="A81" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR10</t>
@@ -35618,7 +37978,7 @@
       </c>
       <c r="J81" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright white effect, coarser appearance and brighter than P426-PP05.</t>
+          <t>Iskrzący, jasny biały efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP05.</t>
         </is>
       </c>
       <c r="K81" s="48" t="inlineStr">
@@ -35652,8 +38012,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="36" customHeight="1">
+      <c r="R81" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright white effect, coarser appearance and brighter than P426-PP05.</t>
+        </is>
+      </c>
+      <c r="S81" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny biały efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="48" customHeight="1">
       <c r="A82" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR11</t>
@@ -35699,7 +38069,7 @@
       </c>
       <c r="J82" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright gold effect, coarser appearance and brighter than P426-PP09.</t>
+          <t>Iskrzący, jasny złoty efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP09.</t>
         </is>
       </c>
       <c r="K82" s="48" t="inlineStr">
@@ -35733,8 +38103,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="36" customHeight="1">
+      <c r="R82" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright gold effect, coarser appearance and brighter than P426-PP09.</t>
+        </is>
+      </c>
+      <c r="S82" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny złoty efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="48" customHeight="1">
       <c r="A83" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR12</t>
@@ -35780,7 +38160,7 @@
       </c>
       <c r="J83" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright red effect, coarser appearance and brighter than P426-PP08.</t>
+          <t>Iskrzący, jasny czerwony efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP08.</t>
         </is>
       </c>
       <c r="K83" s="48" t="inlineStr">
@@ -35814,8 +38194,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
+      <c r="R83" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright red effect, coarser appearance and brighter than P426-PP08.</t>
+        </is>
+      </c>
+      <c r="S83" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny czerwony efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="48" customHeight="1">
       <c r="A84" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR13</t>
@@ -35861,7 +38251,7 @@
       </c>
       <c r="J84" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright blue effect, coarser appearance and brighter than P426-PP07.</t>
+          <t>Iskrzący, jasny niebieski efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP07.</t>
         </is>
       </c>
       <c r="K84" s="48" t="inlineStr">
@@ -35895,8 +38285,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="85" ht="36" customHeight="1">
+      <c r="R84" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright blue effect, coarser appearance and brighter than P426-PP07.</t>
+        </is>
+      </c>
+      <c r="S84" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny niebieski efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="48" customHeight="1">
       <c r="A85" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR14</t>
@@ -35942,7 +38342,7 @@
       </c>
       <c r="J85" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright green effect, coarser appearance and brighter than P426-PP65.</t>
+          <t>Iskrzący, jasny zielony efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP65.</t>
         </is>
       </c>
       <c r="K85" s="48" t="inlineStr">
@@ -35976,8 +38376,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="36" customHeight="1">
+      <c r="R85" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright green effect, coarser appearance and brighter than P426-PP65.</t>
+        </is>
+      </c>
+      <c r="S85" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny zielony efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP65.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="48" customHeight="1">
       <c r="A86" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR15</t>
@@ -36023,7 +38433,7 @@
       </c>
       <c r="J86" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright magenta red effect, coarser appearance and brighter than P426-PP61.</t>
+          <t>Iskrzący, jasny magenta-czerwony efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP61.</t>
         </is>
       </c>
       <c r="K86" s="48" t="inlineStr">
@@ -36057,8 +38467,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="87" ht="36" customHeight="1">
+      <c r="R86" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright magenta red effect, coarser appearance and brighter than P426-PP61.</t>
+        </is>
+      </c>
+      <c r="S86" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny magenta-czerwony efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="48" customHeight="1">
       <c r="A87" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR16</t>
@@ -36104,7 +38524,7 @@
       </c>
       <c r="J87" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright copper effect, coarser appearance and brighter than P426-PP10.</t>
+          <t>Iskrzący, jasny miedziany efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP10.</t>
         </is>
       </c>
       <c r="K87" s="48" t="inlineStr">
@@ -36138,8 +38558,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
+      <c r="R87" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright copper effect, coarser appearance and brighter than P426-PP10.</t>
+        </is>
+      </c>
+      <c r="S87" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny miedziany efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="48" customHeight="1">
       <c r="A88" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR17</t>
@@ -36170,7 +38600,7 @@
       </c>
       <c r="G88" s="49" t="inlineStr">
         <is>
-          <t>Cosmic Turquoise flake pigment.</t>
+          <t>Cosmic Turquoise</t>
         </is>
       </c>
       <c r="H88" s="49" t="inlineStr">
@@ -36180,12 +38610,12 @@
       </c>
       <c r="I88" s="49" t="inlineStr">
         <is>
-          <t>Cosmic Turquoise flake pigment.</t>
+          <t>Cosmic Turquoise</t>
         </is>
       </c>
       <c r="J88" s="49" t="inlineStr">
         <is>
-          <t>Sparkle bright unique marine blue</t>
+          <t>Iskrzący, unikalny morski błękit (turkus) — płatek Xirallic o wyraźnej iskrze.</t>
         </is>
       </c>
       <c r="K88" s="49" t="inlineStr">
@@ -36223,8 +38653,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="89" ht="36" customHeight="1">
+      <c r="R88" s="49" t="inlineStr">
+        <is>
+          <t>Sparkle bright unique marine blue flake pigment.</t>
+        </is>
+      </c>
+      <c r="S88" s="49" t="inlineStr">
+        <is>
+          <t>Iskrzący, unikalny morski błękit (turkus) — płatek Xirallic o wyraźnej iskrze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="48" customHeight="1">
       <c r="A89" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P433-XR18</t>
@@ -36270,7 +38710,7 @@
       </c>
       <c r="J89" s="48" t="inlineStr">
         <is>
-          <t>Sparkle bright violet effect, coarser appearance and brighter than P426-PP64.</t>
+          <t>Iskrzący, jasny fioletowy efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP64.</t>
         </is>
       </c>
       <c r="K89" s="48" t="inlineStr">
@@ -36304,8 +38744,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="90" ht="36" customHeight="1">
+      <c r="R89" s="48" t="inlineStr">
+        <is>
+          <t>Sparkle bright violet effect, coarser appearance and brighter than P426-PP64.</t>
+        </is>
+      </c>
+      <c r="S89" s="48" t="inlineStr">
+        <is>
+          <t>Iskrzący, jasny fioletowy efekt Xirallic; grubsze ziarno i jaśniejszy niż P426-PP64.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="48" customHeight="1">
       <c r="A90" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P434-CS32</t>
@@ -36336,7 +38786,7 @@
       </c>
       <c r="G90" s="49" t="inlineStr">
         <is>
-          <t>Viola Fantasy unique violet to silver to green to blue colour</t>
+          <t>Viola Fantasy</t>
         </is>
       </c>
       <c r="H90" s="49" t="inlineStr">
@@ -36346,12 +38796,12 @@
       </c>
       <c r="I90" s="49" t="inlineStr">
         <is>
-          <t>Viola Fantasy unique violet to silver to green to blue colour</t>
+          <t>Viola Fantasy</t>
         </is>
       </c>
       <c r="J90" s="49" t="inlineStr">
         <is>
-          <t>Special effect white silica flake that creates a travel.</t>
+          <t>Efektowy biały płatek krzemionkowy Colorstream: unikalny travel fiolet → srebro → zieleń → błękit.</t>
         </is>
       </c>
       <c r="K90" s="49" t="inlineStr">
@@ -36389,8 +38839,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="91" ht="36" customHeight="1">
+      <c r="R90" s="49" t="inlineStr">
+        <is>
+          <t>Special effect white silica flake that creates a unique violet to silver to green to blue colour travel.</t>
+        </is>
+      </c>
+      <c r="S90" s="49" t="inlineStr">
+        <is>
+          <t>Efektowy biały płatek krzemionkowy Colorstream: unikalny travel fiolet → srebro → zieleń → błękit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="48" customHeight="1">
       <c r="A91" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P434-CS33</t>
@@ -36421,7 +38881,7 @@
       </c>
       <c r="G91" s="49" t="inlineStr">
         <is>
-          <t>Arctic Fire colour travel from subtle turquoise through</t>
+          <t>Arctic Fire</t>
         </is>
       </c>
       <c r="H91" s="49" t="inlineStr">
@@ -36431,12 +38891,12 @@
       </c>
       <c r="I91" s="49" t="inlineStr">
         <is>
-          <t>Arctic Fire colour travel from subtle turquoise through</t>
+          <t>Arctic Fire</t>
         </is>
       </c>
       <c r="J91" s="49" t="inlineStr">
         <is>
-          <t>Special effect silica flake that creates a unique brilliant silver to red.</t>
+          <t>Efektowy płatek krzemionkowy Colorstream: travel od subtelnego turkusu przez błyszczące srebro do czerwieni.</t>
         </is>
       </c>
       <c r="K91" s="49" t="inlineStr">
@@ -36474,8 +38934,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="92" ht="36" customHeight="1">
+      <c r="R91" s="49" t="inlineStr">
+        <is>
+          <t>Special effect silica flake that creates a unique colour travel from subtle turquoise through brilliant silver to red.</t>
+        </is>
+      </c>
+      <c r="S91" s="49" t="inlineStr">
+        <is>
+          <t>Efektowy płatek krzemionkowy Colorstream: travel od subtelnego turkusu przez błyszczące srebro do czerwieni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
       <c r="A92" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P434-CS34</t>
@@ -36506,7 +38976,7 @@
       </c>
       <c r="G92" s="49" t="inlineStr">
         <is>
-          <t>Tropic Sunrise colour travel from green to silver to reddish</t>
+          <t>Tropic Sunrise</t>
         </is>
       </c>
       <c r="H92" s="49" t="inlineStr">
@@ -36516,12 +38986,12 @@
       </c>
       <c r="I92" s="49" t="inlineStr">
         <is>
-          <t>Tropic Sunrise colour travel from green to silver to reddish</t>
+          <t>Tropic Sunrise</t>
         </is>
       </c>
       <c r="J92" s="49" t="inlineStr">
         <is>
-          <t>Special effect silica flake that creates a unique orange.</t>
+          <t>Efektowy płatek krzemionkowy Colorstream: travel zieleń → srebro → czerwonawa pomarańcz.</t>
         </is>
       </c>
       <c r="K92" s="49" t="inlineStr">
@@ -36559,8 +39029,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="93" ht="36" customHeight="1">
+      <c r="R92" s="49" t="inlineStr">
+        <is>
+          <t>Special effect silica flake that creates a unique colour travel from green to silver to reddish orange.</t>
+        </is>
+      </c>
+      <c r="S92" s="49" t="inlineStr">
+        <is>
+          <t>Efektowy płatek krzemionkowy Colorstream: travel zieleń → srebro → czerwonawa pomarańcz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
       <c r="A93" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P434-CS35</t>
@@ -36591,7 +39071,7 @@
       </c>
       <c r="G93" s="49" t="inlineStr">
         <is>
-          <t>Lapis Sunlight colour travel from gold to green to blue.</t>
+          <t>Lapis Sunlight</t>
         </is>
       </c>
       <c r="H93" s="49" t="inlineStr">
@@ -36601,12 +39081,12 @@
       </c>
       <c r="I93" s="49" t="inlineStr">
         <is>
-          <t>Lapis Sunlight colour travel from gold to green to blue.</t>
+          <t>Lapis Sunlight</t>
         </is>
       </c>
       <c r="J93" s="49" t="inlineStr">
         <is>
-          <t>Special effect silica flake that creates a unique</t>
+          <t>Efektowy płatek krzemionkowy Colorstream: travel złoto → zieleń → błękit.</t>
         </is>
       </c>
       <c r="K93" s="49" t="inlineStr">
@@ -36644,8 +39124,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="36" customHeight="1">
+      <c r="R93" s="49" t="inlineStr">
+        <is>
+          <t>Special effect silica flake that creates a unique colour travel from gold to green to blue.</t>
+        </is>
+      </c>
+      <c r="S93" s="49" t="inlineStr">
+        <is>
+          <t>Efektowy płatek krzemionkowy Colorstream: travel złoto → zieleń → błękit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
       <c r="A94" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P435-GF37</t>
@@ -36691,7 +39181,7 @@
       </c>
       <c r="J94" s="48" t="inlineStr">
         <is>
-          <t>Silver metal-coated glass flakes, used to create bright colours with intense sparkle and flare. The effect is particularly evident in bright sunlight.</t>
+          <t>Srebrne płatki szkła pokryte metalem — jasne kolory z intensywną iskrą i flare. Efekt szczególnie widoczny w ostrym słońcu.</t>
         </is>
       </c>
       <c r="K94" s="48" t="inlineStr">
@@ -36725,8 +39215,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="95" ht="36" customHeight="1">
+      <c r="R94" s="48" t="inlineStr">
+        <is>
+          <t>Silver metal-coated glass flakes, used to create bright colours with intense sparkle and flare. The effect is particularly evident in bright sunlight.</t>
+        </is>
+      </c>
+      <c r="S94" s="48" t="inlineStr">
+        <is>
+          <t>Srebrne płatki szkła pokryte metalem — jasne kolory z intensywną iskrą i flare. Efekt szczególnie widoczny w ostrym słońcu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="48" customHeight="1">
       <c r="A95" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX20</t>
@@ -36765,8 +39265,16 @@
           <t>2K CHROMAFLAIR CYAN TO PURPLE</t>
         </is>
       </c>
-      <c r="I95" s="48" t="inlineStr"/>
-      <c r="J95" s="48" t="inlineStr"/>
+      <c r="I95" s="48" t="inlineStr">
+        <is>
+          <t>CHROMAFLAIR CYAN TO PURPLE</t>
+        </is>
+      </c>
+      <c r="J95" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel cyjan → fiolet. Dodaje kątowe przesunięcie koloru, nie krycie.</t>
+        </is>
+      </c>
       <c r="K95" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -36798,8 +39306,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="96" ht="36" customHeight="1">
+      <c r="R95" s="48" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from cyan through purple.</t>
+        </is>
+      </c>
+      <c r="S95" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel cyjan → fiolet. Dodaje kątowe przesunięcie koloru, nie krycie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="48" customHeight="1">
       <c r="A96" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX21</t>
@@ -36838,8 +39356,16 @@
           <t>2K CHROMAFLAIR SILVER TO GREEN</t>
         </is>
       </c>
-      <c r="I96" s="48" t="inlineStr"/>
-      <c r="J96" s="48" t="inlineStr"/>
+      <c r="I96" s="48" t="inlineStr">
+        <is>
+          <t>CHROMAFLAIR SILVER TO GREEN</t>
+        </is>
+      </c>
+      <c r="J96" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel srebro → zieleń.</t>
+        </is>
+      </c>
       <c r="K96" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -36871,8 +39397,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="97" ht="36" customHeight="1">
+      <c r="R96" s="48" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from silver through green.</t>
+        </is>
+      </c>
+      <c r="S96" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel srebro → zieleń.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
       <c r="A97" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX22</t>
@@ -36911,8 +39447,16 @@
           <t>2K CHROMAFLAIR GREEN TO PURPLE</t>
         </is>
       </c>
-      <c r="I97" s="48" t="inlineStr"/>
-      <c r="J97" s="48" t="inlineStr"/>
+      <c r="I97" s="48" t="inlineStr">
+        <is>
+          <t>CHROMAFLAIR GREEN TO PURPLE</t>
+        </is>
+      </c>
+      <c r="J97" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel zieleń → fiolet.</t>
+        </is>
+      </c>
       <c r="K97" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -36944,8 +39488,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="98" ht="36" customHeight="1">
+      <c r="R97" s="48" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from green through purple.</t>
+        </is>
+      </c>
+      <c r="S97" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel zieleń → fiolet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
       <c r="A98" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX23</t>
@@ -36984,8 +39538,16 @@
           <t>2K CHROMAFLAIR BLUE TO RED</t>
         </is>
       </c>
-      <c r="I98" s="48" t="inlineStr"/>
-      <c r="J98" s="48" t="inlineStr"/>
+      <c r="I98" s="48" t="inlineStr">
+        <is>
+          <t>CHROMAFLAIR BLUE TO RED</t>
+        </is>
+      </c>
+      <c r="J98" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel błękit → czerwień.</t>
+        </is>
+      </c>
       <c r="K98" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -37017,8 +39579,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
+      <c r="R98" s="48" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from blue through red.</t>
+        </is>
+      </c>
+      <c r="S98" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel błękit → czerwień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="48" customHeight="1">
       <c r="A99" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX24</t>
@@ -37057,8 +39629,16 @@
           <t>2K CHROMAFLAIR MAGENTA TO GOLD</t>
         </is>
       </c>
-      <c r="I99" s="48" t="inlineStr"/>
-      <c r="J99" s="48" t="inlineStr"/>
+      <c r="I99" s="48" t="inlineStr">
+        <is>
+          <t>CHROMAFLAIR MAGENTA TO GOLD</t>
+        </is>
+      </c>
+      <c r="J99" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel magenta → złoto.</t>
+        </is>
+      </c>
       <c r="K99" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -37090,8 +39670,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="100" ht="36" customHeight="1">
+      <c r="R99" s="48" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from magenta through gold.</t>
+        </is>
+      </c>
+      <c r="S99" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel magenta → złoto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="48" customHeight="1">
       <c r="A100" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX25</t>
@@ -37130,8 +39720,16 @@
           <t>2K CHROMAFLAIR GOLD TO SILVER</t>
         </is>
       </c>
-      <c r="I100" s="48" t="inlineStr"/>
-      <c r="J100" s="48" t="inlineStr"/>
+      <c r="I100" s="48" t="inlineStr">
+        <is>
+          <t>CHROMAFLAIR GOLD TO SILVER</t>
+        </is>
+      </c>
+      <c r="J100" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel złoto → srebro.</t>
+        </is>
+      </c>
       <c r="K100" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -37163,8 +39761,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="101" ht="36" customHeight="1">
+      <c r="R100" s="48" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from gold through silver.</t>
+        </is>
+      </c>
+      <c r="S100" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel złoto → srebro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
       <c r="A101" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX26</t>
@@ -37203,8 +39811,16 @@
           <t>2K CHROMAFLAIR RED TO GOLD</t>
         </is>
       </c>
-      <c r="I101" s="48" t="inlineStr"/>
-      <c r="J101" s="48" t="inlineStr"/>
+      <c r="I101" s="48" t="inlineStr">
+        <is>
+          <t>CHROMAFLAIR RED TO GOLD</t>
+        </is>
+      </c>
+      <c r="J101" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel czerwień → złoto.</t>
+        </is>
+      </c>
       <c r="K101" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -37236,8 +39852,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="102" ht="36" customHeight="1">
+      <c r="R101" s="48" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from red through gold.</t>
+        </is>
+      </c>
+      <c r="S101" s="48" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę (ChromaFlair): travel czerwień → złoto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="48" customHeight="1">
       <c r="A102" s="49" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-FX51</t>
@@ -37268,7 +39894,7 @@
       </c>
       <c r="G102" s="49" t="inlineStr">
         <is>
-          <t>Silver Flair intense light source.</t>
+          <t>Silver Flair</t>
         </is>
       </c>
       <c r="H102" s="49" t="inlineStr">
@@ -37278,12 +39904,12 @@
       </c>
       <c r="I102" s="49" t="inlineStr">
         <is>
-          <t>Silver Flair intense light source.</t>
+          <t>Silver Flair</t>
         </is>
       </c>
       <c r="J102" s="49" t="inlineStr">
         <is>
-          <t>Exhibits a unique rainbow multi coloured effect, particularly in silver colours under</t>
+          <t>Tęczowy, wielobarwny efekt (rainbow), szczególnie w srebrnych kolorach przy intensywnym świetle.</t>
         </is>
       </c>
       <c r="K102" s="49" t="inlineStr">
@@ -37321,8 +39947,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="103" ht="36" customHeight="1">
+      <c r="R102" s="49" t="inlineStr">
+        <is>
+          <t>Exhibits a unique rainbow multi coloured effect, particularly in silver colours under intense light source.</t>
+        </is>
+      </c>
+      <c r="S102" s="49" t="inlineStr">
+        <is>
+          <t>Tęczowy, wielobarwny efekt (rainbow), szczególnie w srebrnych kolorach przy intensywnym świetle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="48" customHeight="1">
       <c r="A103" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P440-LM01</t>
@@ -37361,8 +39997,16 @@
           <t>2K LIQUID METAL SUPER FINE</t>
         </is>
       </c>
-      <c r="I103" s="48" t="inlineStr"/>
-      <c r="J103" s="48" t="inlineStr"/>
+      <c r="I103" s="48" t="inlineStr">
+        <is>
+          <t>LIQUID METAL SUPER FINE</t>
+        </is>
+      </c>
+      <c r="J103" s="48" t="inlineStr">
+        <is>
+          <t>Próżniowe płatki metalu (liquid metal) o efekcie stopionego metalu. Bardzo drobne ziarno, lustrzany połysk.</t>
+        </is>
+      </c>
       <c r="K103" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -37394,8 +40038,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="104" ht="36" customHeight="1">
+      <c r="R103" s="48" t="inlineStr">
+        <is>
+          <t>Vacuumized metal flakes with a unique optical effect similar to a molten metal appearance.</t>
+        </is>
+      </c>
+      <c r="S103" s="48" t="inlineStr">
+        <is>
+          <t>Próżniowe płatki metalu (liquid metal) o efekcie stopionego metalu. Bardzo drobne ziarno, lustrzany połysk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="48" customHeight="1">
       <c r="A104" s="48" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P450-EC50</t>
@@ -37434,8 +40088,16 @@
           <t>BRILLIANT RED</t>
         </is>
       </c>
-      <c r="I104" s="48" t="inlineStr"/>
-      <c r="J104" s="48" t="inlineStr"/>
+      <c r="I104" s="48" t="inlineStr">
+        <is>
+          <t>BRILLIANT RED</t>
+        </is>
+      </c>
+      <c r="J104" s="48" t="inlineStr">
+        <is>
+          <t>Jaskrawa czerwień (toner EC). Dodaje czysty, intensywny czerwony ton.</t>
+        </is>
+      </c>
       <c r="K104" s="48" t="inlineStr">
         <is>
           <t>g</t>
@@ -37467,8 +40129,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="105" ht="36" customHeight="1">
+      <c r="R104" s="48" t="inlineStr">
+        <is>
+          <t>Brilliant red effect / toner.</t>
+        </is>
+      </c>
+      <c r="S104" s="48" t="inlineStr">
+        <is>
+          <t>Jaskrawa czerwień (toner EC). Dodaje czysty, intensywny czerwony ton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="48" customHeight="1">
       <c r="A105" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P420-982</t>
@@ -37504,46 +40176,56 @@
       </c>
       <c r="J105" s="50" t="inlineStr">
         <is>
+          <t>Transparentny tlenek żółty z ciemniejszym flopem niż P420-983. Żółć tlenkowa bez silnego krycia, pogłębia cień.</t>
+        </is>
+      </c>
+      <c r="K105" s="50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L105" s="50" t="inlineStr">
+        <is>
+          <t>Toner</t>
+        </is>
+      </c>
+      <c r="M105" s="50" t="inlineStr">
+        <is>
+          <t>DODANY Z PDF</t>
+        </is>
+      </c>
+      <c r="N105" s="50" t="inlineStr">
+        <is>
+          <t>Kod występuje w przewodniku dobarwiania, brak w ODS</t>
+        </is>
+      </c>
+      <c r="O105" s="50" t="inlineStr">
+        <is>
+          <t>PDF_AUTOCOLOR</t>
+        </is>
+      </c>
+      <c r="P105" s="50" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="Q105" s="50" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="R105" s="50" t="inlineStr">
+        <is>
           <t>Transparent yellow oxide with a darker flop than P420-983.</t>
         </is>
       </c>
-      <c r="K105" s="50" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L105" s="50" t="inlineStr">
-        <is>
-          <t>Toner</t>
-        </is>
-      </c>
-      <c r="M105" s="50" t="inlineStr">
-        <is>
-          <t>DODANY Z PDF</t>
-        </is>
-      </c>
-      <c r="N105" s="50" t="inlineStr">
-        <is>
-          <t>Kod występuje w przewodniku dobarwiania, brak w ODS</t>
-        </is>
-      </c>
-      <c r="O105" s="50" t="inlineStr">
-        <is>
-          <t>PDF_AUTOCOLOR</t>
-        </is>
-      </c>
-      <c r="P105" s="50" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="Q105" s="50" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="36" customHeight="1">
+      <c r="S105" s="50" t="inlineStr">
+        <is>
+          <t>Transparentny tlenek żółty z ciemniejszym flopem niż P420-983. Żółć tlenkowa bez silnego krycia, pogłębia cień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="48" customHeight="1">
       <c r="A106" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4370</t>
@@ -37568,18 +40250,18 @@
       <c r="F106" s="50" t="inlineStr"/>
       <c r="G106" s="50" t="inlineStr">
         <is>
-          <t>Super Fine Liquid Metal that have a unique optical</t>
+          <t>Super Fine Liquid Metal</t>
         </is>
       </c>
       <c r="H106" s="50" t="inlineStr"/>
       <c r="I106" s="50" t="inlineStr">
         <is>
-          <t>Super Fine Liquid Metal that have a unique optical</t>
+          <t>Super Fine Liquid Metal</t>
         </is>
       </c>
       <c r="J106" s="50" t="inlineStr">
         <is>
-          <t>Vacuumized metal flakes effect similar to a molten metal appearance.</t>
+          <t>Próżniowe płatki metalu — unikalny efekt optyczny jak stopiony metal. Bardzo drobne ziarno, lustrzany połysk.</t>
         </is>
       </c>
       <c r="K106" s="50" t="inlineStr">
@@ -37617,8 +40299,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="107" ht="36" customHeight="1">
+      <c r="R106" s="50" t="inlineStr">
+        <is>
+          <t>Vacuumized metal flakes that have a unique optical effect similar to a molten metal appearance.</t>
+        </is>
+      </c>
+      <c r="S106" s="50" t="inlineStr">
+        <is>
+          <t>Próżniowe płatki metalu — unikalny efekt optyczny jak stopiony metal. Bardzo drobne ziarno, lustrzany połysk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="48" customHeight="1">
       <c r="A107" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P426-HE07</t>
@@ -37643,16 +40335,20 @@
       <c r="F107" s="50" t="inlineStr"/>
       <c r="G107" s="50" t="inlineStr">
         <is>
-          <t>Blue Flash Organic blue coloured aluminium flake.</t>
+          <t>Blue Flash</t>
         </is>
       </c>
       <c r="H107" s="50" t="inlineStr"/>
       <c r="I107" s="50" t="inlineStr">
         <is>
-          <t>Blue Flash Organic blue coloured aluminium flake.</t>
-        </is>
-      </c>
-      <c r="J107" s="50" t="inlineStr"/>
+          <t>Blue Flash</t>
+        </is>
+      </c>
+      <c r="J107" s="50" t="inlineStr">
+        <is>
+          <t>Organiczny niebieski płatek aluminiowy. Barwione ziarno — niebieski błysk metaliku.</t>
+        </is>
+      </c>
       <c r="K107" s="50" t="inlineStr">
         <is>
           <t>g</t>
@@ -37688,8 +40384,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="108" ht="36" customHeight="1">
+      <c r="R107" s="50" t="inlineStr">
+        <is>
+          <t>Organic blue coloured aluminium flake.</t>
+        </is>
+      </c>
+      <c r="S107" s="50" t="inlineStr">
+        <is>
+          <t>Organiczny niebieski płatek aluminiowy. Barwione ziarno — niebieski błysk metaliku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="48" customHeight="1">
       <c r="A108" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|P434-CS31</t>
@@ -37714,18 +40420,18 @@
       <c r="F108" s="50" t="inlineStr"/>
       <c r="G108" s="50" t="inlineStr">
         <is>
-          <t>Autumn Mystery a unique red to gold to bronze to green colour</t>
+          <t>Autumn Mystery</t>
         </is>
       </c>
       <c r="H108" s="50" t="inlineStr"/>
       <c r="I108" s="50" t="inlineStr">
         <is>
-          <t>Autumn Mystery a unique red to gold to bronze to green colour</t>
+          <t>Autumn Mystery</t>
         </is>
       </c>
       <c r="J108" s="50" t="inlineStr">
         <is>
-          <t>Special effect orange silica flake that creates travel.</t>
+          <t>Efektowy pomarańczowy płatek krzemionkowy Colorstream: unikalny travel czerwony → złoty → brąz → zieleń.</t>
         </is>
       </c>
       <c r="K108" s="50" t="inlineStr">
@@ -37763,8 +40469,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="109" ht="36" customHeight="1">
+      <c r="R108" s="50" t="inlineStr">
+        <is>
+          <t>Special effect orange silica flake that creates a unique red to gold to bronze to green colour travel.</t>
+        </is>
+      </c>
+      <c r="S108" s="50" t="inlineStr">
+        <is>
+          <t>Efektowy pomarańczowy płatek krzemionkowy Colorstream: unikalny travel czerwony → złoty → brąz → zieleń.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="48" customHeight="1">
       <c r="A109" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4987</t>
@@ -37789,18 +40505,18 @@
       <c r="F109" s="50" t="inlineStr"/>
       <c r="G109" s="50" t="inlineStr">
         <is>
-          <t>Cyan to Purple through purple.</t>
+          <t>Cyan to Purple</t>
         </is>
       </c>
       <c r="H109" s="50" t="inlineStr"/>
       <c r="I109" s="50" t="inlineStr">
         <is>
-          <t>Cyan to Purple through purple.</t>
+          <t>Cyan to Purple</t>
         </is>
       </c>
       <c r="J109" s="50" t="inlineStr">
         <is>
-          <t>Colour shifting flake. Colour shifts from cyan</t>
+          <t>Płatek zmieniający barwę: travel cyjan → fiolet.</t>
         </is>
       </c>
       <c r="K109" s="50" t="inlineStr">
@@ -37838,8 +40554,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="110" ht="36" customHeight="1">
+      <c r="R109" s="50" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from cyan through purple.</t>
+        </is>
+      </c>
+      <c r="S109" s="50" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę: travel cyjan → fiolet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="48" customHeight="1">
       <c r="A110" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4988</t>
@@ -37864,18 +40590,18 @@
       <c r="F110" s="50" t="inlineStr"/>
       <c r="G110" s="50" t="inlineStr">
         <is>
-          <t>Silver to Green through green.</t>
+          <t>Silver to Green</t>
         </is>
       </c>
       <c r="H110" s="50" t="inlineStr"/>
       <c r="I110" s="50" t="inlineStr">
         <is>
-          <t>Silver to Green through green.</t>
+          <t>Silver to Green</t>
         </is>
       </c>
       <c r="J110" s="50" t="inlineStr">
         <is>
-          <t>Colour shifting flake. Colour shifts from silver</t>
+          <t>Płatek zmieniający barwę: travel srebro → zieleń.</t>
         </is>
       </c>
       <c r="K110" s="50" t="inlineStr">
@@ -37913,8 +40639,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="111" ht="36" customHeight="1">
+      <c r="R110" s="50" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from silver through green.</t>
+        </is>
+      </c>
+      <c r="S110" s="50" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę: travel srebro → zieleń.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="48" customHeight="1">
       <c r="A111" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4989</t>
@@ -37939,18 +40675,18 @@
       <c r="F111" s="50" t="inlineStr"/>
       <c r="G111" s="50" t="inlineStr">
         <is>
-          <t>Green to Purple through purple.</t>
+          <t>Green to Purple</t>
         </is>
       </c>
       <c r="H111" s="50" t="inlineStr"/>
       <c r="I111" s="50" t="inlineStr">
         <is>
-          <t>Green to Purple through purple.</t>
+          <t>Green to Purple</t>
         </is>
       </c>
       <c r="J111" s="50" t="inlineStr">
         <is>
-          <t>Colour shifting flake. Colour shifts from green</t>
+          <t>Płatek zmieniający barwę: travel zieleń → fiolet.</t>
         </is>
       </c>
       <c r="K111" s="50" t="inlineStr">
@@ -37988,8 +40724,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="112" ht="36" customHeight="1">
+      <c r="R111" s="50" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from green through purple.</t>
+        </is>
+      </c>
+      <c r="S111" s="50" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę: travel zieleń → fiolet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="48" customHeight="1">
       <c r="A112" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4990</t>
@@ -38014,18 +40760,18 @@
       <c r="F112" s="50" t="inlineStr"/>
       <c r="G112" s="50" t="inlineStr">
         <is>
-          <t>Blue to Red through red.</t>
+          <t>Blue to Red</t>
         </is>
       </c>
       <c r="H112" s="50" t="inlineStr"/>
       <c r="I112" s="50" t="inlineStr">
         <is>
-          <t>Blue to Red through red.</t>
+          <t>Blue to Red</t>
         </is>
       </c>
       <c r="J112" s="50" t="inlineStr">
         <is>
-          <t>Colour shifting flake. Colour shifts from blue</t>
+          <t>Płatek zmieniający barwę: travel błękit → czerwień.</t>
         </is>
       </c>
       <c r="K112" s="50" t="inlineStr">
@@ -38063,8 +40809,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="113" ht="36" customHeight="1">
+      <c r="R112" s="50" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from blue through red.</t>
+        </is>
+      </c>
+      <c r="S112" s="50" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę: travel błękit → czerwień.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="48" customHeight="1">
       <c r="A113" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4991</t>
@@ -38089,18 +40845,18 @@
       <c r="F113" s="50" t="inlineStr"/>
       <c r="G113" s="50" t="inlineStr">
         <is>
-          <t>Magenta to Gold magenta through gold.</t>
+          <t>Magenta to Gold</t>
         </is>
       </c>
       <c r="H113" s="50" t="inlineStr"/>
       <c r="I113" s="50" t="inlineStr">
         <is>
-          <t>Magenta to Gold magenta through gold.</t>
+          <t>Magenta to Gold</t>
         </is>
       </c>
       <c r="J113" s="50" t="inlineStr">
         <is>
-          <t>Colour shifting flake. Colour shifts from</t>
+          <t>Płatek zmieniający barwę: travel magenta → złoto.</t>
         </is>
       </c>
       <c r="K113" s="50" t="inlineStr">
@@ -38138,8 +40894,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="114" ht="36" customHeight="1">
+      <c r="R113" s="50" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from magenta through gold.</t>
+        </is>
+      </c>
+      <c r="S113" s="50" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę: travel magenta → złoto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="48" customHeight="1">
       <c r="A114" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4994</t>
@@ -38164,18 +40930,18 @@
       <c r="F114" s="50" t="inlineStr"/>
       <c r="G114" s="50" t="inlineStr">
         <is>
-          <t>Gold to Silver through silver.</t>
+          <t>Gold to Silver</t>
         </is>
       </c>
       <c r="H114" s="50" t="inlineStr"/>
       <c r="I114" s="50" t="inlineStr">
         <is>
-          <t>Gold to Silver through silver.</t>
+          <t>Gold to Silver</t>
         </is>
       </c>
       <c r="J114" s="50" t="inlineStr">
         <is>
-          <t>Colour shifting flake. Colour shifts from gold</t>
+          <t>Płatek zmieniający barwę: travel złoto → srebro.</t>
         </is>
       </c>
       <c r="K114" s="50" t="inlineStr">
@@ -38213,8 +40979,18 @@
           <t>NIE</t>
         </is>
       </c>
-    </row>
-    <row r="115" ht="36" customHeight="1">
+      <c r="R114" s="50" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from gold through silver.</t>
+        </is>
+      </c>
+      <c r="S114" s="50" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę: travel złoto → srebro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="48" customHeight="1">
       <c r="A115" s="50" t="inlineStr">
         <is>
           <t>AUTOCOLOR|VM4995</t>
@@ -38239,18 +41015,18 @@
       <c r="F115" s="50" t="inlineStr"/>
       <c r="G115" s="50" t="inlineStr">
         <is>
-          <t>Red to Gold through gold. Yellow, Green, Blue,</t>
+          <t>Red to Gold</t>
         </is>
       </c>
       <c r="H115" s="50" t="inlineStr"/>
       <c r="I115" s="50" t="inlineStr">
         <is>
-          <t>Red to Gold through gold. Yellow, Green, Blue,</t>
+          <t>Red to Gold</t>
         </is>
       </c>
       <c r="J115" s="50" t="inlineStr">
         <is>
-          <t>Colour shifting flake. Colour shifts from red Violet, Red, etc. Colour viewing angle that is heavily influenced by metallic or pearl pigments in a formula. Colour viewing angle that is generally darker and influenced mostly by the conventional pigments in a metallic or pearlescent colour.</t>
+          <t>Płatek zmieniający barwę: travel czerwień → złoto.</t>
         </is>
       </c>
       <c r="K115" s="50" t="inlineStr">
@@ -38286,15 +41062,25 @@
       <c r="Q115" s="50" t="inlineStr">
         <is>
           <t>NIE</t>
+        </is>
+      </c>
+      <c r="R115" s="50" t="inlineStr">
+        <is>
+          <t>Colour shifting flake. Colour shifts from red through gold.</t>
+        </is>
+      </c>
+      <c r="S115" s="50" t="inlineStr">
+        <is>
+          <t>Płatek zmieniający barwę: travel czerwień → złoto.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
-  <autoFilter ref="A8:Q115"/>
+  <autoFilter ref="A8:S115"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38326,6 +41112,8 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -38356,7 +41144,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kopia robocza bazy. Oryginalne pliki ODS/PDF nie są zmieniane. Klucz = SYSTEM|NR_PIGMENTU.</t>
+          <t>Kopia robocza bazy. Oryginalne pliki ODS/PDF nie są zmieniane. Klucz = SYSTEM|NR_PIGMENTU. AUTOCOLOR: OPIS_DOBARWIANIA i OPIS_DZIALANIA_PL po polsku (tint chart); nazwy katalogowe EN. DUXONE: opisy z PDF PL.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -38464,8 +41252,18 @@
           <t>W_SZABLONIE_ODS</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+      <c r="R8" s="26" t="inlineStr">
+        <is>
+          <t>OPIS_EN</t>
+        </is>
+      </c>
+      <c r="S8" s="26" t="inlineStr">
+        <is>
+          <t>OPIS_DZIALANIA_PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5110</t>
@@ -38531,8 +41329,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+      <c r="R9" s="48" t="inlineStr"/>
+      <c r="S9" s="48" t="inlineStr"/>
+    </row>
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5111</t>
@@ -38605,8 +41405,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+      <c r="R10" s="48" t="inlineStr"/>
+      <c r="S10" s="48" t="inlineStr">
+        <is>
+          <t>Najmocniejszy i najbardziej nasycony czarny pigment
+DX5111 jest ciemniejszy patrząc „pod dużym kątem” (flop) niż DX5110
+Zamień DX5110 na DX5111: stężenie DX5110 x 2
+Ma niebieskie zabarwienie</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5121</t>
@@ -38679,8 +41488,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+      <c r="R11" s="48" t="inlineStr"/>
+      <c r="S11" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty pigment
+Najbardziej czerwonawy pigment z rodziny tlenków trans
+Ciemniejszy i bardziej zielonkawy odcień patrząc „pod dużym kątem” niż
+DX5126 oraz DX5122</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5122</t>
@@ -38752,8 +41570,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+      <c r="R12" s="48" t="inlineStr"/>
+      <c r="S12" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty pigment
+Czerwony patrząc „pod dużym kątem” i „na wprost”
+Czerwony w świetle żarówkowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5123</t>
@@ -38824,8 +41650,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+      <c r="R13" s="48" t="inlineStr"/>
+      <c r="S13" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty, czerwony komponent
+Taki sam jak DX5147, ale bardziej czerwony i bardziej niebieski</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5126</t>
@@ -38897,8 +41730,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+      <c r="R14" s="48" t="inlineStr"/>
+      <c r="S14" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty pigment
+Najbardziej żółtawy brąz
+Zielony/żółty odcień i jasny czerwony patrząc „pod dużym kątem”</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5130</t>
@@ -38964,8 +41805,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+      <c r="R15" s="48" t="inlineStr"/>
+      <c r="S15" s="48" t="inlineStr"/>
+    </row>
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5134</t>
@@ -39039,8 +41882,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+      <c r="R16" s="48" t="inlineStr"/>
+      <c r="S16" s="48" t="inlineStr">
+        <is>
+          <t>Jest używany w kolorach z efektem aby uzyskać kolor bardziej żołty patrząc „pod
+kątem” oraz bardziej niebieski i jaśniejszy patrząc „pod dużym kątem” (flop)
+Nie używać więcej niż 40% na wagę receptury by uniknąć problemów z
+trwałością
+Dodatki modyfikujące</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5136</t>
@@ -39171,8 +42024,75 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+      <c r="R17" s="48" t="inlineStr"/>
+      <c r="S17" s="48" t="inlineStr">
+        <is>
+          <t>Tylko do użycia w kolorach metalicznych i perłowych.
+Powoduje ściemnienie koloru przy paotrzeniu „pod kątem” (NRSP)
+Skutki uboczne:
+Spowoduje rozjaśnienie „pod dużym katem” i płatki aluminium staną
+się jaśniejsze.
+Ponieważ płatki aluminium staną się jaśniejsze, może istnieć
+konieczność udania się po drobniejsze aluminium.
+Maksimum 12% w całkowitej wadze formuły koloru
+Procedura aplikacji próbek kolorów Duxone® :
+1. Dokładnie wybrać odpowiedni kolor we właściwym miejscu na samochodzie, na
+prawidłowo oświetlanej powierzchni (w razie potrzeby mogą być użyte różne
+źródła światła, w celu osiągnięcia właściwego koloru).
+2. Użyj dokumentacji Variant Color Documentation korzystając z wzorca koloru,
+który musi być w dobrym stanie.
+3. Użyj pistoletu natryskowego przy właściwych ustawieniach (otwarcie i ciśnienie
+na wejściu do pistoletu)
+4. Należy ustawić pistolet natryskowy na całkowite otwarcie wydatku materiału w
+pistolecie i nie modyfikować kształtu natrysku po ustawieniu pistoletu (próbka
+koloru jest nakładana za pomocą pistoletu "całkowicie otwartego").
+1.2 Wykonywanie próbek kolorów
+Aplikacja &amp; Korygowanie
+1.2 Wykonywanie próbek kolorów
+Aplikacja &amp; Korygowanie
+Procedura aplikacji próbek kolorów Duxone® :
+5. Użyj próbki kolorów o minimalnych wymiarach10x15 cm (nie należy stosować
+mniejszych próbek, ponieważ są zbyt wrażliwe na wahania aplikacji).
+6. Nanoś bazę Duxone® na całym panelu (od góry do dołu, z użyciem 50%
+zakładki).
+7. Pozostawić do wyschnięcia. Przestrzegać zaleceń do suszenia lakieru
+bazowego, gdzie jest maksymalna temperatura = 40ºC.
+8. Przed oceną koloru należy nanieść lakier bezbarwny.
+1.2 Wykonywanie próbek kolorów
+Aplikacja &amp; Korygowanie
+Co nie powinno się zdarzyć przy wykonywaniu próbki koloru:
+1. Nie zmieniaj kształtu natrysku w czasie aplikacji koloru na próbkę.
+Inny kształt = inne ciśnienie = inna atomizacja (rozpylenie).
+2. Nie odmuchuj dla wysuszenia panelu przy użyciu pistoletu natryskowego,
+to może wywołać przepływ powietrza 13 m/s.
+3. Nie nagrzewaj panelu powyżej 40°C.
+4. Nie aplikuj lakieru bazowego zbyt mokro, lecz próbuj uzyskać mokry film
+na panelu w zgodzie z tym, co można uzyskać na samochodzie.
+15
+Jak obserwować kolor?
+Kolor a kąt patrzenia
+„na wprost” – źródło światła
+jest nad obserwatorem 45°
+„pod kątem” – źródło światła
+jest nad obserwatorem 15°
+„pod dużym kątem” – źródło
+światła jest za obserwatorem
+110°
+DX5…
+DX51.. → Komponenty Solid
+DX52.. → Komponenty Aluminiowe &amp; Perlowe
+DX53.. → Komponenty Xirallic
+DX01..
+ALUMINIOWE
+Komponenty Solid
+SOLID
+Komponenty perłowe XIRALLIC
+PERŁOWE &amp;
+XIRALLIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
       <c r="A18" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5161</t>
@@ -39244,8 +42164,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+      <c r="R18" s="48" t="inlineStr"/>
+      <c r="S18" s="48" t="inlineStr">
+        <is>
+          <t>Bardzo przezroczysty „pod kątem” (15°)
+Bardzo czysty pomarańczowy
+Ciemny pomarańczowy komponent w świetle żarówkowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5143</t>
@@ -39317,8 +42245,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+      <c r="R19" s="48" t="inlineStr"/>
+      <c r="S19" s="48" t="inlineStr">
+        <is>
+          <t>Używać w kolorach metalicznych tylko w razie konieczności
+Substytut dla pigmentów zawierających ołów
+Ciemny pomarańczowy komponent w świetle sodowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
       <c r="A20" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5144</t>
@@ -39391,8 +42327,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="R20" s="48" t="inlineStr"/>
+      <c r="S20" s="48" t="inlineStr">
+        <is>
+          <t>Nasycony, kryjący czerwony komponent
+Przeważnie używany w kolorach Solid
+Może być używany w małych ilościach w kolorach z efektem do wytworzenia
+czystego, jasnego czerwonego flopu (patrząc „pod duzym kątem”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5145</t>
@@ -39466,8 +42411,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+      <c r="R21" s="48" t="inlineStr"/>
+      <c r="S21" s="48" t="inlineStr">
+        <is>
+          <t>Czysty czerwony o niebieskim odcieniu
+Mniej czerwonawy pigment w świetle żarówkowym w przeciwieństwie do
+DX5146 i DX5189
+Jeśłi zamieniasz DX5146 lub DX5189 na DX5145: zmniejsz stężenie o 5% i
+zwiększ stężenie DX5110 o 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
       <c r="A22" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5142</t>
@@ -39539,8 +42494,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+      <c r="R22" s="48" t="inlineStr"/>
+      <c r="S22" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty czerwony
+Podobny do DX5123 ale bardziej niebieski odcień.
+Bardzo jasny i czysty pod żródłem światła lampy (F11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5146</t>
@@ -39613,8 +42576,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+      <c r="R23" s="48" t="inlineStr"/>
+      <c r="S23" s="48" t="inlineStr">
+        <is>
+          <t>Czerwony o niebieskim odcieniu, przezroczysty komponent
+DX5146 jest mniej nienasycony od DX5189
+Najbardziej czerwony czerwony komponent patrząc „pod dużym kątem” (flop)
+Bardziej przezroczysty od DX5189</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
       <c r="A24" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5147</t>
@@ -39685,8 +42657,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="R24" s="48" t="inlineStr"/>
+      <c r="S24" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty, czerwony komponent (żywy, nasycony pomarańczowy)
+Nasycony czerwony o żółtym odcieniu pod każdym kątem</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5149</t>
@@ -39757,8 +42736,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
+      <c r="R25" s="48" t="inlineStr"/>
+      <c r="S25" s="48" t="inlineStr">
+        <is>
+          <t>Bardziej czerwonawy pigment w świetle dziennym (D65)
+Ciemny w świetle sodowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="51" t="inlineStr">
         <is>
           <t>DUXONE|DX5155</t>
@@ -39820,8 +42806,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+      <c r="R26" s="51" t="inlineStr"/>
+      <c r="S26" s="51" t="inlineStr"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5162</t>
@@ -39894,8 +42882,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+      <c r="R27" s="48" t="inlineStr"/>
+      <c r="S27" s="48" t="inlineStr">
+        <is>
+          <t>Kryjacy komponent dla kolorów solid
+Stosowany w małych ilościach w kolorach z efektem do uzyskania bardzo
+zielonego i jasnego wyglądu „pod dużym kątem” (flop)
+Zielony w świetle żarówkowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5163</t>
@@ -39969,8 +42966,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+      <c r="R28" s="48" t="inlineStr"/>
+      <c r="S28" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty żółty komponent (żywy, nasycony czerwony)
+Żółty z czerwonym odcieniem w świetle dziennym (D65)
+Zielony efekt w świetle żarówkowym
+Ten komponent jest bardziej nasycony jak DX5162
+Do użytku z kolorami metalicznymi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5166</t>
@@ -40042,8 +43049,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+      <c r="R29" s="48" t="inlineStr"/>
+      <c r="S29" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty żółty odcień
+Najbardziej czerwonawy żółty komponent w świetle żarówkowym
+Staje się jaśniejszy w oświetleniu sodowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
       <c r="A30" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5167</t>
@@ -40115,8 +43130,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+      <c r="R30" s="48" t="inlineStr"/>
+      <c r="S30" s="48" t="inlineStr">
+        <is>
+          <t>Kryjący komponent dla kolorów solid
+Nasycony żółty odcień
+Najciemniejszy żółty w oświetleniu sodowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5168</t>
@@ -40188,8 +43211,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+      <c r="R31" s="48" t="inlineStr"/>
+      <c r="S31" s="48" t="inlineStr">
+        <is>
+          <t>Kryjący komponent o zielono / żółtym odcieniu
+Może być używany w małych ilościach do kolorów z efektem dla uzyskania
+jasnego i żółtego wyglądu „pod dużym kątem” (flop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
       <c r="A32" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5171</t>
@@ -40260,8 +43291,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+      <c r="R32" s="48" t="inlineStr"/>
+      <c r="S32" s="48" t="inlineStr">
+        <is>
+          <t>Jaśniejszy od DX5172 patrząc „pod dużym kątem”
+Zielony z odcieniem żółtego</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5172</t>
@@ -40331,8 +43369,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+      <c r="R33" s="48" t="inlineStr"/>
+      <c r="S33" s="48" t="inlineStr">
+        <is>
+          <t>Zielony z odcieniem niebieskiego</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5173</t>
@@ -40405,8 +43449,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+      <c r="R34" s="48" t="inlineStr"/>
+      <c r="S34" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty zielony z odcieniem żółtego
+Zielono-żółty w świetle dziennym (D65) i czerwonawy efekt w świetle
+żarówkowym w kolorach metalicznych
+Może być używany z kolorami Solid w dużych ilościach (jeśli jest taka potrzeba)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
       <c r="A35" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5174</t>
@@ -40477,8 +43530,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+      <c r="R35" s="48" t="inlineStr"/>
+      <c r="S35" s="48" t="inlineStr">
+        <is>
+          <t>Nasycony, przezroczysty zielony z zółtym odcieniem
+Podobny do DX5173 ale bardziej nasycony i czystrzy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
       <c r="A36" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5181</t>
@@ -40552,8 +43612,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+      <c r="R36" s="48" t="inlineStr"/>
+      <c r="S36" s="48" t="inlineStr">
+        <is>
+          <t>Zielony w świetle dziennym (D65)
+Staje się bardziej zielony w świetle żarówkowym
+Zielony patrząc „na wprost”
+Zielony
+Czerwony</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1">
       <c r="A37" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5182</t>
@@ -40624,8 +43694,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+      <c r="R37" s="48" t="inlineStr"/>
+      <c r="S37" s="48" t="inlineStr">
+        <is>
+          <t>Niebieski z zielonym odcieniem „pod dużym kątem” (flop)
+Czerwony patrząc „na wprost”</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
       <c r="A38" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5184</t>
@@ -40697,8 +43774,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+      <c r="R38" s="48" t="inlineStr"/>
+      <c r="S38" s="48" t="inlineStr">
+        <is>
+          <t>„Na wprost”
+„Pod dużym kątem”
+Ogólnie - Światło dzienne (D65) / światło słoneczne</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
       <c r="A39" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5185</t>
@@ -40770,8 +43855,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
+      <c r="R39" s="48" t="inlineStr"/>
+      <c r="S39" s="48" t="inlineStr">
+        <is>
+          <t>Przezroczysty pigment
+Czerwonawy niebieski w świetle dziennym (D65) i najczerwieńszy ze wszystkich
+niebieskich w świetle żarówkowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
       <c r="A40" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5187</t>
@@ -40843,8 +43936,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
+      <c r="R40" s="48" t="inlineStr"/>
+      <c r="S40" s="48" t="inlineStr">
+        <is>
+          <t>Mniej nasycony niż DX5188
+Bardziej czerwony patrząc „pod dużym kątem” (flop) niż DX5188
+Bardziej zielony w świetle żarówkowym w porównaniu do DX5188</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1">
       <c r="A41" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5188</t>
@@ -40916,8 +44017,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
+      <c r="R41" s="48" t="inlineStr"/>
+      <c r="S41" s="48" t="inlineStr">
+        <is>
+          <t>Bardzo nasycony czerwonawy fiolet
+Bardziej zielony patrząc „pod dużym kątem” (flop) niż DX5187 i brudniejszy
+Czerwony w świetle żarówkowym w porównaniu do DX5187</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
       <c r="A42" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5189</t>
@@ -40988,8 +44097,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
+      <c r="R42" s="48" t="inlineStr"/>
+      <c r="S42" s="48" t="inlineStr">
+        <is>
+          <t>Najbardziej nienasycony czerwony o niebieskim odcieniu
+Najbardziej czerwonawy w świetle żarówkowym</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1">
       <c r="A43" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5211</t>
@@ -41063,8 +44179,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
+      <c r="R43" s="48" t="inlineStr"/>
+      <c r="S43" s="48" t="inlineStr">
+        <is>
+          <t>Komponenty aluminiowe pod względem iskrzenia się
+SOLID
+ALUMINIOWE
+PERŁOWE &amp;
+XIRALLIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
       <c r="A44" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5212</t>
@@ -41135,8 +44261,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
+      <c r="R44" s="48" t="inlineStr"/>
+      <c r="S44" s="48" t="inlineStr">
+        <is>
+          <t>Skrzący się „pod dużym kątem”
+Jednakowa jasność patrząc „pod kątem”, „na wprost” oraz „pod dużym kątem”</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
       <c r="A45" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5213</t>
@@ -41207,8 +44340,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
+      <c r="R45" s="48" t="inlineStr"/>
+      <c r="S45" s="48" t="inlineStr">
+        <is>
+          <t>Jasnoskrzący się (iskrzący się)
+Jednakowa jasność patrząc „pod kątem”, „na wprost” oraz „pod dużym kątem”</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
       <c r="A46" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5214</t>
@@ -41281,8 +44421,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
+      <c r="R46" s="48" t="inlineStr"/>
+      <c r="S46" s="48" t="inlineStr">
+        <is>
+          <t>Grubość ziarna identyczna jak w DX5215
+Ciemniejszy patrząc „pod kątem” niż DX5215
+Taki sam efekt patrząc „pod dużym kątem” jak DX5215
+DX5214 = DX5215 + 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5215</t>
@@ -41353,8 +44502,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
+      <c r="R47" s="48" t="inlineStr"/>
+      <c r="S47" s="48" t="inlineStr">
+        <is>
+          <t>Przejrzysty (czysty) patrząc „na wprost”
+Jasny pod 3 kątami widzenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
       <c r="A48" s="51" t="inlineStr">
         <is>
           <t>DUXONE|DX5216</t>
@@ -41416,8 +44572,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
+      <c r="R48" s="51" t="inlineStr"/>
+      <c r="S48" s="51" t="inlineStr"/>
+    </row>
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5217</t>
@@ -41488,8 +44646,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+      <c r="R49" s="48" t="inlineStr"/>
+      <c r="S49" s="48" t="inlineStr">
+        <is>
+          <t>Jasny patrząc „na wprost” i brudny (rozmyty) „pod dużym kątem”
+Ciemny patrząc „pod kątem”</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5221</t>
@@ -41560,8 +44725,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+      <c r="R50" s="48" t="inlineStr"/>
+      <c r="S50" s="48" t="inlineStr">
+        <is>
+          <t>Taki sam jak DX5223, ale jaśniejszy
+Komponent aluminium „silver dollar”</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5223</t>
@@ -41631,8 +44803,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
+      <c r="R51" s="48" t="inlineStr"/>
+      <c r="S51" s="48" t="inlineStr">
+        <is>
+          <t>Bardzo jasny patrząc „pod kątem” i ciemniejszy „pod dużym kątem”</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1">
       <c r="A52" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5224</t>
@@ -41704,8 +44882,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
+      <c r="R52" s="48" t="inlineStr"/>
+      <c r="S52" s="48" t="inlineStr">
+        <is>
+          <t>Aluminium pokryte tlenkiem żelaza (żółty)
+Wielkość ziarna podobna do DX5215
+Jaśniejszy patrząc „pod kątem” i czerwony „pod dużym kątem” (flop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
       <c r="A53" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5225</t>
@@ -41777,8 +44963,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
+      <c r="R53" s="48" t="inlineStr"/>
+      <c r="S53" s="48" t="inlineStr">
+        <is>
+          <t>Aluminium pokryte tlenkiem żelaza (pomarańczowy)
+Wielkość ziarna identyczna jak w DX5215
+Jaśniejszy patrząc „pod kątem” i czerwony „pod dużym kątem” (flop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
       <c r="A54" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5226</t>
@@ -41851,8 +45045,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
+      <c r="R54" s="48" t="inlineStr"/>
+      <c r="S54" s="48" t="inlineStr">
+        <is>
+          <t>Komponent aluminium „silver dollar”; nowszy typ od DX5223 i DX5221
+Drobne ziarno w świetle dziennym, ale bardziej skrzący się w świetle
+słonecznym
+Bardzo jasny patrząc „pod kątem” i ciemniejszy „pod dużym kątem” (flop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
       <c r="A55" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5227</t>
@@ -41926,8 +45129,18 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
+      <c r="R55" s="48" t="inlineStr"/>
+      <c r="S55" s="48" t="inlineStr">
+        <is>
+          <t>Takie same właściwości jak DX5226, ale jaśniejszy w świetle słonecznym
+DROBNE
+ZIARNO
+GRUBE
+ZIARNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
       <c r="A56" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5231</t>
@@ -41998,8 +45211,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
+      <c r="R56" s="48" t="inlineStr"/>
+      <c r="S56" s="48" t="inlineStr">
+        <is>
+          <t>Półprzezroczysty
+Średnia wielkość ziarna</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1">
       <c r="A57" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5232</t>
@@ -42072,8 +45292,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="36" customHeight="1">
+      <c r="R57" s="48" t="inlineStr"/>
+      <c r="S57" s="48" t="inlineStr">
+        <is>
+          <t>Półprzezroczysty
+Drobna wielkość ziarna
+Ciemny patrząc „na wprost” i jaśniejszy patrząc „pod dużym kątem” (flop)
+jak DX5231</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1">
       <c r="A58" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5241</t>
@@ -42144,8 +45373,15 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
+      <c r="R58" s="48" t="inlineStr"/>
+      <c r="S58" s="48" t="inlineStr">
+        <is>
+          <t>Średniej wielkości ziarno
+Efekt koloru czerwonego pod każdym kątem</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1">
       <c r="A59" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5242</t>
@@ -42218,8 +45454,17 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="60" ht="36" customHeight="1">
+      <c r="R59" s="48" t="inlineStr"/>
+      <c r="S59" s="48" t="inlineStr">
+        <is>
+          <t>Średnia-drobna wielkość ziarna
+Efekt kolorystyczny taki sam jak w DX5241, ale ze względu na drobniejsza
+wielkość ziarna w DX5242 nasycenie jest mniej jasne, a wygląd ciemniejszy
+patrząc „na wprost” i jaśniejszy „pod dużym kątem” (flop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
       <c r="A60" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5243</t>
@@ -42291,8 +45536,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
+      <c r="R60" s="48" t="inlineStr"/>
+      <c r="S60" s="48" t="inlineStr">
+        <is>
+          <t>Półprzezroczysty
+Średniej wielkości ziarno
+Czerwony patrząc „na wpros” a bardzo zielony „pod dużym kątem” (flop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
       <c r="A61" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5244</t>
@@ -42364,8 +45617,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="36" customHeight="1">
+      <c r="R61" s="48" t="inlineStr"/>
+      <c r="S61" s="48" t="inlineStr">
+        <is>
+          <t>Kryjący
+Średniej wielkości ziarno
+Będzie dawał efekt miedzianego odcienia pod każdym kątem</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
       <c r="A62" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5251</t>
@@ -42437,8 +45698,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="36" customHeight="1">
+      <c r="R62" s="48" t="inlineStr"/>
+      <c r="S62" s="48" t="inlineStr">
+        <is>
+          <t>Średniej wielkości ziarno
+Półprzezroczysty
+Czysty, niebieski patrząc „na wprost” z żółtawym, jasnym flopem</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
       <c r="A63" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5261</t>
@@ -42510,8 +45779,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
+      <c r="R63" s="48" t="inlineStr"/>
+      <c r="S63" s="48" t="inlineStr">
+        <is>
+          <t>Półprzezroczysty
+Średniej wielkości ziarno
+Czysty, zielony patrząc „na wprost” z czerwonawym, jasnym flopem</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
       <c r="A64" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5271</t>
@@ -42583,8 +45860,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="36" customHeight="1">
+      <c r="R64" s="48" t="inlineStr"/>
+      <c r="S64" s="48" t="inlineStr">
+        <is>
+          <t>Półprzezroczysty
+Średniej wielkości ziarno
+Żółtawy złoty kolor patrząc „na wprost” z jasnym, niebieskim flopem</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5281</t>
@@ -42656,8 +45941,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="36" customHeight="1">
+      <c r="R65" s="48" t="inlineStr"/>
+      <c r="S65" s="48" t="inlineStr">
+        <is>
+          <t>Półprzezroczysty
+Średniej wielkości ziarno
+Czysty, fioletowy patrząc „na wprost” z żółtym, pomarańczowym flopem</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="48" customHeight="1">
       <c r="A66" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5299</t>
@@ -42729,8 +46022,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+      <c r="R66" s="48" t="inlineStr"/>
+      <c r="S66" s="48" t="inlineStr">
+        <is>
+          <t>Tylko do użytku w kolorach z efektem
+Tworzy bardziej jednolitą powłokę
+Dodatki modyfikujące</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="48" customHeight="1">
       <c r="A67" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5300</t>
@@ -42800,8 +46101,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
+      <c r="R67" s="48" t="inlineStr"/>
+      <c r="S67" s="48" t="inlineStr">
+        <is>
+          <t>Dużo jaśniejszy w symulowanym świetle słonecznym niż DX5231</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5301</t>
@@ -42871,8 +46178,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="36" customHeight="1">
+      <c r="R68" s="48" t="inlineStr"/>
+      <c r="S68" s="48" t="inlineStr">
+        <is>
+          <t>Jaśniejszy w symulowanym świetle słonecznym niż DX5241</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="48" customHeight="1">
       <c r="A69" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5302</t>
@@ -42942,8 +46255,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
+      <c r="R69" s="48" t="inlineStr"/>
+      <c r="S69" s="48" t="inlineStr">
+        <is>
+          <t>Dużo jaśniejszy w symulowanym świetle słonecznym niż DX5251</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="48" customHeight="1">
       <c r="A70" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5303</t>
@@ -43013,8 +46332,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="71" ht="36" customHeight="1">
+      <c r="R70" s="48" t="inlineStr"/>
+      <c r="S70" s="48" t="inlineStr">
+        <is>
+          <t>Dużo jaśniejszy w symulowanym świetle słonecznym niż DX5261</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="48" customHeight="1">
       <c r="A71" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5304</t>
@@ -43084,8 +46409,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="36" customHeight="1">
+      <c r="R71" s="48" t="inlineStr"/>
+      <c r="S71" s="48" t="inlineStr">
+        <is>
+          <t>Jaśniejszy w symulowanym świetle słonecznym niż DX5271</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1">
       <c r="A72" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX5305</t>
@@ -43155,8 +46486,14 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="36" customHeight="1">
+      <c r="R72" s="48" t="inlineStr"/>
+      <c r="S72" s="48" t="inlineStr">
+        <is>
+          <t>Jaśniejszy w symulowanym świetle słonecznym niż DX5244</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="48" customHeight="1">
       <c r="A73" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX0112</t>
@@ -43234,8 +46571,22 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="36" customHeight="1">
+      <c r="R73" s="48" t="inlineStr"/>
+      <c r="S73" s="48" t="inlineStr">
+        <is>
+          <t>Ma żółte zabarwienie
+Zamień DX5110 na DX0112 gdy stężenie DX5110 jest mniejsze niż 0.45%
+całości wagi receptury; kiedy stężenie komponentu DX0112 jest większe niż 8%,
+zastosuj DX5110
+Zamień DX5110 na DX0112: stężenie DX5110 x 10
+SOLID
+ALUMINIUM
+PERŁOWE &amp;
+XIRALLIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="48" customHeight="1">
       <c r="A74" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX0124</t>
@@ -43307,8 +46658,16 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="36" customHeight="1">
+      <c r="R74" s="48" t="inlineStr"/>
+      <c r="S74" s="48" t="inlineStr">
+        <is>
+          <t>Kryjacy komponent o czerwonym / żółtym odcieniu
+Może być używany w małych ilościach do kolorów z efektem dla uzyskania
+jasnego i czerwonego wyglądu „pod dużym kątem” (flop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="48" customHeight="1">
       <c r="A75" s="48" t="inlineStr">
         <is>
           <t>DUXONE|DX0132</t>
@@ -43384,8 +46743,20 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="36" customHeight="1">
+      <c r="R75" s="48" t="inlineStr"/>
+      <c r="S75" s="48" t="inlineStr">
+        <is>
+          <t>Sprawia, że kolor solidowy jest jaśniejszy
+Może być używany w małych ilościach w kolorach z efektem do rozjaśnienia
+koloru „pod dużym kątem” (flop) i ściemnienia „pod kątem”.
+Zamień DX5130 na DX0132 gdy stężenie DX5130 jest mniejsze niż 0.45%
+całości wagi receptury; kiedy stężenie komponentu DX0132 jest większe niż 8%,
+zastosuj DX5130
+Zamień DX5130 na DX0132: stężenie DX5130 x 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="48" customHeight="1">
       <c r="A76" s="51" t="inlineStr">
         <is>
           <t>DUXONE|DX11</t>
@@ -43447,8 +46818,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="36" customHeight="1">
+      <c r="R76" s="51" t="inlineStr"/>
+      <c r="S76" s="51" t="inlineStr"/>
+    </row>
+    <row r="77" ht="48" customHeight="1">
       <c r="A77" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT100</t>
@@ -43510,8 +46883,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="36" customHeight="1">
+      <c r="R77" s="51" t="inlineStr"/>
+      <c r="S77" s="51" t="inlineStr"/>
+    </row>
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT101</t>
@@ -43573,8 +46948,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="36" customHeight="1">
+      <c r="R78" s="51" t="inlineStr"/>
+      <c r="S78" s="51" t="inlineStr"/>
+    </row>
+    <row r="79" ht="48" customHeight="1">
       <c r="A79" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT102</t>
@@ -43636,8 +47013,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
+      <c r="R79" s="51" t="inlineStr"/>
+      <c r="S79" s="51" t="inlineStr"/>
+    </row>
+    <row r="80" ht="48" customHeight="1">
       <c r="A80" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT103</t>
@@ -43699,8 +47078,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="36" customHeight="1">
+      <c r="R80" s="51" t="inlineStr"/>
+      <c r="S80" s="51" t="inlineStr"/>
+    </row>
+    <row r="81" ht="48" customHeight="1">
       <c r="A81" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT104</t>
@@ -43762,8 +47143,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="36" customHeight="1">
+      <c r="R81" s="51" t="inlineStr"/>
+      <c r="S81" s="51" t="inlineStr"/>
+    </row>
+    <row r="82" ht="48" customHeight="1">
       <c r="A82" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT105</t>
@@ -43825,8 +47208,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="36" customHeight="1">
+      <c r="R82" s="51" t="inlineStr"/>
+      <c r="S82" s="51" t="inlineStr"/>
+    </row>
+    <row r="83" ht="48" customHeight="1">
       <c r="A83" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT106</t>
@@ -43888,8 +47273,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
+      <c r="R83" s="51" t="inlineStr"/>
+      <c r="S83" s="51" t="inlineStr"/>
+    </row>
+    <row r="84" ht="48" customHeight="1">
       <c r="A84" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT107</t>
@@ -43951,8 +47338,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="85" ht="36" customHeight="1">
+      <c r="R84" s="51" t="inlineStr"/>
+      <c r="S84" s="51" t="inlineStr"/>
+    </row>
+    <row r="85" ht="48" customHeight="1">
       <c r="A85" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT108</t>
@@ -44014,8 +47403,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="36" customHeight="1">
+      <c r="R85" s="51" t="inlineStr"/>
+      <c r="S85" s="51" t="inlineStr"/>
+    </row>
+    <row r="86" ht="48" customHeight="1">
       <c r="A86" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT109</t>
@@ -44077,8 +47468,10 @@
           <t>TAK</t>
         </is>
       </c>
-    </row>
-    <row r="87" ht="36" customHeight="1">
+      <c r="R86" s="51" t="inlineStr"/>
+      <c r="S86" s="51" t="inlineStr"/>
+    </row>
+    <row r="87" ht="48" customHeight="1">
       <c r="A87" s="51" t="inlineStr">
         <is>
           <t>DUXONE|AXT110</t>
@@ -44140,13 +47533,15 @@
           <t>TAK</t>
         </is>
       </c>
+      <c r="R87" s="51" t="inlineStr"/>
+      <c r="S87" s="51" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
-  <autoFilter ref="A8:Q87"/>
+  <autoFilter ref="A8:S87"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
+++ b/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
@@ -1896,7 +1896,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>Mieszanie systemów: receptura bazowa AUTOCOLOR może zawierać pigmenty DUXONE i odwrotnie. Nie usuwaj wierszy tabel — zeruj ilość (status USUNIĘTO). Komórki złote = wpis, szare = formuła (ochrona hasłem: lakier). Źródła nazw: PDF Nexa Autocolor 2K Tint Chart oraz Duxone Tint Descriptions PL; kody z szablonów ODS.</t>
+          <t>Mieszanie systemów: receptura bazowa AUTOCOLOR może zawierać pigmenty DUXONE i odwrotnie. Nie usuwaj wierszy tabel — zeruj ilość (status USUNIĘTO). Komórki złote = wpis, szare = formuła (arkusze bez ochrony — edycja i zapis bez hasła). Źródła nazw: PDF Nexa Autocolor 2K Tint Chart oraz Duxone Tint Descriptions PL; kody z szablonów ODS.</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,6 @@
     <row r="31"/>
     <row r="32"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="46">
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="A29:L32"/>
@@ -12933,7 +12932,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <autoFilter ref="A8:N194"/>
   <mergeCells count="3">
     <mergeCell ref="B4:N4"/>
@@ -13055,17 +13053,17 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>Hasło ochrony arkuszy</t>
+          <t>Ochrona arkuszy</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>lakier</t>
+          <t>WYŁĄCZONA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hasło odblokowania formuł. Nie udostępniaj osobom edytującym tylko ilości.</t>
+          <t>Arkusze bez hasła — pełna edycja i zapis. Złote = wpis, szare = formuła.</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13148,6 @@
     <row r="21"/>
     <row r="22"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -18778,7 +18775,6 @@
       <c r="I508" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -20148,7 +20144,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -20258,7 +20253,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -21721,7 +21715,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <autoFilter ref="A11:J51"/>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
@@ -24230,7 +24223,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <autoFilter ref="A11:P51"/>
   <mergeCells count="5">
     <mergeCell ref="A1:P1"/>
@@ -24544,7 +24536,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -27657,7 +27648,6 @@
       <c r="C104" s="13" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="15">
     <mergeCell ref="B97:C97"/>
     <mergeCell ref="A4:H4"/>
@@ -30662,7 +30652,6 @@
       <c r="L208" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <autoFilter ref="A8:L208"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -31118,7 +31107,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <mergeCells count="22">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
@@ -41076,7 +41064,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <autoFilter ref="A8:S115"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
@@ -47537,7 +47524,6 @@
       <c r="S87" s="51" t="inlineStr"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DAF9"/>
   <autoFilter ref="A8:S87"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>

--- a/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
+++ b/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
@@ -27,8 +27,12 @@
     <definedName name="Ust_Jednostka">USTAWIENIA!$B$9</definedName>
     <definedName name="Ust_Tolerancja">USTAWIENIA!$B$10</definedName>
     <definedName name="Lista_Systemow">LISTY!$A$9:$A$10</definedName>
-    <definedName name="Lista_AUTOCOLOR">BAZA_AUTOCOLOR!$C$9:$C$115</definedName>
-    <definedName name="Lista_DUXONE">BAZA_DUXONE!$C$9:$C$87</definedName>
+    <definedName name="Lista_AUTOCOLOR">LISTY!$F$9:$F$115</definedName>
+    <definedName name="Lista_DUXONE">LISTY!$H$9:$H$87</definedName>
+    <definedName name="ListaAC">LISTY!$F$9:$F$115</definedName>
+    <definedName name="ListaDX">LISTY!$H$9:$H$87</definedName>
+    <definedName name="ListaAC_NR">LISTY!$E$9:$E$115</definedName>
+    <definedName name="ListaDX_NR">LISTY!$G$9:$G$87</definedName>
     <definedName name="PigmentyKlucz">PIGMENTY!$A$9:$I$194</definedName>
     <definedName name="Meta_Nazwa">START!$C$5</definedName>
     <definedName name="Meta_Numer">START!$C$6</definedName>
@@ -1770,7 +1774,7 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Arkusz RECEPTURA_ORYGINALNA: wybierz SYSTEM, potem NR z listy. Ilość w gramach. Nazwa uzupełni się sama.</t>
+          <t>Arkusz RECEPTURA_ORYGINALNA: SYSTEM z listy, potem kliknij NR PIGMENTU — lista z wybranej bazy. Ilość w gramach. Nazwa uzupełni się sama.</t>
         </is>
       </c>
     </row>
@@ -20158,11 +20162,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -20193,7 +20204,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Arkusz techniczny — listy rozwijane.</t>
+          <t>Źródło list rozwijanych NR PIGMENTU. Etykieta = kod | nazwa. Makro i Validity biorą zakres z J9/K9.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -20226,6 +20237,41 @@
           <t>PRESETY_MASY_G</t>
         </is>
       </c>
+      <c r="E8" s="53" t="inlineStr">
+        <is>
+          <t>AUTOCOLOR_NR</t>
+        </is>
+      </c>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>AUTOCOLOR_LISTA</t>
+        </is>
+      </c>
+      <c r="G8" s="53" t="inlineStr">
+        <is>
+          <t>DUXONE_NR</t>
+        </is>
+      </c>
+      <c r="H8" s="53" t="inlineStr">
+        <is>
+          <t>DUXONE_LISTA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LICZBA</t>
+        </is>
+      </c>
+      <c r="J8" s="53" t="inlineStr">
+        <is>
+          <t>ADRES_LISTA_AC</t>
+        </is>
+      </c>
+      <c r="K8" s="53" t="inlineStr">
+        <is>
+          <t>ADRES_LISTA_DX</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20236,6 +20282,41 @@
       <c r="C9" t="n">
         <v>100</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>P192-475</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>P192-475 | REGULATOR BAZY</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DX5110</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DX5110 | DEEP BLACK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>wiersze listy →</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>LISTY!$F$9:$F$115</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>LISTY!$H$9:$H$87</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20245,17 +20326,2076 @@
       </c>
       <c r="C10" t="n">
         <v>500</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>P192-528</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>P192-528 | REGULATOR UŁOŻENIA ZIARNA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DX5111</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DX5111 | BLACK</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>liczba kodów →</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>107</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="n">
         <v>1000</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>P192-5600</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>P192-5600 | REGULATOR FLOPU</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DX5121</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DX5121 | EFFECT BROWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>P420-902RT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P420-902RT | RT Pale White</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DX5122</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DX5122 | EFFECT BROWN RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>P420-903RT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>P420-903RT | RT Medium Pale Yellow</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DX5123</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DX5123 | TRANSPARENT MAROON</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>P420-904RT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>P420-904RT | RT Transparent Black</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DX5126</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DX5126 | EFFECT OCRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>P420-905</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>P420-905 | Yellow Oxide</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DX5130</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DX5130 | WHITE HS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>P420-907</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>P420-907 | Red Oxide</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DX5134</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DX5134 | EFFECT WHITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>P420-908RT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>P420-908RT | RT Russet</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DX5136</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DX5136 | Metallic Adjuster</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P420-910RT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>P420-910RT | RT Deep Blue</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DX5161</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DX5161 | ORANGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P420-920</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>P420-920 | Violet</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DX5143</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>DX5143 | RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>P420-926</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>P420-926 | Super Red</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DX5144</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DX5144 | DARK RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>P420-930</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>P420-930 | Lake Blue</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DX5145</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>DX5145 | PINK RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P420-933</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>P420-933 | Blue Black</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DX5142</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DX5142 | FLAMING RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>P420-938</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>P420-938 | Tone Controller</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DX5146</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DX5146 | MAGENTA RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>P420-942</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>P420-942 | Transoxide Red</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DX5147</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DX5147 | LIGHT RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>P420-952</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>P420-952 | Fast Blue</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DX5149</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>DX5149 | BRIGHT RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>P420-960RT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>P420-960RT | RT Burgundy</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DX5155</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DX5155</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>P420-975</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>P420-975 | Bronze Green</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DX5162</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DX5162 | YELLOW ORANGE (LEAD FREE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>P420-978</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>P420-978 | Brown</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DX5163</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DX5163 | EFFECT YELLOW (LEAD FREE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P420-983</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>P420-983 | Strong Yellow</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DX5166</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>DX5166 | EFFECT LIGHT YELLOW (LEAD FREE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>P425-900</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>P425-900 | HS Super White</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DX5167</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DX5167 | YELLOW (LEAD FREE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>P425-919</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>P425-919 | HS Clean Red Violet</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DX5168</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>DX5168 | YELLOW BROWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>P425-921</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>P425-921 | HS Claret</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DX5171</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DX5171 | YELLOW GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>P425-922</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>P425-922 | HS Lagoon Blue</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DX5172</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DX5172 | GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>P425-941</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>P425-941 | HS Strong Red</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DX5173</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DX5173 | BRIGHT GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>P425-948</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>P425-948 | HS Black</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DX5174</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>DX5174 | GOLD GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>P425-950</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>P425-950 | HS Jet Black</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DX5181</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DX5181 | GREEN BLUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>P425-954</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>P425-954 | HS Blue Green</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DX5182</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DX5182 | EFFECT BLUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>P425-956</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>P425-956 | HS Super Blue</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DX5184</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DX5184 | „Pod kątem”</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>P425-957</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>P425-957 | HS Fast Blue</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DX5185</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DX5185 | RED BLUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>P425-971</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>P425-971 | HS Brilliant Red</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DX5187</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DX5187 | VIOLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>P425-984</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>P425-984 | HS Medium Fine Aluminium</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DX5188</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DX5188 | RED VIOLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>P425-985</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>P425-985 | HS Fine Aluminium</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DX5189</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>DX5189 | DARK MAGENTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>P425-986</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>P425-986 | HS Medium Aluminium</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DX5211</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>DX5211 | Komponenty aluminiowe pod względem grubości ziarna</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>P425-987</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>P425-987 | Medium Coarse Aluminium</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DX5212</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>DX5212 | COARSE SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>P425-988</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>P425-988 | HS Coarse Aluminium</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DX5213</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>DX5213 | MEDIUM COARSE SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>P425-989</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>P425-989 | HS Very Coarse Aluminium</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DX5214</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>DX5214 | MEDIUM SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>P425-991</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>P425-991 | Fine Satin Aluminium</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DX5215</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DX5215 | FINE SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>P425-992</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>P425-992 | HS Shining Coarse Aluminium</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DX5216</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>DX5216</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>P425-998</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>P425-998 | HS Coarse Silver Dollar Aluminium</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DX5217</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DX5217 | EXTRA FINE SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>P425-EB02</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>P425-EB02 | KONWERTER BAZY DO KOMÓR SILNIKA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DX5221</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DX5221 | COARSE BRIGHT SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>P426-HE02</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>P426-HE02 | Blue Frost</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DX5223</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DX5223 | MEDIUM BRIGHT SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>P426-HE03</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>P426-HE03 | Graphite Flake</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DX5224</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DX5224 | GOLD ALU</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>P426-HE04</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>P426-HE04 | Gold Flash</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DX5225</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>DX5225 | ORANGE ALU</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>P426-HE05</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>P426-HE05 | Orange Flash</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DX5226</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>DX5226 | FINE EXTRA BRIGHT ALU</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>P426-HE08</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>P426-HE08 | BLUE ALUMINIUM</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DX5227</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DX5227 | MEDIUM FINE BRIGHT ALU</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>P426-PP05</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>P426-PP05 | White Pearl</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DX5231</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>DX5231 | SILVER PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>P426-PP06</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>P426-PP06 | Fine White Pearl</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DX5232</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>DX5232 | FINE SILVER PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>P426-PP07</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>P426-PP07 | Blue Pearl</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DX5241</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>DX5241 | RED PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>P426-PP08</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>P426-PP08 | Red Pearl</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DX5242</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DX5242 | FINE RED PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>P426-PP09</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>P426-PP09 | Gold Pearl</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DX5243</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>DX5243 | SUPER RED PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>P426-PP10</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>P426-PP10 | Copper Pearl</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DX5244</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DX5244 | RED BROWN PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>P426-PP60</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>P426-PP60 | White Satin Pearl</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DX5251</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>DX5251 | BLUE PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>P426-PP61</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>P426-PP61 | Fine Red Pearl</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DX5261</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DX5261 | GREEN PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>P426-PP62</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>P426-PP62 | Fine Russet Pearl</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DX5271</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>DX5271 | GOLD PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>P426-PP63</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>P426-PP63 | Fine Blue Pearl</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DX5281</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DX5281 | LILAC PEARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>P426-PP64</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>P426-PP64 | Medium Violet Pearl</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DX5299</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>DX5299 | UNISILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>P426-PP65</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>P426-PP65 | Medium Green Pearl</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DX5300</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>DX5300 | WHITE CRYSTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>P426-PP68</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>P426-PP68 | Orange Pearl</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DX5301</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>DX5301 | RED CRYSTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>P429-914</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>P429-914 | HS CLEAN BLUE VIOLET</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DX5302</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>DX5302 | BLUE CRYSTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>P429-917</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>P429-917 | HS GREEN GOLD</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DX5303</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>DX5303 | GREEN CRYSTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>P429-923</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>P429-923 | HS Bright Maroon</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DX5304</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>DX5304 | GOLD CRYSTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>P429-932</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>P429-932 | HS CLEAN ORGANIC ORANGE</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DX5305</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>DX5305 | COPPER CRYSTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>P429-937</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>P429-937 | HS Pale Yellow</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DX0112</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>DX0112 | BLACK (KOMPONENT O MAŁEJ SILE KRYCIA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>P429-961</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>P429-961 | HS Clean Magenta</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DX0124</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>DX0124 | BROWN RED (PIGMENT O MAŁEJ SILE KRYCIA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>P429-967</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>P429-967 | HS Deep Angle Black</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DX0132</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>DX0132 | WHITE (KOMPONENT O MAŁEJ SILE KRYCIA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>P429-972</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>P429-972 | HS Bright Amber</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DX11</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>DX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>P429-973</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>P429-973 | HS Bright Orange</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>AXT100</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>AXT100</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>P429-976</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>P429-976 | HS Red Violet</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>AXT101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>AXT101</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>P429-980</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>P429-980 | HS Speed Red</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>AXT102</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>AXT102</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>P429-981</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>P429-981 | Transparent Gold</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>AXT103</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>AXT103</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>P433-XR10</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>P433-XR10 | Crystal Silver</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>AXT104</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>AXT104</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>P433-XR11</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>P433-XR11 | Sunbeam Gold</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>AXT105</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>AXT105</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>P433-XR12</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>P433-XR12 | Radiant Red</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>AXT106</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>AXT106</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>P433-XR13</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>P433-XR13 | Galaxy Blue</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>AXT107</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>AXT107</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>P433-XR14</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>P433-XR14 | Stellar Green</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>AXT108</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>AXT108</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>P433-XR15</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>P433-XR15 | Solaris Red</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>AXT109</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>AXT109</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>P433-XR16</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>P433-XR16 | Fireside Copper</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>AXT110</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>AXT110</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>P433-XR17</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>P433-XR17 | Cosmic Turquoise</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>P433-XR18</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>P433-XR18 | Amethyst Dream</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>P434-CS32</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>P434-CS32 | Viola Fantasy</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>P434-CS33</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>P434-CS33 | Arctic Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>P434-CS34</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>P434-CS34 | Tropic Sunrise</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>P434-CS35</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>P434-CS35 | Lapis Sunlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>P435-GF37</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>P435-GF37 | Silver Glass</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>P440-FX20</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>P440-FX20 | CHROMAFLAIR CYAN TO PURPLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>P440-FX21</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>P440-FX21 | CHROMAFLAIR SILVER TO GREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>P440-FX22</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>P440-FX22 | CHROMAFLAIR GREEN TO PURPLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>P440-FX23</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>P440-FX23 | CHROMAFLAIR BLUE TO RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>P440-FX24</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>P440-FX24 | CHROMAFLAIR MAGENTA TO GOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>P440-FX25</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>P440-FX25 | CHROMAFLAIR GOLD TO SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>P440-FX26</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>P440-FX26 | CHROMAFLAIR RED TO GOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>P440-FX51</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>P440-FX51 | Silver Flair</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>P440-LM01</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>P440-LM01 | LIQUID METAL SUPER FINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>P450-EC50</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>P450-EC50 | BRILLIANT RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>P420-982</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>P420-982 | Trans Oxide Yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>VM4370</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>VM4370 | Super Fine Liquid Metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>P426-HE07</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>P426-HE07 | Blue Flash</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>P434-CS31</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>P434-CS31 | Autumn Mystery</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>VM4987</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>VM4987 | Cyan to Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>VM4988</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>VM4988 | Silver to Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>VM4989</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>VM4989 | Green to Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>VM4990</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>VM4990 | Blue to Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>VM4991</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>VM4991 | Magenta to Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>VM4994</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>VM4994 | Gold to Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>VM4995</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>VM4995 | Red to Gold</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20272,7 +22412,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -20427,7 +22567,7 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>Wpisz SYSTEM (AUTOCOLOR lub DUXONE), potem NR z listy zależnej. Możesz mieszać systemy. Ilość ≥ 0. Ten sam klucz dwa razy = DUPLIKAT (zsumuj ilości).</t>
+          <t>Najpierw SYSTEM (AUTOCOLOR / DUXONE) z listy, potem kliknij NR PIGMENTU — otworzy się lista z tej bazy. Każdy wiersz ma własny SYSTEM (można mieszać). Po wyborze numeru nazwa i jednostka uzupełnią się same. Ilość ≥ 0. Ten sam klucz dwa razy = DUPLIKAT (zsumuj ilości).</t>
         </is>
       </c>
     </row>
@@ -20516,7 +22656,7 @@
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="14">
-        <f>IF(C12="","",B12&amp;"|"&amp;C12)</f>
+        <f>IF(C12="","",B12&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C12)),TRIM(LEFT(C12,FIND(" | ",C12)-1)),C12))</f>
         <v/>
       </c>
       <c r="J12" s="14">
@@ -20556,7 +22696,7 @@
       </c>
       <c r="H13" s="8" t="n"/>
       <c r="I13" s="14">
-        <f>IF(C13="","",B13&amp;"|"&amp;C13)</f>
+        <f>IF(C13="","",B13&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C13)),TRIM(LEFT(C13,FIND(" | ",C13)-1)),C13))</f>
         <v/>
       </c>
       <c r="J13" s="14">
@@ -20596,7 +22736,7 @@
       </c>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="14">
-        <f>IF(C14="","",B14&amp;"|"&amp;C14)</f>
+        <f>IF(C14="","",B14&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C14)),TRIM(LEFT(C14,FIND(" | ",C14)-1)),C14))</f>
         <v/>
       </c>
       <c r="J14" s="14">
@@ -20626,7 +22766,7 @@
       </c>
       <c r="H15" s="8" t="n"/>
       <c r="I15" s="14">
-        <f>IF(C15="","",B15&amp;"|"&amp;C15)</f>
+        <f>IF(C15="","",B15&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C15)),TRIM(LEFT(C15,FIND(" | ",C15)-1)),C15))</f>
         <v/>
       </c>
       <c r="J15" s="14">
@@ -20656,7 +22796,7 @@
       </c>
       <c r="H16" s="8" t="n"/>
       <c r="I16" s="14">
-        <f>IF(C16="","",B16&amp;"|"&amp;C16)</f>
+        <f>IF(C16="","",B16&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C16)),TRIM(LEFT(C16,FIND(" | ",C16)-1)),C16))</f>
         <v/>
       </c>
       <c r="J16" s="14">
@@ -20686,7 +22826,7 @@
       </c>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="14">
-        <f>IF(C17="","",B17&amp;"|"&amp;C17)</f>
+        <f>IF(C17="","",B17&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C17)),TRIM(LEFT(C17,FIND(" | ",C17)-1)),C17))</f>
         <v/>
       </c>
       <c r="J17" s="14">
@@ -20716,7 +22856,7 @@
       </c>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="14">
-        <f>IF(C18="","",B18&amp;"|"&amp;C18)</f>
+        <f>IF(C18="","",B18&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C18)),TRIM(LEFT(C18,FIND(" | ",C18)-1)),C18))</f>
         <v/>
       </c>
       <c r="J18" s="14">
@@ -20746,7 +22886,7 @@
       </c>
       <c r="H19" s="8" t="n"/>
       <c r="I19" s="14">
-        <f>IF(C19="","",B19&amp;"|"&amp;C19)</f>
+        <f>IF(C19="","",B19&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C19)),TRIM(LEFT(C19,FIND(" | ",C19)-1)),C19))</f>
         <v/>
       </c>
       <c r="J19" s="14">
@@ -20776,7 +22916,7 @@
       </c>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="14">
-        <f>IF(C20="","",B20&amp;"|"&amp;C20)</f>
+        <f>IF(C20="","",B20&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C20)),TRIM(LEFT(C20,FIND(" | ",C20)-1)),C20))</f>
         <v/>
       </c>
       <c r="J20" s="14">
@@ -20806,7 +22946,7 @@
       </c>
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="14">
-        <f>IF(C21="","",B21&amp;"|"&amp;C21)</f>
+        <f>IF(C21="","",B21&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C21)),TRIM(LEFT(C21,FIND(" | ",C21)-1)),C21))</f>
         <v/>
       </c>
       <c r="J21" s="14">
@@ -20836,7 +22976,7 @@
       </c>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="14">
-        <f>IF(C22="","",B22&amp;"|"&amp;C22)</f>
+        <f>IF(C22="","",B22&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C22)),TRIM(LEFT(C22,FIND(" | ",C22)-1)),C22))</f>
         <v/>
       </c>
       <c r="J22" s="14">
@@ -20866,7 +23006,7 @@
       </c>
       <c r="H23" s="8" t="n"/>
       <c r="I23" s="14">
-        <f>IF(C23="","",B23&amp;"|"&amp;C23)</f>
+        <f>IF(C23="","",B23&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C23)),TRIM(LEFT(C23,FIND(" | ",C23)-1)),C23))</f>
         <v/>
       </c>
       <c r="J23" s="14">
@@ -20896,7 +23036,7 @@
       </c>
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="14">
-        <f>IF(C24="","",B24&amp;"|"&amp;C24)</f>
+        <f>IF(C24="","",B24&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C24)),TRIM(LEFT(C24,FIND(" | ",C24)-1)),C24))</f>
         <v/>
       </c>
       <c r="J24" s="14">
@@ -20926,7 +23066,7 @@
       </c>
       <c r="H25" s="8" t="n"/>
       <c r="I25" s="14">
-        <f>IF(C25="","",B25&amp;"|"&amp;C25)</f>
+        <f>IF(C25="","",B25&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C25)),TRIM(LEFT(C25,FIND(" | ",C25)-1)),C25))</f>
         <v/>
       </c>
       <c r="J25" s="14">
@@ -20956,7 +23096,7 @@
       </c>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="14">
-        <f>IF(C26="","",B26&amp;"|"&amp;C26)</f>
+        <f>IF(C26="","",B26&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C26)),TRIM(LEFT(C26,FIND(" | ",C26)-1)),C26))</f>
         <v/>
       </c>
       <c r="J26" s="14">
@@ -20986,7 +23126,7 @@
       </c>
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="14">
-        <f>IF(C27="","",B27&amp;"|"&amp;C27)</f>
+        <f>IF(C27="","",B27&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C27)),TRIM(LEFT(C27,FIND(" | ",C27)-1)),C27))</f>
         <v/>
       </c>
       <c r="J27" s="14">
@@ -21016,7 +23156,7 @@
       </c>
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="14">
-        <f>IF(C28="","",B28&amp;"|"&amp;C28)</f>
+        <f>IF(C28="","",B28&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C28)),TRIM(LEFT(C28,FIND(" | ",C28)-1)),C28))</f>
         <v/>
       </c>
       <c r="J28" s="14">
@@ -21046,7 +23186,7 @@
       </c>
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="14">
-        <f>IF(C29="","",B29&amp;"|"&amp;C29)</f>
+        <f>IF(C29="","",B29&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C29)),TRIM(LEFT(C29,FIND(" | ",C29)-1)),C29))</f>
         <v/>
       </c>
       <c r="J29" s="14">
@@ -21076,7 +23216,7 @@
       </c>
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="14">
-        <f>IF(C30="","",B30&amp;"|"&amp;C30)</f>
+        <f>IF(C30="","",B30&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C30)),TRIM(LEFT(C30,FIND(" | ",C30)-1)),C30))</f>
         <v/>
       </c>
       <c r="J30" s="14">
@@ -21106,7 +23246,7 @@
       </c>
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="14">
-        <f>IF(C31="","",B31&amp;"|"&amp;C31)</f>
+        <f>IF(C31="","",B31&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C31)),TRIM(LEFT(C31,FIND(" | ",C31)-1)),C31))</f>
         <v/>
       </c>
       <c r="J31" s="14">
@@ -21136,7 +23276,7 @@
       </c>
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="14">
-        <f>IF(C32="","",B32&amp;"|"&amp;C32)</f>
+        <f>IF(C32="","",B32&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C32)),TRIM(LEFT(C32,FIND(" | ",C32)-1)),C32))</f>
         <v/>
       </c>
       <c r="J32" s="14">
@@ -21166,7 +23306,7 @@
       </c>
       <c r="H33" s="8" t="n"/>
       <c r="I33" s="14">
-        <f>IF(C33="","",B33&amp;"|"&amp;C33)</f>
+        <f>IF(C33="","",B33&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C33)),TRIM(LEFT(C33,FIND(" | ",C33)-1)),C33))</f>
         <v/>
       </c>
       <c r="J33" s="14">
@@ -21196,7 +23336,7 @@
       </c>
       <c r="H34" s="8" t="n"/>
       <c r="I34" s="14">
-        <f>IF(C34="","",B34&amp;"|"&amp;C34)</f>
+        <f>IF(C34="","",B34&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C34)),TRIM(LEFT(C34,FIND(" | ",C34)-1)),C34))</f>
         <v/>
       </c>
       <c r="J34" s="14">
@@ -21226,7 +23366,7 @@
       </c>
       <c r="H35" s="8" t="n"/>
       <c r="I35" s="14">
-        <f>IF(C35="","",B35&amp;"|"&amp;C35)</f>
+        <f>IF(C35="","",B35&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C35)),TRIM(LEFT(C35,FIND(" | ",C35)-1)),C35))</f>
         <v/>
       </c>
       <c r="J35" s="14">
@@ -21256,7 +23396,7 @@
       </c>
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="14">
-        <f>IF(C36="","",B36&amp;"|"&amp;C36)</f>
+        <f>IF(C36="","",B36&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C36)),TRIM(LEFT(C36,FIND(" | ",C36)-1)),C36))</f>
         <v/>
       </c>
       <c r="J36" s="14">
@@ -21286,7 +23426,7 @@
       </c>
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="14">
-        <f>IF(C37="","",B37&amp;"|"&amp;C37)</f>
+        <f>IF(C37="","",B37&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C37)),TRIM(LEFT(C37,FIND(" | ",C37)-1)),C37))</f>
         <v/>
       </c>
       <c r="J37" s="14">
@@ -21316,7 +23456,7 @@
       </c>
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="14">
-        <f>IF(C38="","",B38&amp;"|"&amp;C38)</f>
+        <f>IF(C38="","",B38&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C38)),TRIM(LEFT(C38,FIND(" | ",C38)-1)),C38))</f>
         <v/>
       </c>
       <c r="J38" s="14">
@@ -21346,7 +23486,7 @@
       </c>
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="14">
-        <f>IF(C39="","",B39&amp;"|"&amp;C39)</f>
+        <f>IF(C39="","",B39&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C39)),TRIM(LEFT(C39,FIND(" | ",C39)-1)),C39))</f>
         <v/>
       </c>
       <c r="J39" s="14">
@@ -21376,7 +23516,7 @@
       </c>
       <c r="H40" s="8" t="n"/>
       <c r="I40" s="14">
-        <f>IF(C40="","",B40&amp;"|"&amp;C40)</f>
+        <f>IF(C40="","",B40&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C40)),TRIM(LEFT(C40,FIND(" | ",C40)-1)),C40))</f>
         <v/>
       </c>
       <c r="J40" s="14">
@@ -21406,7 +23546,7 @@
       </c>
       <c r="H41" s="8" t="n"/>
       <c r="I41" s="14">
-        <f>IF(C41="","",B41&amp;"|"&amp;C41)</f>
+        <f>IF(C41="","",B41&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C41)),TRIM(LEFT(C41,FIND(" | ",C41)-1)),C41))</f>
         <v/>
       </c>
       <c r="J41" s="14">
@@ -21436,7 +23576,7 @@
       </c>
       <c r="H42" s="8" t="n"/>
       <c r="I42" s="14">
-        <f>IF(C42="","",B42&amp;"|"&amp;C42)</f>
+        <f>IF(C42="","",B42&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C42)),TRIM(LEFT(C42,FIND(" | ",C42)-1)),C42))</f>
         <v/>
       </c>
       <c r="J42" s="14">
@@ -21466,7 +23606,7 @@
       </c>
       <c r="H43" s="8" t="n"/>
       <c r="I43" s="14">
-        <f>IF(C43="","",B43&amp;"|"&amp;C43)</f>
+        <f>IF(C43="","",B43&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C43)),TRIM(LEFT(C43,FIND(" | ",C43)-1)),C43))</f>
         <v/>
       </c>
       <c r="J43" s="14">
@@ -21496,7 +23636,7 @@
       </c>
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="14">
-        <f>IF(C44="","",B44&amp;"|"&amp;C44)</f>
+        <f>IF(C44="","",B44&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C44)),TRIM(LEFT(C44,FIND(" | ",C44)-1)),C44))</f>
         <v/>
       </c>
       <c r="J44" s="14">
@@ -21526,7 +23666,7 @@
       </c>
       <c r="H45" s="8" t="n"/>
       <c r="I45" s="14">
-        <f>IF(C45="","",B45&amp;"|"&amp;C45)</f>
+        <f>IF(C45="","",B45&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C45)),TRIM(LEFT(C45,FIND(" | ",C45)-1)),C45))</f>
         <v/>
       </c>
       <c r="J45" s="14">
@@ -21556,7 +23696,7 @@
       </c>
       <c r="H46" s="8" t="n"/>
       <c r="I46" s="14">
-        <f>IF(C46="","",B46&amp;"|"&amp;C46)</f>
+        <f>IF(C46="","",B46&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C46)),TRIM(LEFT(C46,FIND(" | ",C46)-1)),C46))</f>
         <v/>
       </c>
       <c r="J46" s="14">
@@ -21586,7 +23726,7 @@
       </c>
       <c r="H47" s="8" t="n"/>
       <c r="I47" s="14">
-        <f>IF(C47="","",B47&amp;"|"&amp;C47)</f>
+        <f>IF(C47="","",B47&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C47)),TRIM(LEFT(C47,FIND(" | ",C47)-1)),C47))</f>
         <v/>
       </c>
       <c r="J47" s="14">
@@ -21616,7 +23756,7 @@
       </c>
       <c r="H48" s="8" t="n"/>
       <c r="I48" s="14">
-        <f>IF(C48="","",B48&amp;"|"&amp;C48)</f>
+        <f>IF(C48="","",B48&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C48)),TRIM(LEFT(C48,FIND(" | ",C48)-1)),C48))</f>
         <v/>
       </c>
       <c r="J48" s="14">
@@ -21646,7 +23786,7 @@
       </c>
       <c r="H49" s="8" t="n"/>
       <c r="I49" s="14">
-        <f>IF(C49="","",B49&amp;"|"&amp;C49)</f>
+        <f>IF(C49="","",B49&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C49)),TRIM(LEFT(C49,FIND(" | ",C49)-1)),C49))</f>
         <v/>
       </c>
       <c r="J49" s="14">
@@ -21676,7 +23816,7 @@
       </c>
       <c r="H50" s="8" t="n"/>
       <c r="I50" s="14">
-        <f>IF(C50="","",B50&amp;"|"&amp;C50)</f>
+        <f>IF(C50="","",B50&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C50)),TRIM(LEFT(C50,FIND(" | ",C50)-1)),C50))</f>
         <v/>
       </c>
       <c r="J50" s="14">
@@ -21706,7 +23846,7 @@
       </c>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="14">
-        <f>IF(C51="","",B51&amp;"|"&amp;C51)</f>
+        <f>IF(C51="","",B51&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C51)),TRIM(LEFT(C51,FIND(" | ",C51)-1)),C51))</f>
         <v/>
       </c>
       <c r="J51" s="14">
@@ -21739,8 +23879,8 @@
     <dataValidation sqref="E12:E51" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ilość ujemna" error="Ilość nie może być ujemna." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="C12:C51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT("Lista_"&amp;B12)</formula1>
+    <dataValidation sqref="C12:C51" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="NR PIGMENTU" prompt="Wybierz pigment z listy (baza = SYSTEM w tym wierszu). Nie wpisuj kodu ręcznie." type="list">
+      <formula1>=INDIRECT(IF($B12="DUXONE",LISTY!$K$9,LISTY!$J$9))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21758,7 +23898,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -21945,7 +24085,7 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>Kolumny złote: SYSTEM, NR, ILOŚĆ WŁASNA, UWAGI. ILOŚĆ DO ZWAŻENIA = ilość własna × masa docelowa / masa własna (przeliczenie na 100 g / 500 g / 1 kg / dowolna). STATUS: BEZ ZMIAN / ZWIĘKSZONO / ZMNIEJSZONO / DODANO / USUNIĘTO. Usunięcie = ilość własna 0 przy ilości oryginalnej &gt; 0.</t>
+          <t>Kolumny złote: SYSTEM, NR, ILOŚĆ WŁASNA, UWAGI. Kliknij NR PIGMENTU — lista z bazy SYSTEM w tym wierszu (można mieszać AUTOCOLOR i DUXONE). ILOŚĆ DO ZWAŻENIA = ilość własna × masa docelowa / masa własna (przeliczenie na 100 g / 500 g / 1 kg / dowolna). STATUS: BEZ ZMIAN / ZWIĘKSZONO / ZMNIEJSZONO / DODANO / USUNIĘTO. Usunięcie = ilość własna 0 przy ilości oryginalnej &gt; 0.</t>
         </is>
       </c>
     </row>
@@ -22092,7 +24232,7 @@
         <v/>
       </c>
       <c r="P12" s="14">
-        <f>IF(C12="","",B12&amp;"|"&amp;C12)</f>
+        <f>IF(C12="","",B12&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C12)),TRIM(LEFT(C12,FIND(" | ",C12)-1)),C12))</f>
         <v/>
       </c>
     </row>
@@ -22156,7 +24296,7 @@
         <v/>
       </c>
       <c r="P13" s="14">
-        <f>IF(C13="","",B13&amp;"|"&amp;C13)</f>
+        <f>IF(C13="","",B13&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C13)),TRIM(LEFT(C13,FIND(" | ",C13)-1)),C13))</f>
         <v/>
       </c>
     </row>
@@ -22220,7 +24360,7 @@
         <v/>
       </c>
       <c r="P14" s="14">
-        <f>IF(C14="","",B14&amp;"|"&amp;C14)</f>
+        <f>IF(C14="","",B14&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C14)),TRIM(LEFT(C14,FIND(" | ",C14)-1)),C14))</f>
         <v/>
       </c>
     </row>
@@ -22274,7 +24414,7 @@
         <v/>
       </c>
       <c r="P15" s="14">
-        <f>IF(C15="","",B15&amp;"|"&amp;C15)</f>
+        <f>IF(C15="","",B15&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C15)),TRIM(LEFT(C15,FIND(" | ",C15)-1)),C15))</f>
         <v/>
       </c>
     </row>
@@ -22328,7 +24468,7 @@
         <v/>
       </c>
       <c r="P16" s="14">
-        <f>IF(C16="","",B16&amp;"|"&amp;C16)</f>
+        <f>IF(C16="","",B16&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C16)),TRIM(LEFT(C16,FIND(" | ",C16)-1)),C16))</f>
         <v/>
       </c>
     </row>
@@ -22382,7 +24522,7 @@
         <v/>
       </c>
       <c r="P17" s="14">
-        <f>IF(C17="","",B17&amp;"|"&amp;C17)</f>
+        <f>IF(C17="","",B17&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C17)),TRIM(LEFT(C17,FIND(" | ",C17)-1)),C17))</f>
         <v/>
       </c>
     </row>
@@ -22436,7 +24576,7 @@
         <v/>
       </c>
       <c r="P18" s="14">
-        <f>IF(C18="","",B18&amp;"|"&amp;C18)</f>
+        <f>IF(C18="","",B18&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C18)),TRIM(LEFT(C18,FIND(" | ",C18)-1)),C18))</f>
         <v/>
       </c>
     </row>
@@ -22490,7 +24630,7 @@
         <v/>
       </c>
       <c r="P19" s="14">
-        <f>IF(C19="","",B19&amp;"|"&amp;C19)</f>
+        <f>IF(C19="","",B19&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C19)),TRIM(LEFT(C19,FIND(" | ",C19)-1)),C19))</f>
         <v/>
       </c>
     </row>
@@ -22544,7 +24684,7 @@
         <v/>
       </c>
       <c r="P20" s="14">
-        <f>IF(C20="","",B20&amp;"|"&amp;C20)</f>
+        <f>IF(C20="","",B20&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C20)),TRIM(LEFT(C20,FIND(" | ",C20)-1)),C20))</f>
         <v/>
       </c>
     </row>
@@ -22598,7 +24738,7 @@
         <v/>
       </c>
       <c r="P21" s="14">
-        <f>IF(C21="","",B21&amp;"|"&amp;C21)</f>
+        <f>IF(C21="","",B21&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C21)),TRIM(LEFT(C21,FIND(" | ",C21)-1)),C21))</f>
         <v/>
       </c>
     </row>
@@ -22652,7 +24792,7 @@
         <v/>
       </c>
       <c r="P22" s="14">
-        <f>IF(C22="","",B22&amp;"|"&amp;C22)</f>
+        <f>IF(C22="","",B22&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C22)),TRIM(LEFT(C22,FIND(" | ",C22)-1)),C22))</f>
         <v/>
       </c>
     </row>
@@ -22706,7 +24846,7 @@
         <v/>
       </c>
       <c r="P23" s="14">
-        <f>IF(C23="","",B23&amp;"|"&amp;C23)</f>
+        <f>IF(C23="","",B23&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C23)),TRIM(LEFT(C23,FIND(" | ",C23)-1)),C23))</f>
         <v/>
       </c>
     </row>
@@ -22760,7 +24900,7 @@
         <v/>
       </c>
       <c r="P24" s="14">
-        <f>IF(C24="","",B24&amp;"|"&amp;C24)</f>
+        <f>IF(C24="","",B24&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C24)),TRIM(LEFT(C24,FIND(" | ",C24)-1)),C24))</f>
         <v/>
       </c>
     </row>
@@ -22814,7 +24954,7 @@
         <v/>
       </c>
       <c r="P25" s="14">
-        <f>IF(C25="","",B25&amp;"|"&amp;C25)</f>
+        <f>IF(C25="","",B25&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C25)),TRIM(LEFT(C25,FIND(" | ",C25)-1)),C25))</f>
         <v/>
       </c>
     </row>
@@ -22868,7 +25008,7 @@
         <v/>
       </c>
       <c r="P26" s="14">
-        <f>IF(C26="","",B26&amp;"|"&amp;C26)</f>
+        <f>IF(C26="","",B26&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C26)),TRIM(LEFT(C26,FIND(" | ",C26)-1)),C26))</f>
         <v/>
       </c>
     </row>
@@ -22922,7 +25062,7 @@
         <v/>
       </c>
       <c r="P27" s="14">
-        <f>IF(C27="","",B27&amp;"|"&amp;C27)</f>
+        <f>IF(C27="","",B27&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C27)),TRIM(LEFT(C27,FIND(" | ",C27)-1)),C27))</f>
         <v/>
       </c>
     </row>
@@ -22976,7 +25116,7 @@
         <v/>
       </c>
       <c r="P28" s="14">
-        <f>IF(C28="","",B28&amp;"|"&amp;C28)</f>
+        <f>IF(C28="","",B28&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C28)),TRIM(LEFT(C28,FIND(" | ",C28)-1)),C28))</f>
         <v/>
       </c>
     </row>
@@ -23030,7 +25170,7 @@
         <v/>
       </c>
       <c r="P29" s="14">
-        <f>IF(C29="","",B29&amp;"|"&amp;C29)</f>
+        <f>IF(C29="","",B29&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C29)),TRIM(LEFT(C29,FIND(" | ",C29)-1)),C29))</f>
         <v/>
       </c>
     </row>
@@ -23084,7 +25224,7 @@
         <v/>
       </c>
       <c r="P30" s="14">
-        <f>IF(C30="","",B30&amp;"|"&amp;C30)</f>
+        <f>IF(C30="","",B30&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C30)),TRIM(LEFT(C30,FIND(" | ",C30)-1)),C30))</f>
         <v/>
       </c>
     </row>
@@ -23138,7 +25278,7 @@
         <v/>
       </c>
       <c r="P31" s="14">
-        <f>IF(C31="","",B31&amp;"|"&amp;C31)</f>
+        <f>IF(C31="","",B31&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C31)),TRIM(LEFT(C31,FIND(" | ",C31)-1)),C31))</f>
         <v/>
       </c>
     </row>
@@ -23192,7 +25332,7 @@
         <v/>
       </c>
       <c r="P32" s="14">
-        <f>IF(C32="","",B32&amp;"|"&amp;C32)</f>
+        <f>IF(C32="","",B32&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C32)),TRIM(LEFT(C32,FIND(" | ",C32)-1)),C32))</f>
         <v/>
       </c>
     </row>
@@ -23246,7 +25386,7 @@
         <v/>
       </c>
       <c r="P33" s="14">
-        <f>IF(C33="","",B33&amp;"|"&amp;C33)</f>
+        <f>IF(C33="","",B33&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C33)),TRIM(LEFT(C33,FIND(" | ",C33)-1)),C33))</f>
         <v/>
       </c>
     </row>
@@ -23300,7 +25440,7 @@
         <v/>
       </c>
       <c r="P34" s="14">
-        <f>IF(C34="","",B34&amp;"|"&amp;C34)</f>
+        <f>IF(C34="","",B34&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C34)),TRIM(LEFT(C34,FIND(" | ",C34)-1)),C34))</f>
         <v/>
       </c>
     </row>
@@ -23354,7 +25494,7 @@
         <v/>
       </c>
       <c r="P35" s="14">
-        <f>IF(C35="","",B35&amp;"|"&amp;C35)</f>
+        <f>IF(C35="","",B35&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C35)),TRIM(LEFT(C35,FIND(" | ",C35)-1)),C35))</f>
         <v/>
       </c>
     </row>
@@ -23408,7 +25548,7 @@
         <v/>
       </c>
       <c r="P36" s="14">
-        <f>IF(C36="","",B36&amp;"|"&amp;C36)</f>
+        <f>IF(C36="","",B36&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C36)),TRIM(LEFT(C36,FIND(" | ",C36)-1)),C36))</f>
         <v/>
       </c>
     </row>
@@ -23462,7 +25602,7 @@
         <v/>
       </c>
       <c r="P37" s="14">
-        <f>IF(C37="","",B37&amp;"|"&amp;C37)</f>
+        <f>IF(C37="","",B37&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C37)),TRIM(LEFT(C37,FIND(" | ",C37)-1)),C37))</f>
         <v/>
       </c>
     </row>
@@ -23516,7 +25656,7 @@
         <v/>
       </c>
       <c r="P38" s="14">
-        <f>IF(C38="","",B38&amp;"|"&amp;C38)</f>
+        <f>IF(C38="","",B38&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C38)),TRIM(LEFT(C38,FIND(" | ",C38)-1)),C38))</f>
         <v/>
       </c>
     </row>
@@ -23570,7 +25710,7 @@
         <v/>
       </c>
       <c r="P39" s="14">
-        <f>IF(C39="","",B39&amp;"|"&amp;C39)</f>
+        <f>IF(C39="","",B39&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C39)),TRIM(LEFT(C39,FIND(" | ",C39)-1)),C39))</f>
         <v/>
       </c>
     </row>
@@ -23624,7 +25764,7 @@
         <v/>
       </c>
       <c r="P40" s="14">
-        <f>IF(C40="","",B40&amp;"|"&amp;C40)</f>
+        <f>IF(C40="","",B40&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C40)),TRIM(LEFT(C40,FIND(" | ",C40)-1)),C40))</f>
         <v/>
       </c>
     </row>
@@ -23678,7 +25818,7 @@
         <v/>
       </c>
       <c r="P41" s="14">
-        <f>IF(C41="","",B41&amp;"|"&amp;C41)</f>
+        <f>IF(C41="","",B41&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C41)),TRIM(LEFT(C41,FIND(" | ",C41)-1)),C41))</f>
         <v/>
       </c>
     </row>
@@ -23732,7 +25872,7 @@
         <v/>
       </c>
       <c r="P42" s="14">
-        <f>IF(C42="","",B42&amp;"|"&amp;C42)</f>
+        <f>IF(C42="","",B42&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C42)),TRIM(LEFT(C42,FIND(" | ",C42)-1)),C42))</f>
         <v/>
       </c>
     </row>
@@ -23786,7 +25926,7 @@
         <v/>
       </c>
       <c r="P43" s="14">
-        <f>IF(C43="","",B43&amp;"|"&amp;C43)</f>
+        <f>IF(C43="","",B43&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C43)),TRIM(LEFT(C43,FIND(" | ",C43)-1)),C43))</f>
         <v/>
       </c>
     </row>
@@ -23840,7 +25980,7 @@
         <v/>
       </c>
       <c r="P44" s="14">
-        <f>IF(C44="","",B44&amp;"|"&amp;C44)</f>
+        <f>IF(C44="","",B44&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C44)),TRIM(LEFT(C44,FIND(" | ",C44)-1)),C44))</f>
         <v/>
       </c>
     </row>
@@ -23894,7 +26034,7 @@
         <v/>
       </c>
       <c r="P45" s="14">
-        <f>IF(C45="","",B45&amp;"|"&amp;C45)</f>
+        <f>IF(C45="","",B45&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C45)),TRIM(LEFT(C45,FIND(" | ",C45)-1)),C45))</f>
         <v/>
       </c>
     </row>
@@ -23948,7 +26088,7 @@
         <v/>
       </c>
       <c r="P46" s="14">
-        <f>IF(C46="","",B46&amp;"|"&amp;C46)</f>
+        <f>IF(C46="","",B46&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C46)),TRIM(LEFT(C46,FIND(" | ",C46)-1)),C46))</f>
         <v/>
       </c>
     </row>
@@ -24002,7 +26142,7 @@
         <v/>
       </c>
       <c r="P47" s="14">
-        <f>IF(C47="","",B47&amp;"|"&amp;C47)</f>
+        <f>IF(C47="","",B47&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C47)),TRIM(LEFT(C47,FIND(" | ",C47)-1)),C47))</f>
         <v/>
       </c>
     </row>
@@ -24056,7 +26196,7 @@
         <v/>
       </c>
       <c r="P48" s="14">
-        <f>IF(C48="","",B48&amp;"|"&amp;C48)</f>
+        <f>IF(C48="","",B48&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C48)),TRIM(LEFT(C48,FIND(" | ",C48)-1)),C48))</f>
         <v/>
       </c>
     </row>
@@ -24110,7 +26250,7 @@
         <v/>
       </c>
       <c r="P49" s="14">
-        <f>IF(C49="","",B49&amp;"|"&amp;C49)</f>
+        <f>IF(C49="","",B49&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C49)),TRIM(LEFT(C49,FIND(" | ",C49)-1)),C49))</f>
         <v/>
       </c>
     </row>
@@ -24164,7 +26304,7 @@
         <v/>
       </c>
       <c r="P50" s="14">
-        <f>IF(C50="","",B50&amp;"|"&amp;C50)</f>
+        <f>IF(C50="","",B50&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C50)),TRIM(LEFT(C50,FIND(" | ",C50)-1)),C50))</f>
         <v/>
       </c>
     </row>
@@ -24218,7 +26358,7 @@
         <v/>
       </c>
       <c r="P51" s="14">
-        <f>IF(C51="","",B51&amp;"|"&amp;C51)</f>
+        <f>IF(C51="","",B51&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",C51)),TRIM(LEFT(C51,FIND(" | ",C51)-1)),C51))</f>
         <v/>
       </c>
     </row>
@@ -24265,8 +26405,8 @@
     <dataValidation sqref="F12:F51" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ilość ujemna" error="Ilość nie może być ujemna." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="C12:C51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT("Lista_"&amp;B12)</formula1>
+    <dataValidation sqref="C12:C51" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="NR PIGMENTU" prompt="Wybierz pigment z listy (baza = SYSTEM w tym wierszu). Nie wpisuj kodu ręcznie." type="list">
+      <formula1>=INDIRECT(IF($B12="DUXONE",LISTY!$K$9,LISTY!$J$9))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30755,7 +32895,7 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>IF(OR(B4="",B5=""),"",B4&amp;"|"&amp;B5)</f>
+        <f>IF(OR(B4="",B5=""),"",B4&amp;"|"&amp;IF(ISNUMBER(FIND(" | ",B5)),TRIM(LEFT(B5,FIND(" | ",B5)-1)),B5))</f>
         <v/>
       </c>
       <c r="C6">
@@ -31135,8 +33275,8 @@
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Niedozwolona wartość" error="Wybierz wartość z listy." promptTitle="Wybór" prompt="Wybierz z listy rozwijanej." type="list">
       <formula1>=Lista_Systemow</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT("Lista_"&amp;B4)</formula1>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="NR PIGMENTU" prompt="Wybierz pigment z listy (baza = SYSTEM w tym wierszu). Nie wpisuj kodu ręcznie." type="list">
+      <formula1>=INDIRECT(IF($B4="DUXONE",LISTY!$K$9,LISTY!$J$9))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
+++ b/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>Makro ImportujZPdf: wskaż PDF receptury Autocolor/Duxone (kody + ilości w g). WczytajOstatniImport ładuje data/import/ostatni.json. Tint chart bez ilości = komunikat, bez zmiany składu.</t>
+          <t>Makro ImportujZPdf: natychmiast okno Windows (jak Eksplorator), filtr PDF. WczytajOstatniImport ładuje data/import/ostatni.json. Anulowanie i tint chart bez ilości = komunikat, bez zmiany składu.</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Wskaż PDF przyciskiem albo: Narzędzia → Makra → ImportujZPdf</t>
+          <t>Przycisk otwiera okno Windows (jak Eksplorator). Anulowanie nie czyści składu.</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>Przykład testowy: data/import/przyklad_receptura_test.pdf. Przewodniki tint chart (bez kolumny ilości) nie są recepturą — pojawi się „nie znaleziono receptury”, skład nie zostanie wyczyszczony.</t>
+          <t>Przycisk Importuj otwiera natywne okno Windows (PDF). Anulowanie nie czyści składu. Przykład testowy: data/import/przyklad_receptura_test.pdf. Przewodniki tint chart (bez kolumny ilości) nie są recepturą — pojawi się „nie znaleziono receptury”.</t>
         </is>
       </c>
     </row>

--- a/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
+++ b/receptury-lakiery/RECEPTURY_LAKIERY.xlsx
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Przycisk otwiera okno Windows (jak Eksplorator). Anulowanie nie czyści składu.</t>
+          <t>Przycisk Importuj → od razu okno Otwórz (PDF). Gdy martwy: Narzędzia→Makra→ImportujZPdf.</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>Przycisk Importuj otwiera natywne okno Windows (PDF). Anulowanie nie czyści składu. Przykład testowy: data/import/przyklad_receptura_test.pdf. Przewodniki tint chart (bez kolumny ilości) nie są recepturą — pojawi się „nie znaleziono receptury”.</t>
+          <t>Kliknij Importuj recepturę z PDF — od razu otworzy się okno Otwórz (jak Eksplorator), filtr PDF. Gdy przycisk nie działa: Narzędzia → Makra → Uruchom makro → Standard → modReceptury → ImportujZPdf. Przykład: data/import/przyklad_receptura_test.pdf. Tint chart bez ilości = „nie znaleziono receptury”.</t>
         </is>
       </c>
     </row>
